--- a/data/input/adidas.xlsx
+++ b/data/input/adidas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CC343B-9ABC-4A4F-B0DF-6A486C727623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1C17BB-63C3-8B43-ACDE-66712D840BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2260" yWindow="600" windowWidth="26540" windowHeight="17400" activeTab="3" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="5900" yWindow="600" windowWidth="22900" windowHeight="17400" activeTab="2" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="277">
   <si>
     <t>ID</t>
   </si>
@@ -246,87 +246,9 @@
     <t>neutral</t>
   </si>
   <si>
-    <t>posiitve</t>
-  </si>
-  <si>
     <t>negative</t>
   </si>
   <si>
-    <t>DEU20A06-02</t>
-  </si>
-  <si>
-    <t>DEU20A06-01</t>
-  </si>
-  <si>
-    <t>DEU20A06-00</t>
-  </si>
-  <si>
-    <t>DEU20A07-01</t>
-  </si>
-  <si>
-    <t>DEU20A07-00</t>
-  </si>
-  <si>
-    <t>DEU20A07-02</t>
-  </si>
-  <si>
-    <t>DEU20A07-03</t>
-  </si>
-  <si>
-    <t>DEU20A08-00</t>
-  </si>
-  <si>
-    <t>DEU20A08-01</t>
-  </si>
-  <si>
-    <t>DEU20A08-02</t>
-  </si>
-  <si>
-    <t>DEU20A09-00</t>
-  </si>
-  <si>
-    <t>DEU20A09-01</t>
-  </si>
-  <si>
-    <t>DEU20A10-00</t>
-  </si>
-  <si>
-    <t>DEU20A10-01</t>
-  </si>
-  <si>
-    <t>DEU20A10-02</t>
-  </si>
-  <si>
-    <t>DEU20A04-00</t>
-  </si>
-  <si>
-    <t>DEU20A04-01</t>
-  </si>
-  <si>
-    <t>DEU20A05-00</t>
-  </si>
-  <si>
-    <t>DEU20A05-01</t>
-  </si>
-  <si>
-    <t>DEU20A03-02</t>
-  </si>
-  <si>
-    <t>DEU20A03-01</t>
-  </si>
-  <si>
-    <t>DEU20A03-00</t>
-  </si>
-  <si>
-    <t>DEU20A02-02</t>
-  </si>
-  <si>
-    <t>DEU20A02-01</t>
-  </si>
-  <si>
-    <t>DEU20A02-00</t>
-  </si>
-  <si>
     <t>The company emphasizes how it used the challenges of 2020 to improve adidas and drive positive organizational change.</t>
   </si>
   <si>
@@ -414,9 +336,6 @@
     <t>Introduces an expression of appreciation toward the company’s stakeholders.</t>
   </si>
   <si>
-    <t>DEU20A10-03</t>
-  </si>
-  <si>
     <t>Expresses care and well wishes toward the recipients at the close of the communication.</t>
   </si>
   <si>
@@ -424,9 +343,6 @@
   </si>
   <si>
     <t>Expresses appreciation for employees and recognizes their resilience and commitment during a challenging year.</t>
-  </si>
-  <si>
-    <t>DEU20A10-04</t>
   </si>
   <si>
     <t>And I would also like to say thank you to you, our shareholders, for the trust you have placed in us. We will continue to do everything we can to remain worthy of this trust.</t>
@@ -543,6 +459,441 @@
   </si>
   <si>
     <t>DEU23A00-00</t>
+  </si>
+  <si>
+    <t>DEU20A01-04</t>
+  </si>
+  <si>
+    <t>DEU20A01-05</t>
+  </si>
+  <si>
+    <t>DEU20A01-06</t>
+  </si>
+  <si>
+    <t>DEU20A01-07</t>
+  </si>
+  <si>
+    <t>DEU20A01-08</t>
+  </si>
+  <si>
+    <t>DEU20A01-09</t>
+  </si>
+  <si>
+    <t>DEU20A01-10</t>
+  </si>
+  <si>
+    <t>DEU20A01-11</t>
+  </si>
+  <si>
+    <t>DEU20A01-12</t>
+  </si>
+  <si>
+    <t>DEU20A01-13</t>
+  </si>
+  <si>
+    <t>DEU20A01-14</t>
+  </si>
+  <si>
+    <t>DEU20A01-15</t>
+  </si>
+  <si>
+    <t>DEU20A01-16</t>
+  </si>
+  <si>
+    <t>DEU20A01-17</t>
+  </si>
+  <si>
+    <t>DEU20A01-18</t>
+  </si>
+  <si>
+    <t>DEU20A01-19</t>
+  </si>
+  <si>
+    <t>DEU20A01-20</t>
+  </si>
+  <si>
+    <t>DEU20A01-21</t>
+  </si>
+  <si>
+    <t>DEU20A01-22</t>
+  </si>
+  <si>
+    <t>DEU20A01-23</t>
+  </si>
+  <si>
+    <t>DEU20A01-24</t>
+  </si>
+  <si>
+    <t>DEU20A01-25</t>
+  </si>
+  <si>
+    <t>DEU20A01-26</t>
+  </si>
+  <si>
+    <t>DEU20A01-27</t>
+  </si>
+  <si>
+    <t>DEU20A01-28</t>
+  </si>
+  <si>
+    <t>DEU20A01-29</t>
+  </si>
+  <si>
+    <t>DEU20A01-30</t>
+  </si>
+  <si>
+    <t>DEU21A01-00</t>
+  </si>
+  <si>
+    <t>DEU21A01-01</t>
+  </si>
+  <si>
+    <t>DEU21A01-02</t>
+  </si>
+  <si>
+    <t>DEU21A01-03</t>
+  </si>
+  <si>
+    <t>DEU21A01-04</t>
+  </si>
+  <si>
+    <t>DEU21A01-05</t>
+  </si>
+  <si>
+    <t>DEU21A01-06</t>
+  </si>
+  <si>
+    <t>DEU21A01-07</t>
+  </si>
+  <si>
+    <t>DEU21A01-08</t>
+  </si>
+  <si>
+    <t>DEU21A01-09</t>
+  </si>
+  <si>
+    <t>DEU21A01-10</t>
+  </si>
+  <si>
+    <t>DEU21A01-11</t>
+  </si>
+  <si>
+    <t>DEU21A01-12</t>
+  </si>
+  <si>
+    <t>DEU21A01-13</t>
+  </si>
+  <si>
+    <t>DEU21A01-14</t>
+  </si>
+  <si>
+    <t>DEU21A01-15</t>
+  </si>
+  <si>
+    <t>DEU21A01-16</t>
+  </si>
+  <si>
+    <t>DEU21A01-17</t>
+  </si>
+  <si>
+    <t>DEU21A01-18</t>
+  </si>
+  <si>
+    <t>DEU21A01-19</t>
+  </si>
+  <si>
+    <t>DEU21A01-20</t>
+  </si>
+  <si>
+    <t>DEU21A01-21</t>
+  </si>
+  <si>
+    <t>DEU21A01-22</t>
+  </si>
+  <si>
+    <t>DEU21A01-23</t>
+  </si>
+  <si>
+    <t>DEU21A01-24</t>
+  </si>
+  <si>
+    <t>DEU21A01-25</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bjørn Gulden </t>
+  </si>
+  <si>
+    <t>Interview</t>
+  </si>
+  <si>
+    <t>adidas is a company like no other. We have all the ingredients to win.</t>
+  </si>
+  <si>
+    <t>HELLO BJØRN, AND WELCOME TO THE THREE STRIPES. OR SHOULD WE RATHER SAY: ‘WELCOME BACK’ TO THE THREE STRIPES?</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>Well, you can say both. It’s a ‘welcome’ and of course it’s a ‘welcome back’ and I appreciate both. It’s like coming home to the brand I have always had strong feelings for. My father was an adidas player and I played sports in adidas all the time when I was a kid. And of course, it was my first job. I followed adidas even when I was working in different parts of the industry, so being allowed to come back is a great honor.</t>
+  </si>
+  <si>
+    <t>HOW DID IT FEEL COMING TO THE OFFICE AS ADIDAS CEO AT THE BEGINNING OF THE YEAR?</t>
+  </si>
+  <si>
+    <t>Walking into the building gave me a very positive feeling. Of course, I’m aware that things are not great and that the expectation is on us that we will improve. And I can sense that hope.</t>
+  </si>
+  <si>
+    <t>YOU’VE BEEN AN ATHLETE ALMOST YOUR ENTIRE LIFE AND NOW YOU’RE THE CEO OF ADIDAS. HOW HAS SPORT SHAPED YOUR LIFE AND YOUR LEADERSHIP STYLE?</t>
+  </si>
+  <si>
+    <t>Well, sport is my life. Because my father was a professional athlete, I did all kinds of sports when I was a – from skiing and track and field to handball and football. I went on to play football and handball kid professionally, but unfortunately, an injury ended my career early. My wife was a national champion in gymnastics, and my sons played football at a high level. I spend almost 100% of my time with things that are related to sports.</t>
+  </si>
+  <si>
+    <t>I have a bachelor’s degree and I have a master’s, but the one thing that has taught me the most about leadership is playing team sports. You play with people you like, with people you don’t like, or who are better than you, worse than you, and you must find a spot where you can have the biggest influence on the team. I’ve learned a lot from sport and I’m still learning alot.</t>
+  </si>
+  <si>
+    <t>YOU DESCRIBE YOURSELF AS A ‘SPORTS ROMANTIC.’ WHAT DO YOU MEAN BY THAT?</t>
+  </si>
+  <si>
+    <t>I think all sports are important. There’s a tendency to focus on the big ones like football, basketball and running, but smaller sports are just as interesting. I always felt that Adi Dassler was also a sports romantic, trying to deliver the best equipment for all sports. And I have the same philosophy. Visibility across many sports brings a lot of worth because that will give us credibility. That’s why I’m a sports romantic. I love all sports.</t>
+  </si>
+  <si>
+    <t>YOU MENTIONED TEAM SPORTS EARLIER. HOW DO YOU BUILD A WINNING TEAM?</t>
+  </si>
+  <si>
+    <t>Well, it’s difficult to say how I build a winning team because the word ‘I’ is a little bit misleading. I think we build winning teams by showing respect for each other, playing to each other’s individual strengths and trying to make our colleagues better. That’s the best formula. When you look at the Football World Cup, the best team on paper doesn’t always win. Often, the team that comes together and acts like a team wins.</t>
+  </si>
+  <si>
+    <t>Of course, you need a coach, and you need captains. In the end, we need to remember that a bad coach can make a good team bad, but a great coach alone can’t make a bad team good. All the players need to play their roles and make their teammates better, not only themselves. Those are the teams that will win in the future.</t>
+  </si>
+  <si>
+    <t>Then there’s the culture of the company. We’re operating in so many different markets that we are dependent on a truly multicultural team. I also think our workplace should be the most fun place to be. We should laugh a lot and we should not take ourselves too seriously. We should be allowed to be different, and we need to show each other respect. It doesn’t matter who you are or what job you have, we are all adidas. With this comes the team spirit that we will need to win.</t>
+  </si>
+  <si>
+    <t>NOW LET’S SHIFT GEARS AND TALK ABOUT THE BUSINESS. WHAT’S YOUR VIEW ON THE CURRENT STATE OF AFFAIRS?</t>
+  </si>
+  <si>
+    <t>You look at the numbers and it’s obvious that we’re not performing the way we should. I have said it many times, but we have all the ingredients to win: We have a great brand, we have credibility, we have authenticity, we have innovation, we have collaborations, we have very talented people, and we have a global network.</t>
+  </si>
+  <si>
+    <t>But covid-19 brought problems for adidas that maybe weren’t addressed as pragmatically as they should have been. Now we are locked into a strategy that isn’t really tied to how the world has changed – pandemic and everything that came after.</t>
+  </si>
+  <si>
+    <t>Now we should please our multi-brand retail partners and their consumers. They need to see strong income, but we also need strong direct-to-consumer sales for ourselves. We have to deal with all these channels in an optimized way and with more discipline in how we go to market.</t>
+  </si>
+  <si>
+    <t>We know 2022 was a difficult year and 2023 won’t be much easier. Our entire industry has suffered from high inventory levels and, as a result, there is a lot of discounting going on in the marketplace.</t>
+  </si>
+  <si>
+    <t>But we do have some winners, especially in the performance area. We have a very good football business with great new concepts and products, and we’ve made huge progress in running, which is maybe the most difficult area to qualify in. I love to see that we’ve established ourselves in the outdoor industry, our golf business is doing well, and we have some exciting things coming up in basketball.</t>
+  </si>
+  <si>
+    <t>On the lifestyle side, we have collaborations with Gucci, Prada, Moncler, and more. I think when people say we’re not exciting, maybe sometimes we are too exciting and don’t celebrate the individual wins because we have so many. I’m sure that if we get some time, we can – and will – turn this into a very successful formula. Again, we just need to work a little bit more on the basics.</t>
+  </si>
+  <si>
+    <t>WHAT DOES ADIDAS NEED TO FOCUS ON TO GET BACK ON TRACK?</t>
+  </si>
+  <si>
+    <t>We need to focus on the core of our business, which is design, development, sourcing, marketing, selling, and delivering product. We should never forget that we are a shoe, apparel, and accessories brand that sells physical product. Everything around that should support this, so right now, that means focusing on the product, on how we go-to-market and being the most service-minded organization both to our retail partners and the consumer.</t>
+  </si>
+  <si>
+    <t>We should be the most liked brand by both athletes and by those who are influential in our business. We need to create the best product and must always remember that our consumers – although informed globally – still think and act locally.</t>
+  </si>
+  <si>
+    <t>WHAT’S YOUR VIEW ON THE IMPORTANCE OF OUR MARKETS?</t>
+  </si>
+  <si>
+    <t>During covid-19, markets drifted away from each other. China was open and closed at the same time, the US was open, but Europe was closed – that meant that the launch of products and the flow of our industry switched from being very global to very local. The political tensions and economic chaos of the last three years have also fed into this.</t>
+  </si>
+  <si>
+    <t>The needs in China might be different to those in Germany or in North America. This local focus of giving the consumer what they want has to be top of mind. You cannot tell the consumer what they want. We need to listen to what our consumers want from us. Yes, they are influenced by global athletes, global celebrities, and global products, but we also need to accept that there are local influences. We need to find that balance.</t>
+  </si>
+  <si>
+    <t>We can also optimize our go-to-market processes. Speed has become more important, and we need to be more agile. Things change quickly, and we need to move with this change to stay relevant in the eyes of our consumer.</t>
+  </si>
+  <si>
+    <t>DO YOU WANT TO FOCUS ON SPECIFIC MARKETS?</t>
+  </si>
+  <si>
+    <t>Saying that, as our home market, we should be market leader in Europe. We also know that if you’re not successful in North America, you’re not really a global brand. China has been a growth driver for us. Because of the pandemic and other challenges, however, we ’re not where we used to be, but I have a feeling that things will improve there. Latin America is on fire, which makes me optimistic. And then, there are markets like Korea and Japan which are very directional and very fashion oriented. Here we have a real opportunity to grow.</t>
+  </si>
+  <si>
+    <t>They will be treated equally, yet individually. I think it’s wrong to set priorities and say that one market is more important than the other, we should be strong in every market and tailor our approach for each individual one.</t>
+  </si>
+  <si>
+    <t>So, to win in every market, we need to work more closely with our accounts to find out what works and what doesn’t. If you have a good product and the retailer wants it, our consumers will probably buy it. If the retailer doesn’t want it, then it’s likely the consumer doesn’t want it either.</t>
+  </si>
+  <si>
+    <t>We have both physical stores and e-com sites, so we can always bring whatever we want to market and test it. We’re already sitting on a lot of consumer insights which could definitely help us win in the markets.</t>
+  </si>
+  <si>
+    <t>TALKING ABOUT INSIGHTS AND TRENDS, WHAT TRENDS IN THE INDUSTRY DO YOU SEE RIGHT NOW?</t>
+  </si>
+  <si>
+    <t>There are so many mega trends that are good for us as a company, but the one that I’ve liked most is that, during covid-19, people have been coming back to sports. They’re becoming more health conscious and embracing individual sports – especially in the outdoors – like walking, running, biking, and skiing. There’s also growth in yoga, pilates and a variety of other sports, and that’s very good for us!</t>
+  </si>
+  <si>
+    <t>The workplace is becoming more casual, and people are wearing sneakers and branded sweatshirts to work. It’s clear that working from home has led people to become more casual in every aspect of their lives.</t>
+  </si>
+  <si>
+    <t>Last year also saw the Samba and the Gazelle become that special look everyone wanted. This is something that we own and it’s very, very hot. It has happened organically over the last six to nine months and it’s a trend that we’re really exploiting.</t>
+  </si>
+  <si>
+    <t>ADIDAS HAS ALWAYS HAD A STRONG FOCUS ON SUSTAINABILITY. HOW IMPORTANT IS THIS TOPIC TO YOU?</t>
+  </si>
+  <si>
+    <t>For me, sustainability is a focus all companies must have. Doing things that are good for the next generation – for the planet – is a value that we should all have. This industry – and especially adidas – has done a lot of good stuff for the planet over the last 30 years. Back then, we didn’t think about it at all and look where we are now.</t>
+  </si>
+  <si>
+    <t>Our company has set very clear targets on what we want to achieve, and we will do exactly that. Sustainability is going to be one of the things that every employee – especially those working on product – needs to know about. It’s not something we can delegate to just one department, I believe that everybody in the company needs to have knowledge in this</t>
+  </si>
+  <si>
+    <t>WHAT ARE YOU MOST LOOKING FORWARD TO IN 2023?</t>
+  </si>
+  <si>
+    <t>Well, I look forward to the big sporting events including the FIFA World Cup 2023 in Australia and New Zealand. On the business side, I’m looking forward to making progress on our turnaround and showing our people that we can make a positive shift. Although we have problems in the short term, we can get back to where we belong.</t>
+  </si>
+  <si>
+    <t>DO YOU HAVE ANY FINAL MESSAGE FOR OUR SHAREHOLDERS?</t>
+  </si>
+  <si>
+    <t>adidas is a company like no other. There’s probably no other brand in the world that is as emotional as adidas. We are relevant in sport, in music, in entertainment, and in fashion. Our appeal is global and stretches over multiple generations. And when I look to the future, I see people doing more sport, dressing more casually and being even more brand-driven. Given all this, I think we’re a great company to invest in.</t>
+  </si>
+  <si>
+    <t>DEU22A01-00</t>
+  </si>
+  <si>
+    <t>DEU22A02-00</t>
+  </si>
+  <si>
+    <t>DEU22A03-00</t>
+  </si>
+  <si>
+    <t>DEU22A04-00</t>
+  </si>
+  <si>
+    <t>DEU22A05-00</t>
+  </si>
+  <si>
+    <t>DEU22A06-00</t>
+  </si>
+  <si>
+    <t>DEU22A07-00</t>
+  </si>
+  <si>
+    <t>DEU22A08-00</t>
+  </si>
+  <si>
+    <t>DEU22A09-00</t>
+  </si>
+  <si>
+    <t>DEU22A10-00</t>
+  </si>
+  <si>
+    <t>DEU22A11-00</t>
+  </si>
+  <si>
+    <t>DEU22A12-00</t>
+  </si>
+  <si>
+    <t>DEU22A01-01</t>
+  </si>
+  <si>
+    <t>DEU22A02-01</t>
+  </si>
+  <si>
+    <t>DEU22A03-01</t>
+  </si>
+  <si>
+    <t>DEU22A03-02</t>
+  </si>
+  <si>
+    <t>DEU22A04-01</t>
+  </si>
+  <si>
+    <t>DEU22A05-01</t>
+  </si>
+  <si>
+    <t>DEU22A05-02</t>
+  </si>
+  <si>
+    <t>DEU22A05-03</t>
+  </si>
+  <si>
+    <t>DEU22A06-01</t>
+  </si>
+  <si>
+    <t>DEU22A06-02</t>
+  </si>
+  <si>
+    <t>DEU22A06-03</t>
+  </si>
+  <si>
+    <t>DEU22A06-04</t>
+  </si>
+  <si>
+    <t>DEU22A06-05</t>
+  </si>
+  <si>
+    <t>DEU22A06-06</t>
+  </si>
+  <si>
+    <t>DEU22A07-01</t>
+  </si>
+  <si>
+    <t>DEU22A07-02</t>
+  </si>
+  <si>
+    <t>DEU22A08-01</t>
+  </si>
+  <si>
+    <t>DEU22A08-02</t>
+  </si>
+  <si>
+    <t>DEU22A08-03</t>
+  </si>
+  <si>
+    <t>DEU22A09-01</t>
+  </si>
+  <si>
+    <t>DEU22A09-02</t>
+  </si>
+  <si>
+    <t>DEU22A09-03</t>
+  </si>
+  <si>
+    <t>DEU22A09-04</t>
+  </si>
+  <si>
+    <t>DEU22A10-01</t>
+  </si>
+  <si>
+    <t>DEU22A10-02</t>
+  </si>
+  <si>
+    <t>DEU22A10-03</t>
+  </si>
+  <si>
+    <t>DEU22A11-01</t>
+  </si>
+  <si>
+    <t>DEU22A11-02</t>
+  </si>
+  <si>
+    <t>DEU22A12-01</t>
+  </si>
+  <si>
+    <t>DEU22A13-00</t>
+  </si>
+  <si>
+    <t>DEU22A13-01</t>
+  </si>
+  <si>
+    <t>answer</t>
   </si>
 </sst>
 </file>
@@ -788,6 +1139,36 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -797,6 +1178,9 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -828,39 +1212,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -885,144 +1236,144 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:L33" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:L33" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
   <autoFilter ref="A1:L33" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L33">
     <sortCondition ref="A1:A33"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="60"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="81"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="80"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="79"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="78"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="77"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="76"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="74"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="73"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="72"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="71"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L28" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L28" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="A1:L28" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="81"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="80"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="79"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="78"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="77"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="76"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="75"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="74"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="73"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:L2" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:L45" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L45" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="CEO" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="CEO" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:L2" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:L2" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{EBE99108-B696-314E-A6F0-B2F5F90A863B}" name="ID" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{5D56DC3C-B713-2740-963B-AFE8AEFCCDC5}" name="Text" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{9B2B6519-1CB7-7F49-BB9C-204F11C40D79}" name="Text_type" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{5BA923F9-441B-A649-8784-2B77025D0C03}" name="Leadership_context" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{9F6AE6B8-C490-2940-B971-430EDC2EEE65}" name="Information_valence" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="CEO" dataDxfId="29"/>
-    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{EBE99108-B696-314E-A6F0-B2F5F90A863B}" name="ID" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{5D56DC3C-B713-2740-963B-AFE8AEFCCDC5}" name="Text" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{9B2B6519-1CB7-7F49-BB9C-204F11C40D79}" name="Text_type" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{5BA923F9-441B-A649-8784-2B77025D0C03}" name="Leadership_context" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{9F6AE6B8-C490-2940-B971-430EDC2EEE65}" name="Information_valence" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="CEO" dataDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:L2" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:L2" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="CEO" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="CEO" dataDxfId="29"/>
+    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{98E4B810-202A-7E4C-B2C6-35D4404CA885}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{98E4B810-202A-7E4C-B2C6-35D4404CA885}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{1EDFD034-5D27-3548-B9B9-99583075B81D}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{EFC7714F-3B4F-2845-B40A-79112F4B2DEE}" name="Text" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{5D67890B-5706-D740-BEC3-312FE72ADCFA}" name="Text_type" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{E9A847B5-7204-E54B-A14E-1A948434EC56}" name="Leadership_context" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{BD19C5B7-6C1E-9E43-82A8-7B117D5E0919}" name="Information_valence" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{066F6E4C-E842-4E43-A4B5-EF5133865DBD}" name="Communication_type" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{3D9145EE-B2AE-EA43-B6FF-544CF963E633}" name="Company" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{645C94BF-8E35-754B-B12E-328B4734CE50}" name="Country" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{8EF94B9F-4FD1-7A4E-97D7-9DA2D47E3DD5}" name="Year" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{CFE7CD80-3AA1-9041-8B91-270DDA32612B}" name="Covid" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{77CD3889-4929-7348-B4F3-E407474AFD4D}" name="CEO" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{276FB6D5-C797-B046-B256-4A051057EA9E}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{1EDFD034-5D27-3548-B9B9-99583075B81D}" name="ID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{EFC7714F-3B4F-2845-B40A-79112F4B2DEE}" name="Text" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{5D67890B-5706-D740-BEC3-312FE72ADCFA}" name="Text_type" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{E9A847B5-7204-E54B-A14E-1A948434EC56}" name="Leadership_context" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{BD19C5B7-6C1E-9E43-82A8-7B117D5E0919}" name="Information_valence" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{066F6E4C-E842-4E43-A4B5-EF5133865DBD}" name="Communication_type" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{3D9145EE-B2AE-EA43-B6FF-544CF963E633}" name="Company" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{645C94BF-8E35-754B-B12E-328B4734CE50}" name="Country" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{8EF94B9F-4FD1-7A4E-97D7-9DA2D47E3DD5}" name="Year" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{CFE7CD80-3AA1-9041-8B91-270DDA32612B}" name="Covid" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{77CD3889-4929-7348-B4F3-E407474AFD4D}" name="CEO" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{276FB6D5-C797-B046-B256-4A051057EA9E}" name="Comment" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1432,7 +1783,7 @@
         <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -1470,7 +1821,7 @@
         <v>19</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="85" x14ac:dyDescent="0.2">
@@ -1508,7 +1859,7 @@
         <v>19</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="68" x14ac:dyDescent="0.2">
@@ -1525,7 +1876,7 @@
         <v>59</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>26</v>
@@ -1546,7 +1897,7 @@
         <v>19</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="119" x14ac:dyDescent="0.2">
@@ -1584,12 +1935,12 @@
         <v>19</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>21</v>
@@ -1622,12 +1973,12 @@
         <v>19</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>20</v>
@@ -1660,12 +2011,12 @@
         <v>19</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>13</v>
@@ -1698,12 +2049,12 @@
         <v>19</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -1736,12 +2087,12 @@
         <v>19</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
@@ -1774,12 +2125,12 @@
         <v>19</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="141" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>30</v>
@@ -1791,7 +2142,7 @@
         <v>58</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>26</v>
@@ -1812,12 +2163,12 @@
         <v>19</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>31</v>
@@ -1850,12 +2201,12 @@
         <v>19</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>44</v>
@@ -1888,12 +2239,12 @@
         <v>19</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>32</v>
@@ -1926,12 +2277,12 @@
         <v>19</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="157" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>45</v>
@@ -1964,12 +2315,12 @@
         <v>19</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>33</v>
@@ -2002,12 +2353,12 @@
         <v>19</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>46</v>
@@ -2040,12 +2391,12 @@
         <v>19</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>47</v>
@@ -2078,12 +2429,12 @@
         <v>19</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>34</v>
@@ -2116,12 +2467,12 @@
         <v>19</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>48</v>
@@ -2154,12 +2505,12 @@
         <v>19</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="309" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>52</v>
@@ -2192,12 +2543,12 @@
         <v>19</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>57</v>
@@ -2230,12 +2581,12 @@
         <v>19</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>35</v>
@@ -2268,12 +2619,12 @@
         <v>19</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>49</v>
@@ -2306,12 +2657,12 @@
         <v>19</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>50</v>
@@ -2344,12 +2695,12 @@
         <v>19</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>36</v>
@@ -2382,15 +2733,15 @@
         <v>19</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="323" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>55</v>
@@ -2420,12 +2771,12 @@
         <v>19</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>37</v>
@@ -2458,15 +2809,15 @@
         <v>19</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>55</v>
@@ -2475,7 +2826,7 @@
         <v>61</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>26</v>
@@ -2496,15 +2847,15 @@
         <v>19</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>55</v>
@@ -2534,15 +2885,15 @@
         <v>19</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>55</v>
@@ -2550,16 +2901,34 @@
       <c r="D32" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="E32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="I32" s="1">
-        <v>2020</v>
+        <v>2021</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>38</v>
@@ -2592,7 +2961,7 @@
         <v>19</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2660,10 +3029,10 @@
     </row>
     <row r="2" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>27</v>
@@ -2694,9 +3063,15 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>26</v>
       </c>
@@ -2717,8 +3092,14 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>160</v>
+      </c>
       <c r="B4" s="4" t="s">
-        <v>141</v>
+        <v>113</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>26</v>
@@ -2740,8 +3121,14 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="B5" s="4" t="s">
-        <v>129</v>
+        <v>101</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>26</v>
@@ -2763,8 +3150,14 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>162</v>
+      </c>
       <c r="B6" s="4" t="s">
-        <v>142</v>
+        <v>114</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>26</v>
@@ -2786,8 +3179,14 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>163</v>
+      </c>
       <c r="B7" s="5" t="s">
-        <v>130</v>
+        <v>102</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>26</v>
@@ -2809,8 +3208,14 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="153" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>164</v>
+      </c>
       <c r="B8" s="4" t="s">
-        <v>143</v>
+        <v>115</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>26</v>
@@ -2832,8 +3237,14 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="B9" s="4" t="s">
-        <v>131</v>
+        <v>103</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>26</v>
@@ -2855,8 +3266,14 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="B10" s="4" t="s">
-        <v>144</v>
+        <v>116</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>26</v>
@@ -2878,8 +3295,14 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>167</v>
+      </c>
       <c r="B11" s="4" t="s">
-        <v>145</v>
+        <v>117</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>26</v>
@@ -2901,8 +3324,14 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="B12" s="4" t="s">
-        <v>132</v>
+        <v>104</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>26</v>
@@ -2924,8 +3353,14 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="B13" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>26</v>
@@ -2947,8 +3382,14 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="B14" s="4" t="s">
-        <v>133</v>
+        <v>105</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>26</v>
@@ -2970,8 +3411,14 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="B15" s="4" t="s">
-        <v>147</v>
+        <v>119</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>26</v>
@@ -2993,8 +3440,14 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>172</v>
+      </c>
       <c r="B16" s="4" t="s">
-        <v>134</v>
+        <v>106</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>26</v>
@@ -3015,9 +3468,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="136" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>173</v>
+      </c>
       <c r="B17" s="4" t="s">
-        <v>148</v>
+        <v>120</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>26</v>
@@ -3038,9 +3497,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>174</v>
+      </c>
       <c r="B18" s="4" t="s">
-        <v>135</v>
+        <v>107</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>26</v>
@@ -3061,9 +3526,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="B19" s="4" t="s">
-        <v>149</v>
+        <v>121</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>26</v>
@@ -3084,9 +3555,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="B20" s="4" t="s">
-        <v>150</v>
+        <v>122</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>26</v>
@@ -3107,9 +3584,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="B21" s="4" t="s">
-        <v>136</v>
+        <v>108</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>26</v>
@@ -3130,9 +3613,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="136" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>178</v>
+      </c>
       <c r="B22" s="4" t="s">
-        <v>151</v>
+        <v>123</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>26</v>
@@ -3153,9 +3642,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>179</v>
+      </c>
       <c r="B23" s="4" t="s">
-        <v>137</v>
+        <v>109</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>26</v>
@@ -3176,9 +3671,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="238" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="238" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>180</v>
+      </c>
       <c r="B24" s="4" t="s">
-        <v>152</v>
+        <v>124</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>26</v>
@@ -3199,9 +3700,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>181</v>
+      </c>
       <c r="B25" s="4" t="s">
-        <v>138</v>
+        <v>110</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>26</v>
@@ -3222,9 +3729,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="204" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>182</v>
+      </c>
       <c r="B26" s="4" t="s">
-        <v>153</v>
+        <v>125</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>26</v>
@@ -3245,9 +3758,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>183</v>
+      </c>
       <c r="B27" s="4" t="s">
-        <v>139</v>
+        <v>111</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>26</v>
@@ -3268,9 +3787,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="187" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="B28" s="4" t="s">
-        <v>154</v>
+        <v>126</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>26</v>
@@ -3292,6 +3817,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -3301,7 +3827,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67123D5B-6676-C646-A1DB-D41767ED6EF5}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -3353,11 +3879,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B2" s="4"/>
+        <v>127</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
@@ -3370,8 +3904,1259 @@
       <c r="J2" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>186</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -3435,7 +5220,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="B2" s="4"/>
       <c r="G2" s="1" t="s">
@@ -3515,7 +5300,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="B2" s="4"/>
       <c r="G2" s="1" t="s">
@@ -3528,7 +5313,7 @@
         <v>2024</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -3595,7 +5380,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="B2" s="4"/>
       <c r="G2" s="1" t="s">
@@ -3608,7 +5393,7 @@
         <v>2025</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/adidas.xlsx
+++ b/data/input/adidas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1C17BB-63C3-8B43-ACDE-66712D840BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFFA0EE-76D0-3E47-A456-7F47168FFFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5900" yWindow="600" windowWidth="22900" windowHeight="17400" activeTab="2" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="2640" yWindow="600" windowWidth="34440" windowHeight="17400" activeTab="3" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="358">
   <si>
     <t>ID</t>
   </si>
@@ -894,6 +894,250 @@
   </si>
   <si>
     <t>answer</t>
+  </si>
+  <si>
+    <t>qu</t>
+  </si>
+  <si>
+    <t>Bjørn, you have now completed your first full year at the helm of adidas. How
+do you look back on the year 2023?</t>
+  </si>
+  <si>
+    <t>I think it was a positive year in the sense that a lot of positive things happened vis-à-vis our consumer. At the beginning of the year, we had little success when it comes to the sell-through of our product. But then, during the year, we had a couple of franchises in the Lifestyle area starting to do very well. And they actually continue to develop very well in 2024. First it was the Terrace trend with Samba, Gazelle, and Spezial, but then also Campus accelerated at the back end of the year. We have been steadily increasing the supply to better please the demand of the consumer and, of course, to also give our retail partners good sell-throughs.</t>
+  </si>
+  <si>
+    <t>In the Performance area, the launch of the Predator was fantastic. This football franchise is probably the best we have ever had. In Running, our athletes continued to win a lot of races and break records. With the Adizero Adios Pro Evo 1 we have the shoe that set completely new standards in terms of performance. The halo effect of these victories in our shoes is that we are starting to build a better distribution for our entire running range. This will take a while, but it’s a positive start. Even in basketball, and I say even because that’s probably the area where we haven’t had the biggest success in the past, the Anthony Edwards signature shoe has been selling out every time we launch a new colorway.</t>
+  </si>
+  <si>
+    <t>Improving the relationship with the retailers was one of your priorities for 2023. What feedback have you been receiving from them?</t>
+  </si>
+  <si>
+    <t>Since we have better products in the market and consumer demand is higher, more and more retailers would like to buy more from us now, which is positive, of course. You have to remember that we started the year 2023 with a lot of inventory in our own warehouses, but also in the warehouses of our retail partners. Sell-through was not good and discounts were high. It took a while to replace the bad inventory with good inventory. And it’s probably fair to say that many of the retailers were skeptical at the beginning. But I have the feeling that during the course of the year, they have seen that the pipeline of our products works. They have seen that they can make money with us. As a result, the trust in adidas has started to come back. I hope that the retailers see that we are a company that really wants to be a partner and that they see this all over the world.</t>
+  </si>
+  <si>
+    <t>That’s a big change from being a DTC-led company, which we were twelve months ago. I would say that the relationship between the retailers and us is also improving in the way we talk and work with each other. More importantly, the results for the retailers are starting to show. When retailers sell more with a better margin of a brand, they like to do more. And that’s always the best argument to improve the business.</t>
+  </si>
+  <si>
+    <t>What changes did you make at the product level to lay the foundation for a better future ?</t>
+  </si>
+  <si>
+    <t>I don’t know if I changed so much. I think if you look at the different categories, then in the Lifestyle area, it’s obvious that we have been very classic-driven. We have been very strong on the courtside, which is Terrace and now also Campus. What I tried to do is to scale that at the right speed at the right time to build and keep the heat. We continue to do collabs and limited editions on all the franchises, but at the same time we also make sure that we increase production and give the retailers more of the products that work. And then we do takedowns of the trends that are happening on the more commercial side. We are doing this on the courtside, and now we have started to do the same in running lifestyle. SL72 and Country are two shoes coming out of our archive that we saw potential in. SL72 is also a Terrace shoe, but in an old running style. So far, it has done very well. And then on top of what we do on the classic side, because of the lack of newness in running lifestyle, we have initiated many projects when it gets to completely new silhouettes. Many of those are seeded into the market as we speak. The goal is that we will have new running silhouettes in the Lifestyle area that the market has never seen before at the back end of this year to be scaled in 2025 and beyond.</t>
+  </si>
+  <si>
+    <t>How about the performance side of the business?</t>
+  </si>
+  <si>
+    <t>Here we also looked at what kind of products do we have in the different categories that are ready to go. And we have accelerated quite a few of them. In running, as I said, the whole Adizero range is very, very successful from a performance point of view. The Adizero Adios Pro Evo 1 was initially planned for 2025 and we accelerated that. Now the goal is to scale running also into other price points and to focus more on the comfort and the value side of running. With the new Supernova, which we just launched, and a completely new UltraBoost and Adistar later in the year, the product pipeline looks very strong. And when it comes to distribution, it will be about having sales reps servicing running specialty again and being more ingrained in the running community where the action is happening.</t>
+  </si>
+  <si>
+    <t>In football, we have what we need from a product, a player, and a team point of view. So here we will continue the strategy as is. In basketball, we’ve done a lot of work. I’m very, very convinced that all our signature shoes for players like Anthony Edwards, James Harden, and Damian Lillard are a lot better in 2024 than they had been before. And I mentioned it before: The first positive results are already coming in. I am also very happy with the initial results of Fear of God. College teams in the NCAA now even play in Fear of God jerseys. In outdoor, we have the right product with Terrex. We have now started to commercialize it, also by taking it down to more commercial price points. Also here the task is more to get  a better distribution.</t>
+  </si>
+  <si>
+    <t>And last but not least, Sportswear: We refocused the business unit to make sure that the entire range is more commercial, that we work closer with the accounts, that we become more local. I am pleased to see that our teams have now connected much better with the market, both with retailers and with the consumer.</t>
+  </si>
+  <si>
+    <t>How have these changes in how you create product and bring them to market also changed how you present the brand vis-à-vis the consumer?</t>
+  </si>
+  <si>
+    <t>When it comes to marketing, the strategy is to be visible in sports. Not only the big sports, but also the smaller sports, if you can even call them smaller because some of them are really meaningful in their region. We invested into cricket in India, we extended our partnership with the All Blacks in rugby. We are trying to sign partners across all sports again for the Olympics. Of course, we will not be able to sign everyone we want, but I think the attitude, again, is to be visible in many sports that adidas previously had left and to clearly show up as the best sports brand again.</t>
+  </si>
+  <si>
+    <t>Many adidas athletes performed extremely well in 2023 and in the first months of 2024: Tigist Assefa, Jude Bellingham, Noah Lyles, Patrick Mahomes, Lionel Messi, Mikaela Shiffrin – just to mention a very few. What do these successes mean to the brand?</t>
+  </si>
+  <si>
+    <t>First of all, we need athletes, teams, and federations that perform. Of course, you would like to be with winners. And then secondly, you would like to have people and teams and federations with the right adidas attitude. I think the ones you mentioned have exactly that. Seeing Mahomes leading his team in the Super Bowl to victory again in our product is simply great. He’s a fantastic athlete with a great attitude and he fits our brand extremely well. It’s the same with the fastest man in the world, Noah Lyles. Or watching Shiffrin skiing down the mountains and breaking records. These are all examples of great performing athletes who also have a great personality that fits our brand so well. I am proud that we can work with them. In my opinion, we have the best group of athletes and sports marketing partners that you can dream about.</t>
+  </si>
+  <si>
+    <t>Have these successes changed the way how consumers perceive the brand?</t>
+  </si>
+  <si>
+    <t>Consumers see the changes particularly in the Lifestyle area. Here we are currently trending in a way adidas hasn’t done for a long time. At many retailers, we have the best sell-through in years, which means that more consumers are buying our products again. As a consequence, consumer sentiment towards adidas is turning positive in almost every market. So brand desire has clearly increased. I always repeat the same thing: I don’t think the consumer ever had anything against adidas. I just think we were not visible and maybe not commercial enough in the way that we went to market. And we’re reversing a lot of that as we speak.</t>
+  </si>
+  <si>
+    <t>This year will be a year of sports, with the UEFA EURO 2024 and the Copa América in football, the Olympic and Paralympic Games in Paris all taking place this summer. How important are these events for the adidas business?</t>
+  </si>
+  <si>
+    <t>They all play a little bit of a different role, but what they have in common is that after years of covid and difficult circumstances for big events with no spectators or limited access, it’s the first year again where everything is largely back to normal. I think both athletes and spectators are looking forward to participating in big events and to celebrating sports and being together again. The summer of sport starts with the UEFA EURO in our home market Germany, which, of course, is very special. We all remember the fantastic atmosphere of the football World Cup 2006 in Germany and I think we will see the same again this year. It will be a very important event, not only for sports, but for people's mindset in general. For us, both the EURO and the Copa also have a business impact, because we sell replicas of the different teams, licensed products and the official match ball for the EURO ‘Fussballliebe.’</t>
+  </si>
+  <si>
+    <t>The Olympics and Paralympics are different because they are not necessarily commercial events where we sell a lot of products directly related to them. But the Olympics and Paralympics both create global and local heroes. And they make sport play a bigger role in people's life all over the world. That’s why in general they have a positive impact on sports companies and especially adidas which is the Olympic brand when you look back at our history. It is really good for us that these sports events all happen in 2024, because that fits perfectly with our plan to be the best sports brand again. It is also perfect timing with the product pipeline and the plans we have for 2024 and beyond.</t>
+  </si>
+  <si>
+    <t>I LOVE TO SEE AND DO SPORTS. IT'S MY LIFE AND MY JOB.</t>
+  </si>
+  <si>
+    <t>You are a big sports fan. Which sports event are you personally looking forward to the most?</t>
+  </si>
+  <si>
+    <t>I look forward to all sports events. It doesn’t matter what it is. If it’s a Bundesliga game or if it’s a national championship, a college tournament or the Olympics, I don’t really separate between the events. I love to see and do sports. It’s my life and my job. There are so many good events and to be honest with you, there are good events almost every day in some kind of sport somewhere in the world. So there’s enough to look forward to and it would be kind of unfair to only pick one.</t>
+  </si>
+  <si>
+    <t>adidas will have an extra moment to celebrate this year as it is also the company’s 75th anniversary. What does this heritage mean for the future?</t>
+  </si>
+  <si>
+    <t>For me personally, the 75 as a number doesn’t mean so much because it doesn’t matter if you’re 75 or 76 or 80. The most important thing is which legacy these 75 years have created for the company. We have such a great sports history, both with products and athletes. Everything you see today is built on this foundation. There is no company in the world that has such a heritage in sports. When you visit our archive and see what we have in there, then you know what I am talking about. Therefore, the 75th anniversary gives us an enormous knowledge and product base to build on. That’s very unique for our company.</t>
+  </si>
+  <si>
+    <t>Putting it all together in 2023, what worked better than you expected?</t>
+  </si>
+  <si>
+    <t>The success in Lifestyle maybe came quicker than we had expected. And the consumer reacted positively to our brand, quicker than I thought. I think I said it when I started at adidas last year: The product pipeline that everybody complained about was much better than people said it was. And adidas had already all the ingredients to be successful. It was just that they were not put together in a way that they were visible enough. In general, although we need time to also get the financial results back to former strength, there are so many good things happening in this company – clearly many more than any negative things. All in all, I think we were a little bit further at the end of 2023 than what I expected when we started.</t>
+  </si>
+  <si>
+    <t>Talking about negative things, were there also some challenges that you didn’t see coming?</t>
+  </si>
+  <si>
+    <t>Well, there’s always challenges. I think that the negativity around the company at the beginning was quite tough to manage. But I think we are in much better territory today and can now focus on the many positive things. One thing we clearly need to continue to tackle is our internal complexity. Although we increased our agility, it still takes us too long to make decisions. But we’re on that and I feel that the attitude and the adidas DNA to do stuff is starting to come through again.</t>
+  </si>
+  <si>
+    <t>Looking forward, how will 2024 shape up from a business point of view?</t>
+  </si>
+  <si>
+    <t>The pipeline of products that is going out to the market will continue to improve quarter by quarter. Therefore, the size of the poor performing inventory, not so much in terms of age, but in terms of overall product strength, that we still have in the trade will actually become less and less compared to good inventory. As a result, sales growth should accelerate quarter by quarter. The external factors are, of course, something nobody can control. When we started a year ago, we didn’t have a crisis in the Middle East, we didn’t have the Red Sea issue. We all had hoped that the war in the Ukraine would end. Now we know that this is unfortunately not the case. So we are still living in a very uncertain world. But I think the companies that are agile and flexible in a volatile world will win. And that’s part of our strategy to be agile and flexible.</t>
+  </si>
+  <si>
+    <t>Last year, when you started, you also laid out a plan to bring adidas back to the top step by step between 2023 and 2026. How confident are you that you are on the right track?</t>
+  </si>
+  <si>
+    <t>One year ago, we described where we were and where we should go. By now, I think we confirmed that we have the ingredients to start turning things around in 2023, be a better company in 2024, be a good company in 2025, and then be a good and profitable company in 2026. From where we are today, everything else being equal in the external world, I am confident that this will happen. As a management team, it is our goal to do things short term that are also right long term. We are not trying to impress anybody short-term by doing something stupid in one quarter to look good that has a negative impact maybe in a year’s time. Our goal is to build adidas back again to be the best sports brand and the best sports company in the world, step by step. A company where people are happy to work, that retailers see as a partner, and where consumers like our product. With everything we know today, that means we can be a company that grows double digits each year and has a double-digit operating margin. It’s doable within the timeline that we talked about.</t>
+  </si>
+  <si>
+    <t>What role will the adidas employees play in this plan?</t>
+  </si>
+  <si>
+    <t>They are the reason that we can have the plan. You have to remember that adidas is the brand and the people. I am 100% sure that we have the talents we need. We have a very global and diverse workforce with people that can bring this company to the top again. I think we need to make sure that we find the right structure and the right processes so that our talented people are able to do their job. And that’s what we are in the process of doing. But, again, people are the most important factor that our company has and always will be. You cannot replace people with machines or computers.</t>
+  </si>
+  <si>
+    <t>That’s good to hear. Last question to you, Bjørn: What’s the one thing you personally want to focus on in 2024?</t>
+  </si>
+  <si>
+    <t>Personally: Enjoy life.</t>
+  </si>
+  <si>
+    <t>WE HAVE A VERY GLOBAL AND DIVERSE WORKFORCE WITH PEOPLE THAT CAN BRINGS THIS COMPANY TO THE TOP AGAIN.</t>
+  </si>
+  <si>
+    <t>THE TRUST IN ADIDAS HAS STARTED TO COME BACK.</t>
+  </si>
+  <si>
+    <t>DEU23A01-00</t>
+  </si>
+  <si>
+    <t>DEU23A02-00</t>
+  </si>
+  <si>
+    <t>DEU23A03-00</t>
+  </si>
+  <si>
+    <t>DEU23A04-00</t>
+  </si>
+  <si>
+    <t>DEU23A05-00</t>
+  </si>
+  <si>
+    <t>DEU23A06-00</t>
+  </si>
+  <si>
+    <t>DEU23A07-00</t>
+  </si>
+  <si>
+    <t>DEU23A08-00</t>
+  </si>
+  <si>
+    <t>DEU23A10-00</t>
+  </si>
+  <si>
+    <t>DEU23A11-00</t>
+  </si>
+  <si>
+    <t>DEU23A12-00</t>
+  </si>
+  <si>
+    <t>DEU23A13-00</t>
+  </si>
+  <si>
+    <t>DEU23A14-00</t>
+  </si>
+  <si>
+    <t>DEU23A15-00</t>
+  </si>
+  <si>
+    <t>DEU23A16-00</t>
+  </si>
+  <si>
+    <t>DEU23A01-01</t>
+  </si>
+  <si>
+    <t>DEU23A01-02</t>
+  </si>
+  <si>
+    <t>DEU23A02-01</t>
+  </si>
+  <si>
+    <t>DEU23A02-02</t>
+  </si>
+  <si>
+    <t>DEU23A03-01</t>
+  </si>
+  <si>
+    <t>DEU23A04-01</t>
+  </si>
+  <si>
+    <t>DEU23A04-02</t>
+  </si>
+  <si>
+    <t>DEU23A04-03</t>
+  </si>
+  <si>
+    <t>DEU23A05-01</t>
+  </si>
+  <si>
+    <t>DEU23A06-01</t>
+  </si>
+  <si>
+    <t>DEU23A07-01</t>
+  </si>
+  <si>
+    <t>DEU23A08-01</t>
+  </si>
+  <si>
+    <t>DEU23A08-02</t>
+  </si>
+  <si>
+    <t>DEU23A11-01</t>
+  </si>
+  <si>
+    <t>DEU23A12-01</t>
+  </si>
+  <si>
+    <t>DEU23A13-01</t>
+  </si>
+  <si>
+    <t>DEU23A14-01</t>
+  </si>
+  <si>
+    <t>DEU23A15-01</t>
+  </si>
+  <si>
+    <t>DEU23A16-01</t>
+  </si>
+  <si>
+    <t>DEU23A17-00</t>
+  </si>
+  <si>
+    <t>DEU23A18-00</t>
+  </si>
+  <si>
+    <t>DEU23A18-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quote </t>
+  </si>
+  <si>
+    <t>DEU23A19-00</t>
+  </si>
+  <si>
+    <t>DEU23A19-01</t>
   </si>
 </sst>
 </file>
@@ -928,15 +1172,21 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF2D0"/>
+        <bgColor rgb="FFDAF2D0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -944,11 +1194,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -965,12 +1228,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="84">
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1082,9 +1357,6 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1098,12 +1370,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1284,32 +1550,32 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:L45" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:L45" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A1:L45" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="CEO" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="CEO" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:L2" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:L41" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+  <autoFilter ref="A1:L41" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
@@ -1319,61 +1585,61 @@
     <tableColumn id="3" xr3:uid="{9B2B6519-1CB7-7F49-BB9C-204F11C40D79}" name="Text_type" dataDxfId="51"/>
     <tableColumn id="4" xr3:uid="{5BA923F9-441B-A649-8784-2B77025D0C03}" name="Leadership_context" dataDxfId="50"/>
     <tableColumn id="5" xr3:uid="{9F6AE6B8-C490-2940-B971-430EDC2EEE65}" name="Information_valence" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="CEO" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="CEO" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:L2" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:L2" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="CEO" dataDxfId="29"/>
-    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="32"/>
+    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="CEO" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{98E4B810-202A-7E4C-B2C6-35D4404CA885}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{98E4B810-202A-7E4C-B2C6-35D4404CA885}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{1EDFD034-5D27-3548-B9B9-99583075B81D}" name="ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{EFC7714F-3B4F-2845-B40A-79112F4B2DEE}" name="Text" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{5D67890B-5706-D740-BEC3-312FE72ADCFA}" name="Text_type" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{E9A847B5-7204-E54B-A14E-1A948434EC56}" name="Leadership_context" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{BD19C5B7-6C1E-9E43-82A8-7B117D5E0919}" name="Information_valence" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{066F6E4C-E842-4E43-A4B5-EF5133865DBD}" name="Communication_type" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{3D9145EE-B2AE-EA43-B6FF-544CF963E633}" name="Company" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{645C94BF-8E35-754B-B12E-328B4734CE50}" name="Country" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{8EF94B9F-4FD1-7A4E-97D7-9DA2D47E3DD5}" name="Year" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{CFE7CD80-3AA1-9041-8B91-270DDA32612B}" name="Covid" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{77CD3889-4929-7348-B4F3-E407474AFD4D}" name="CEO" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{276FB6D5-C797-B046-B256-4A051057EA9E}" name="Comment" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{1EDFD034-5D27-3548-B9B9-99583075B81D}" name="ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{EFC7714F-3B4F-2845-B40A-79112F4B2DEE}" name="Text" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{5D67890B-5706-D740-BEC3-312FE72ADCFA}" name="Text_type" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{E9A847B5-7204-E54B-A14E-1A948434EC56}" name="Leadership_context" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{BD19C5B7-6C1E-9E43-82A8-7B117D5E0919}" name="Information_valence" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{066F6E4C-E842-4E43-A4B5-EF5133865DBD}" name="Communication_type" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{3D9145EE-B2AE-EA43-B6FF-544CF963E633}" name="Company" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{645C94BF-8E35-754B-B12E-328B4734CE50}" name="Country" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{8EF94B9F-4FD1-7A4E-97D7-9DA2D47E3DD5}" name="Year" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{CFE7CD80-3AA1-9041-8B91-270DDA32612B}" name="Covid" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{77CD3889-4929-7348-B4F3-E407474AFD4D}" name="CEO" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{276FB6D5-C797-B046-B256-4A051057EA9E}" name="Comment" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5166,7 +5432,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A697CB44-B7FE-7A44-A57E-2275194E09E2}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -5218,11 +5484,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
@@ -5235,8 +5509,1143 @@
       <c r="J2" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="153" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2026</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2027</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="204" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2028</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2029</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2030</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2031</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2032</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2033</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2034</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2035</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2036</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2037</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2038</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2039</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2040</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2041</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2042</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2043</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="1">
+        <v>2044</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="1">
+        <v>2045</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2046</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="1">
+        <v>2047</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2048</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2049</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2050</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2051</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="1">
+        <v>2052</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2053</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2054</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="1">
+        <v>2055</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="1">
+        <v>2056</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="255" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2057</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2058</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="1">
+        <v>2059</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="1">
+        <v>2060</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="1">
+        <v>2061</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="1">
+        <v>2062</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>186</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -5303,6 +6712,9 @@
         <v>130</v>
       </c>
       <c r="B2" s="4"/>
+      <c r="F2" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
@@ -5314,6 +6726,9 @@
       </c>
       <c r="J2" s="1" t="s">
         <v>128</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -5383,6 +6798,9 @@
         <v>129</v>
       </c>
       <c r="B2" s="4"/>
+      <c r="F2" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
@@ -5394,6 +6812,9 @@
       </c>
       <c r="J2" s="1" t="s">
         <v>128</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/adidas.xlsx
+++ b/data/input/adidas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFFA0EE-76D0-3E47-A456-7F47168FFFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901BE30B-3B4C-7646-A575-33EE12AF09E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="600" windowWidth="34440" windowHeight="17400" activeTab="3" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="10060" yWindow="600" windowWidth="20980" windowHeight="17400" activeTab="4" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="399">
   <si>
     <t>ID</t>
   </si>
@@ -1138,6 +1138,135 @@
   </si>
   <si>
     <t>DEU23A19-01</t>
+  </si>
+  <si>
+    <t>2024 WAS A YEAR THAT CONFIRMED THE STRENGTH OF THE BRAND AND THE POTENTIAL OF THE COMPANY</t>
+  </si>
+  <si>
+    <t>Bjørn, 2024 was spectacular in so many ways. How do you reflect on the past year?</t>
+  </si>
+  <si>
+    <t>2024 was a year that confirmed the strength of the brand and the potential of the company. The turnaround in front of the consumer happened quicker than we had even hoped for, which shows the enormous power that this brand has. It was a busy year and it was a year where our people did a fantastic job. But then we also know that we are not at the end of something. We are just at the beginning.</t>
+  </si>
+  <si>
+    <t>Looking back at the summer of sports, what was your favorite moment?</t>
+  </si>
+  <si>
+    <t>That's difficult! When we started the year, we said that 2024 would be the year of sports and I think it was as good as we expected it to be. The Euro ended up being a fantastic event from the atmosphere of the German people and with fans from all over the world. Stadiums were full. A great tournament and also
+great for us. Just think of what we did with the German team, with the pink away jersey but also with the home jersey! And all the fantastic activations we did, especially in Berlin. And then we went to Paris. There was a lot of negativity before the games and then it ended up probably being the best Olympic and Paralympic Games ever. Full stadiums, great atmosphere and unique facilities. This summer showcased how important sport is, building bridges and bringing happiness to people. It makes me proud to be part of it and shows how important adidas can be for people. A great year for sports.</t>
+  </si>
+  <si>
+    <t>2024 was equally exciting on the product side with several adidas franchises making big waves. What was your favorite product last year?</t>
+  </si>
+  <si>
+    <t>There is too many to just name one. We started to turn around the brand with Originals, with what people now call Terrace or T-toe. First Gazelle, then Samba and Spezial, and we further extended that into Campus and SL72 – all shoes that carry the heritage of the brand. But then when you see what we did in Football, with Predator and F50. What we did in Running, with the Adizero Evo, the Adios Pro 4, and the Evo SL. If you look at our Anthony Edwards signature line in Basketball. It's now so many products that are competitive that we can be competitive in all the categories. We definitely have the pipeline we need to further increase distribution and, with the right marketing, achieve strong sell-throughs. Putting Performance and Lifestyle together, the way we have done it in Football by using the Trefoil on the third jerseys and then build a soccer culture collection around it is very unique. Bringing the past and the present together to create culturally relevant products and stories that come out of sport is something that not many brands can do. We can do it very well and we’re just at the beginning of it.</t>
+  </si>
+  <si>
+    <t>While Terrace and Campus are still very popular, you have significantly evolved the Lifestyle offering beyond this over the past seasons. What has changed over the past 12 months?</t>
+  </si>
+  <si>
+    <t>When we brought back Terrace with the Samba, the Gazelle and the Spezial, we brought back a look that made people reconnect with adidas. It was what we needed to get our product on the cool people to make the brand visible. I think the way we then extended it into Campus and also SL72 worked well and showed that the brand is trending. We have a great setup of classics that people will recognize as franchises when we are heating them up. Now we have Megaride, ZX and Climacool coming, in addition to upcoming silhouettes that haven't been in the market before. Of course, you can't be successful with every new launch in Lifestyle, but I'm not worried about that at all. And then, we have the Superstar. The Superstar is maybe most important in the US, where we’re introducing it as we speak. There will be a lot of activations, from Pharrell to Run DMC. The important thing is that, driven by our momentum, we get more space in retail so that the brand is visible across more categories, both in Lifestyle and Performance. I think for 2025 we are in very good shape already. Now we need to make sure that we also have extensions of what we're doing into 2026 and beyond. We have all the tools and all the resources we need to do that very successfully.</t>
+  </si>
+  <si>
+    <t>Are you happy with how the brand now shows up on the Performance side, too?</t>
+  </si>
+  <si>
+    <t>I'm happy with what we see in the showrooms and what we have in the pipeline. Of course, I'm not happy yet with the way we show up in the trade everywhere, I would love for our products to be more visible. But that is also normal. You can't create brand heat and sell through in all categories at the same time. But I'm very happy with the progress, knowing that we need to build more distribution and visibility, and that is of course different from market to market, especially on the Performance side. This attitude of going into the market with what is relevant for the local consumer is very important for us. I think we now have the right people in the markets and the right product pipeline. Now we just need to make sure that we adjust to the different needs in the markets and build even better relationships with the trade. That's what it is all about.</t>
+  </si>
+  <si>
+    <t>You have called adidas a global brand with a local mindset. What exactly does this mean and how do you balance global vs. local?</t>
+  </si>
+  <si>
+    <t>The days where you can build a global collection out of one center and sell it everywhere are over. You clearly see differences today, especially between Europe, the US, and China, but also in the other markets. Global brand with a local mindset means that we need a global vision for the brand - what categories should we be in, what technologies, what innovation, what do we want to stand for? But then we also have to ensure products and marketing are relevant in each market. We want to use the strength of being global, with so many resources in sports marketing and in innovation, but then cater for the local needs with very good local teams that have the authority to do what is relevant in their market. And if we can formalize some of this mindset in our processes and our go-to-market approach, it will make many things easier. Because right now we have to break a lot of internal rules to get there. But we definitely have the right attitude and the right people.</t>
+  </si>
+  <si>
+    <t>WE WANT TO USE THE STRENGTH OF BEING GLOBAL, BUT THEN CATER FOR LOCAL NEEDS.</t>
+  </si>
+  <si>
+    <t>During the past year, the brand has also signed many new partners as well as extended several high-profile contracts. What do all those teams and athletes
+have in common?</t>
+  </si>
+  <si>
+    <t>We have now some 5,500 partners worldwide, which shows you the enormous depth and breadth in our partnerships. Also here, we need the right combination: We have to make sure we have some global stars that give us global brand authenticity. In addition to that, we need people in the different markets that know which partners are relevant locally, which can change over time. As someone working at the headquarter, you should not believe you know what's happening in all the markets. The importance of having good and relevant individuals and teams everywhere is crucial. We have all the resources. We just need to continue to use them better and better.</t>
+  </si>
+  <si>
+    <t>You are personally meeting with many of these partners throughout the year. Was there any one interaction with an individual or team that left a particular lasting impression on you last year?</t>
+  </si>
+  <si>
+    <t>The privilege of meeting so many interesting and inspiring people makes my job kind of a dream. It's very hard to pick one, but the All Blacks visiting us on our campus, showing their team spirit and this mystique about why they perform so well and how they treat each other, was very touching and very motivating for me as a person. Going to the Paralympics, meeting many great athletes and seeing the full stadiums in Paris was also very emotional and very impressive. We also had the German Special Olympics team here on our campus, living and training here. Their positivity was definitely also a personal highlight. It is a huge privilege to meet so many unbelievably strong personalities, not only in the way they compete, but also outside of sports.</t>
+  </si>
+  <si>
+    <t>Many brand partners have been featured in the ‘You Got This’ brand campaign. What does the message mean to you and how does it influence consumers’
+perception of adidas?</t>
+  </si>
+  <si>
+    <t>Sports have for a long time been positioned in a way that the only thing is to win. And a lot of campaigns from other brands and maybe even from adidas have been about winning. It was important for us in this complicated competitive world to remove some of that pressure. When the team came up with ‘You Got This’, I fell in love with it immediately because I think it's so relevant. In the latest chapter, ‘Plus One’, we showcase athletes together with who is important for them. Having someone that motivates you, supports you, protects you, is something that we all are looking for. And I think it showcases adidas as a sports brand for people that would like to win, but also as a sports brand that understands that even if you don't win, you gain this experience in life and this is something even bigger. Extremely well executed and very
+adidas.</t>
+  </si>
+  <si>
+    <t>Behind the scenes, what were the major developments inside the company that you are most proud of?</t>
+  </si>
+  <si>
+    <t>It's obvious that we are still a people business. And we have many good people, who on their own initiative have made an enormous effort to bring adidas back again. That’s something that is very positive to see. I'm proud that we again have an organization that clearly wants to win. And I’m very happy to see that talent is not something that we are missing. We need to continue to support our people so they can be successful in both their functions and in their markets. And that's my job now to give them the support to take adidas back again to be the brand that it should be.</t>
+  </si>
+  <si>
+    <t>And what were the challenges, internal or external, that you spent the most time and energy on in the past year?</t>
+  </si>
+  <si>
+    <t>In the beginning it was to convince the retailers that we are back again. Making sure that people believe that we can win again. And then of course, the message that it's better to break some internal rules and get things done than waiting for something to change formally. That can-do attitude is probably what has made adidas a winning company again. But I'm sure it has also frustrated some people, because it creates some chaos. Of course it’s always a fine balance, because you can't have too much chaos, but many rules in our organization have been set in a world that doesn't exist anymore. We have come a long way in understanding what’s possible and what we are capable of as an organization. Now the task is to simplify the way we work.</t>
+  </si>
+  <si>
+    <t>Turning ahead, how will 2025 shape up? Anything in particular that you are looking forward to this year?</t>
+  </si>
+  <si>
+    <t>The task is of course to bring the momentum from 2024 also through 2025. I believe we have the product pipeline and marketing plans to continue to drive brand heat globally. We then need to make sure we go to market with what is relevant locally. If we do that, I am confident that we will get more distribution for our strong product assortment. Of course we don't know what's going to happen in the world from the geopolitical side. But I'm actually very positive for our industry. I think people will continue to do more sports and do more for their health. We also know that people buy running shoes to walk in because it's comfortable. That increasing importance of comfort will continue. And the lifestyle piece of the market is, of course, also a big and growing part of it. When you look at all those three things, I think globally the industry will grow much quicker than some people believe. And if we have a pipeline of product that we think is on trend and we have the attitude of being agile and more local, I cannot see why we should not be successful. As a global brand, we can reallocate resources between markets and go after growth where there is growth. That's what should make adidas the number one brand in many markets going forward.</t>
+  </si>
+  <si>
+    <t>WE HAVE THE PRODUCT PIPELINE AND MARKETING PLANS TO CONTINUE TO DRIVE BRAND HEAT GLOBALLY</t>
+  </si>
+  <si>
+    <t>When you started two years ago, improving the relationship with your retail partners was a key priority. Have you made the progress that you were envisioning back then?</t>
+  </si>
+  <si>
+    <t>Yes and no. Understandably, it took a while for them to open up to us again. And depending on where in the world you look, that opening up and giving more shelf space to us has happened at different speeds. In our home market in Europe, it was the easiest because we could make our commitment so easily visible. And of course, supplying them with products that they needed to be successful in a difficult marketplace gave them a lot of confidence. It's of course more difficult in the US, given the strong local brands. But also in
+the US, retail partners have started to believe in us and are now giving us more distribution, we just need to have some patience. I think globally, we now have a reputation among retailers that we are there for them. Our people have the service attitude and are starting to get the sales attitude back again. But of
+course there are other brands that have more distribution than us, especially in the US. Our goal must be to get more shelf space so we can prove that when we get that, we get better sell through and then build even stronger and bigger partnerships. We definitely aren’t at the end of improving relationships and increasing distribution.</t>
+  </si>
+  <si>
+    <t>You once said that there is literally no retailer around the world where you couldn’t double the business with. How far are you in achieving this?</t>
+  </si>
+  <si>
+    <t>Of course there are retailers today where we have gone from less than 10% share to more than 20%. In that case, doubling again is not realistic. So given what we have achieved over the past two years the statement is probably not true anymore everywhere. But in many, many markets, it's still the same situation. And there is no retailer around the world where we cannot significantly improve our performance, and there are many with which we can still double our share.</t>
+  </si>
+  <si>
+    <t>Halfway into your path towards being a healthy company in 2026 – what has gone better than expected? And has there been anything that has taken longer than initially anticipated?</t>
+  </si>
+  <si>
+    <t>The brand has turned positive in front of the consumer quicker than we could have hoped for. As I said many times, sometimes you need some luck and sometimes timing is everything. And then, of course, the effort and attitude of our people have been key as well. I think we are a little bit further ahead than I would have thought when we started two years ago. On the other hand, the world has become even more complicated. If you look at the conflicts and tensions around the world, these are making the world more difficult. But if we have the right attitude and are agile when there are changes, we may even turn this into a competitive advantage for us.</t>
+  </si>
+  <si>
+    <t>So you are ahead of plan at halftime. What’s your halftime speech to your team going to look like? Do you need to change your gameplan for the second half?</t>
+  </si>
+  <si>
+    <t>The most important thing is not to fall in the trap of being happy with what we have achieved and starting to defend. I think that we need to have that vision to actually be #1 in all markets. We might not achieve it everywhere, but we should have this attitude because there's no rational reason not to. Think of our 75- year history, all the franchises, the pipeline of technologies, the resources and the reach we have as a brand and as a company. We have all the good reasons to be out there in all the markets around the world – maybe with the exception of the US – with the clear ambition of being #1. That will be the halftime speech.</t>
+  </si>
+  <si>
+    <t>Anything that concerns you, from a personal or a business perspective? How do you deal with the elevated uncertainty that affects us all one way or another?</t>
+  </si>
+  <si>
+    <t>The worst thing you can do in an organization is not to talk about the issues that are difficult. I think we have created a culture to talk about all these uncertainties. We can talk about everything, the things that work well and also about things that haven’t worked. In our industry, not everything that you do will be a success. You will make mistakes, but you need to do many things and that's why you shouldn't stop doing things just because something has gone wrong. And we should not be afraid. Our people have strong personalities and the right attitude to take risks. That's why I'm saying that – if we continue to give them the right frame and the right support – then we are going to be a very, very good company.</t>
+  </si>
+  <si>
+    <t>How do you personally deal with such a volatile environment and the pressure that it brings along?</t>
+  </si>
+  <si>
+    <t>I think I have accepted that uncertainty is part of life. When I look at what we have been through just the last five years, there have been things that no one would have imagined to happen. There are always going to be things that are negative or uncertain. But in the bigger scheme of things, I am so lucky working in an industry that has great potential. I am working in a company that has a lot of potential. I've been in rough times, so I don't get worried that easily. I was much more worried when I was 25 than I am now. So it's probably age and experience that make you not feel the pressure that much.</t>
+  </si>
+  <si>
+    <t>What are you looking forward to the most this year</t>
+  </si>
+  <si>
+    <t>There is no such major sports event in 2025 like last year. And still there are so many fun things to lookforward to that I can't mention only one thing. From a business perspective, I look forward to see a continuous improvement in what we do. And I look forward to see our people feeling that they are successful and energized by that. The best thing is to see our people feeling that they're getting things done and seeing them grow because they're successful.</t>
   </si>
 </sst>
 </file>
@@ -1237,6 +1366,9 @@
   </cellStyles>
   <dxfs count="84">
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1246,6 +1378,36 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1357,6 +1519,9 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1393,91 +1558,55 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1502,144 +1631,144 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:L33" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:L33" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="A1:L33" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L33">
     <sortCondition ref="A1:A33"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="81"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="78"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="77"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="76"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="74"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="73"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="72"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="71"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L28" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L28" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A1:L28" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:L45" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:L45" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
   <autoFilter ref="A1:L45" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="CEO" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="CEO" dataDxfId="29"/>
+    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:L41" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:L41" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
   <autoFilter ref="A1:L41" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{EBE99108-B696-314E-A6F0-B2F5F90A863B}" name="ID" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{5D56DC3C-B713-2740-963B-AFE8AEFCCDC5}" name="Text" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{9B2B6519-1CB7-7F49-BB9C-204F11C40D79}" name="Text_type" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{5BA923F9-441B-A649-8784-2B77025D0C03}" name="Leadership_context" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{9F6AE6B8-C490-2940-B971-430EDC2EEE65}" name="Information_valence" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="CEO" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{EBE99108-B696-314E-A6F0-B2F5F90A863B}" name="ID" dataDxfId="81"/>
+    <tableColumn id="2" xr3:uid="{5D56DC3C-B713-2740-963B-AFE8AEFCCDC5}" name="Text" dataDxfId="80"/>
+    <tableColumn id="3" xr3:uid="{9B2B6519-1CB7-7F49-BB9C-204F11C40D79}" name="Text_type" dataDxfId="79"/>
+    <tableColumn id="4" xr3:uid="{5BA923F9-441B-A649-8784-2B77025D0C03}" name="Leadership_context" dataDxfId="78"/>
+    <tableColumn id="5" xr3:uid="{9F6AE6B8-C490-2940-B971-430EDC2EEE65}" name="Information_valence" dataDxfId="77"/>
+    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="76"/>
+    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="74"/>
+    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="73"/>
+    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="72"/>
+    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="CEO" dataDxfId="71"/>
+    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:L2" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:L42" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L42" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="35"/>
-    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="32"/>
-    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="CEO" dataDxfId="0"/>
-    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="CEO" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{98E4B810-202A-7E4C-B2C6-35D4404CA885}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{98E4B810-202A-7E4C-B2C6-35D4404CA885}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{1EDFD034-5D27-3548-B9B9-99583075B81D}" name="ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{EFC7714F-3B4F-2845-B40A-79112F4B2DEE}" name="Text" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{5D67890B-5706-D740-BEC3-312FE72ADCFA}" name="Text_type" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{E9A847B5-7204-E54B-A14E-1A948434EC56}" name="Leadership_context" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{BD19C5B7-6C1E-9E43-82A8-7B117D5E0919}" name="Information_valence" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{066F6E4C-E842-4E43-A4B5-EF5133865DBD}" name="Communication_type" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{3D9145EE-B2AE-EA43-B6FF-544CF963E633}" name="Company" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{645C94BF-8E35-754B-B12E-328B4734CE50}" name="Country" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{8EF94B9F-4FD1-7A4E-97D7-9DA2D47E3DD5}" name="Year" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{CFE7CD80-3AA1-9041-8B91-270DDA32612B}" name="Covid" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{77CD3889-4929-7348-B4F3-E407474AFD4D}" name="CEO" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{276FB6D5-C797-B046-B256-4A051057EA9E}" name="Comment" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{1EDFD034-5D27-3548-B9B9-99583075B81D}" name="ID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{EFC7714F-3B4F-2845-B40A-79112F4B2DEE}" name="Text" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{5D67890B-5706-D740-BEC3-312FE72ADCFA}" name="Text_type" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{E9A847B5-7204-E54B-A14E-1A948434EC56}" name="Leadership_context" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{BD19C5B7-6C1E-9E43-82A8-7B117D5E0919}" name="Information_valence" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{066F6E4C-E842-4E43-A4B5-EF5133865DBD}" name="Communication_type" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{3D9145EE-B2AE-EA43-B6FF-544CF963E633}" name="Company" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{645C94BF-8E35-754B-B12E-328B4734CE50}" name="Country" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{8EF94B9F-4FD1-7A4E-97D7-9DA2D47E3DD5}" name="Year" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{CFE7CD80-3AA1-9041-8B91-270DDA32612B}" name="Covid" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{77CD3889-4929-7348-B4F3-E407474AFD4D}" name="CEO" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{276FB6D5-C797-B046-B256-4A051057EA9E}" name="Comment" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6655,7 +6784,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F82F056-8FF7-6744-96CE-2950DDB4AA9C}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -6707,11 +6836,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>187</v>
       </c>
@@ -6728,6 +6862,1046 @@
         <v>128</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="B3" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="B4" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2026</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B5" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2027</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="B6" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2028</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="B7" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2029</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="255" x14ac:dyDescent="0.2">
+      <c r="B8" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2030</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="B9" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2031</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+      <c r="B10" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2032</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="B11" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2033</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="204" x14ac:dyDescent="0.2">
+      <c r="B12" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2034</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="B13" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2035</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="B14" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2036</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="B15" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2037</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="B16" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2038</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="B17" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2039</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="B18" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2040</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="B19" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2041</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="B20" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2042</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="221" x14ac:dyDescent="0.2">
+      <c r="B21" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2043</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B22" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2044</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="B23" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="1">
+        <v>2045</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B24" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="1">
+        <v>2046</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="B25" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2047</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B26" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="1">
+        <v>2048</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="289" x14ac:dyDescent="0.2">
+      <c r="B27" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2049</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B28" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2050</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="B29" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2051</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="289" x14ac:dyDescent="0.2">
+      <c r="B30" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2052</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B31" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="1">
+        <v>2053</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="119" x14ac:dyDescent="0.2">
+      <c r="B32" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2054</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="B33" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2055</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="B34" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="1">
+        <v>2056</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="B35" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="1">
+        <v>2057</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="B36" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2058</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="B37" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2059</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="B38" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="1">
+        <v>2060</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B39" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="1">
+        <v>2061</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="B40" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="1">
+        <v>2062</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B41" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="1">
+        <v>2063</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="B42" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="1">
+        <v>2064</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>186</v>
       </c>
     </row>

--- a/data/input/adidas.xlsx
+++ b/data/input/adidas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901BE30B-3B4C-7646-A575-33EE12AF09E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D81409E-5DA8-7240-B127-05BA539FE123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10060" yWindow="600" windowWidth="20980" windowHeight="17400" activeTab="4" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="10060" yWindow="600" windowWidth="20980" windowHeight="17400" activeTab="5" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="439">
   <si>
     <t>ID</t>
   </si>
@@ -1267,6 +1267,126 @@
   </si>
   <si>
     <t>There is no such major sports event in 2025 like last year. And still there are so many fun things to lookforward to that I can't mention only one thing. From a business perspective, I look forward to see a continuous improvement in what we do. And I look forward to see our people feeling that they are successful and energized by that. The best thing is to see our people feeling that they're getting things done and seeing them grow because they're successful.</t>
+  </si>
+  <si>
+    <t>DEU24A01-00</t>
+  </si>
+  <si>
+    <t>DEU24A01-01</t>
+  </si>
+  <si>
+    <t>DEU24A02-00</t>
+  </si>
+  <si>
+    <t>DEU24A02-01</t>
+  </si>
+  <si>
+    <t>DEU24A03-00</t>
+  </si>
+  <si>
+    <t>DEU24A03-01</t>
+  </si>
+  <si>
+    <t>DEU24A04-00</t>
+  </si>
+  <si>
+    <t>DEU24A04-01</t>
+  </si>
+  <si>
+    <t>DEU24A05-00</t>
+  </si>
+  <si>
+    <t>DEU24A05-01</t>
+  </si>
+  <si>
+    <t>DEU24A06-00</t>
+  </si>
+  <si>
+    <t>DEU24A06-01</t>
+  </si>
+  <si>
+    <t>DEU24A07-00</t>
+  </si>
+  <si>
+    <t>DEU24A08-00</t>
+  </si>
+  <si>
+    <t>DEU24A08-01</t>
+  </si>
+  <si>
+    <t>DEU24A09-00</t>
+  </si>
+  <si>
+    <t>DEU24A09-01</t>
+  </si>
+  <si>
+    <t>DEU24A10-00</t>
+  </si>
+  <si>
+    <t>DEU24A10-01</t>
+  </si>
+  <si>
+    <t>DEU24A11-00</t>
+  </si>
+  <si>
+    <t>DEU24A11-01</t>
+  </si>
+  <si>
+    <t>DEU24A12-00</t>
+  </si>
+  <si>
+    <t>DEU24A12-01</t>
+  </si>
+  <si>
+    <t>DEU24A13-00</t>
+  </si>
+  <si>
+    <t>DEU24A13-01</t>
+  </si>
+  <si>
+    <t>DEU24A14-00</t>
+  </si>
+  <si>
+    <t>DEU24A15-00</t>
+  </si>
+  <si>
+    <t>DEU24A15-01</t>
+  </si>
+  <si>
+    <t>DEU24A16-00</t>
+  </si>
+  <si>
+    <t>DEU24A16-01</t>
+  </si>
+  <si>
+    <t>DEU24A17-00</t>
+  </si>
+  <si>
+    <t>DEU24A17-01</t>
+  </si>
+  <si>
+    <t>DEU24A18-00</t>
+  </si>
+  <si>
+    <t>DEU24A18-01</t>
+  </si>
+  <si>
+    <t>DEU24A19-00</t>
+  </si>
+  <si>
+    <t>DEU24A19-01</t>
+  </si>
+  <si>
+    <t>DEU24A20-00</t>
+  </si>
+  <si>
+    <t>DEU24A20-01</t>
+  </si>
+  <si>
+    <t>DEU24A21-00</t>
+  </si>
+  <si>
+    <t>DEU24A21-01</t>
   </si>
 </sst>
 </file>
@@ -6866,6 +6986,9 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>399</v>
+      </c>
       <c r="B3" s="4" t="s">
         <v>359</v>
       </c>
@@ -6892,6 +7015,9 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="B4" s="4" t="s">
         <v>360</v>
       </c>
@@ -6918,6 +7044,9 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>401</v>
+      </c>
       <c r="B5" s="4" t="s">
         <v>361</v>
       </c>
@@ -6944,6 +7073,9 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>402</v>
+      </c>
       <c r="B6" s="4" t="s">
         <v>362</v>
       </c>
@@ -6970,6 +7102,9 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>403</v>
+      </c>
       <c r="B7" s="4" t="s">
         <v>363</v>
       </c>
@@ -6996,6 +7131,9 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="255" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="B8" s="4" t="s">
         <v>364</v>
       </c>
@@ -7022,6 +7160,9 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="B9" s="4" t="s">
         <v>365</v>
       </c>
@@ -7048,6 +7189,9 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>406</v>
+      </c>
       <c r="B10" s="4" t="s">
         <v>366</v>
       </c>
@@ -7074,6 +7218,9 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>407</v>
+      </c>
       <c r="B11" s="4" t="s">
         <v>367</v>
       </c>
@@ -7100,6 +7247,9 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="204" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>408</v>
+      </c>
       <c r="B12" s="4" t="s">
         <v>368</v>
       </c>
@@ -7126,6 +7276,9 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>409</v>
+      </c>
       <c r="B13" s="4" t="s">
         <v>369</v>
       </c>
@@ -7152,6 +7305,9 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>410</v>
+      </c>
       <c r="B14" s="4" t="s">
         <v>370</v>
       </c>
@@ -7178,6 +7334,9 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>411</v>
+      </c>
       <c r="B15" s="4" t="s">
         <v>371</v>
       </c>
@@ -7204,6 +7363,9 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>412</v>
+      </c>
       <c r="B16" s="4" t="s">
         <v>372</v>
       </c>
@@ -7229,7 +7391,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="153" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>413</v>
+      </c>
       <c r="B17" s="4" t="s">
         <v>373</v>
       </c>
@@ -7255,7 +7420,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>414</v>
+      </c>
       <c r="B18" s="4" t="s">
         <v>374</v>
       </c>
@@ -7281,7 +7449,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>415</v>
+      </c>
       <c r="B19" s="4" t="s">
         <v>375</v>
       </c>
@@ -7307,7 +7478,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="68" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>416</v>
+      </c>
       <c r="B20" s="4" t="s">
         <v>376</v>
       </c>
@@ -7333,7 +7507,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="221" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>417</v>
+      </c>
       <c r="B21" s="4" t="s">
         <v>377</v>
       </c>
@@ -7359,7 +7536,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>418</v>
+      </c>
       <c r="B22" s="4" t="s">
         <v>378</v>
       </c>
@@ -7385,7 +7565,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="136" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>419</v>
+      </c>
       <c r="B23" s="4" t="s">
         <v>379</v>
       </c>
@@ -7411,7 +7594,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>420</v>
+      </c>
       <c r="B24" s="4" t="s">
         <v>380</v>
       </c>
@@ -7437,7 +7623,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>421</v>
+      </c>
       <c r="B25" s="4" t="s">
         <v>381</v>
       </c>
@@ -7463,7 +7652,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>422</v>
+      </c>
       <c r="B26" s="4" t="s">
         <v>382</v>
       </c>
@@ -7489,7 +7681,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="289" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="289" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>423</v>
+      </c>
       <c r="B27" s="4" t="s">
         <v>383</v>
       </c>
@@ -7515,7 +7710,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>424</v>
+      </c>
       <c r="B28" s="4" t="s">
         <v>384</v>
       </c>
@@ -7541,7 +7739,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>425</v>
+      </c>
       <c r="B29" s="4" t="s">
         <v>385</v>
       </c>
@@ -7567,7 +7768,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="289" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="289" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>426</v>
+      </c>
       <c r="B30" s="4" t="s">
         <v>386</v>
       </c>
@@ -7593,7 +7797,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>427</v>
+      </c>
       <c r="B31" s="4" t="s">
         <v>387</v>
       </c>
@@ -7619,7 +7826,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="119" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>428</v>
+      </c>
       <c r="B32" s="4" t="s">
         <v>388</v>
       </c>
@@ -7645,7 +7855,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="B33" s="4" t="s">
         <v>389</v>
       </c>
@@ -7671,7 +7884,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="34" spans="2:11" ht="153" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>430</v>
+      </c>
       <c r="B34" s="4" t="s">
         <v>390</v>
       </c>
@@ -7697,7 +7913,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>431</v>
+      </c>
       <c r="B35" s="4" t="s">
         <v>391</v>
       </c>
@@ -7723,7 +7942,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="2:11" ht="153" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>432</v>
+      </c>
       <c r="B36" s="4" t="s">
         <v>392</v>
       </c>
@@ -7749,7 +7971,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>433</v>
+      </c>
       <c r="B37" s="4" t="s">
         <v>393</v>
       </c>
@@ -7775,7 +8000,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>434</v>
+      </c>
       <c r="B38" s="4" t="s">
         <v>394</v>
       </c>
@@ -7801,7 +8029,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>435</v>
+      </c>
       <c r="B39" s="4" t="s">
         <v>395</v>
       </c>
@@ -7827,7 +8058,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="40" spans="2:11" ht="136" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>436</v>
+      </c>
       <c r="B40" s="4" t="s">
         <v>396</v>
       </c>
@@ -7853,7 +8087,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="41" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>437</v>
+      </c>
       <c r="B41" s="4" t="s">
         <v>397</v>
       </c>
@@ -7879,7 +8116,10 @@
         <v>186</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>438</v>
+      </c>
       <c r="B42" s="4" t="s">
         <v>398</v>
       </c>
@@ -7906,6 +8146,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/data/input/adidas.xlsx
+++ b/data/input/adidas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D81409E-5DA8-7240-B127-05BA539FE123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD225898-7EF0-6648-9B5C-FA3989C88F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10060" yWindow="600" windowWidth="20980" windowHeight="17400" activeTab="5" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="1460" yWindow="600" windowWidth="27340" windowHeight="17400" activeTab="5" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1938" uniqueCount="513">
   <si>
     <t>ID</t>
   </si>
@@ -1387,6 +1387,228 @@
   </si>
   <si>
     <t>DEU24A21-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE GLOBAL POTENTIAL FOR ADIDAS IS ALMOST UNLIMITED </t>
+  </si>
+  <si>
+    <t>Bjørn, 2025 was quite an eventful year, to say the least. Before we move to the business side, what was your most memorable sports moment last year?</t>
+  </si>
+  <si>
+    <t>Given the huge amount of great sports events on small or larger stages throughout the year, it wouldn’t be fair to call out just one. When people come together to do sports, this is always fantastic. I think it's fair to say that, for our brand, there were many events where we showed up both with our athletes and our products that were great. It was definitely a great sports year for our company.</t>
+  </si>
+  <si>
+    <t>Turning to the business, how would you summarize 2025?</t>
+  </si>
+  <si>
+    <t>I am very happy and proud of what our people have achieved. I am very happy when you look at our progress over the last three years, it's gone faster than we expected in many areas. In early 2023, we laid out what we thought we had to do over the next four years. 2025 was the third year, and we already achieved many of the goals we set ourselves. We first had growth in the Lifestyle area, especially driven by footwear, through which we created a lot of brand heat globally. We have gotten credibility in Performance again, also in categories where we thought that the road was longer. The development in Running – especially on the high end – has been great. In Football, we've taken back market leadership, and in Basketball, we have innovation and product that I think people didn't believe we can do that quickly. Our visibility in sports – both in big global sports and smaller local sports – has grown enormously. The fact that we have grown double digits for two consecutive years now and achieved double-digit growth all over the world in 2025 shows you the enormous power of this brand.</t>
+  </si>
+  <si>
+    <t>What’s driving this very broad success in your opinion?</t>
+  </si>
+  <si>
+    <t>First of all, credit to the fantastic brand and company we work for. The global potential for adidas is almost unlimited because we have 76 years of history, and we have so many stories to tell. While the brand has been culturally relevant in all our markets, we are now also back as a sports brand all over the world. The combination of the awareness, the history, the cultural relevance, and the performance credibility is quite unique. And becoming a global brand with a local mindset has been a huge enabler across all of this. The brand is strong, and we have very good and talented people that are utilizing the strength of the brand in the local markets. It’s now up to us how we leverage this in the right way, both in the short term and the long term.</t>
+  </si>
+  <si>
+    <t>Can you help us understand what ‘global brand with a local mindset’ means?</t>
+  </si>
+  <si>
+    <t>In a global world where information flows very quickly, you could believe that the choice of consumers is the same everywhere. But it clearly isn’t. We see that different markets have different developments when it comes to taste. The markets are more conscious of their own culture, meaning that the choice of the product, the usage of the product, the meaning of what sport is, are different. I can't force the consumer in China to buy the same product as in Norway. And we all know the difference between Europe and America when it comes to the sports that are relevant. We need to please the consumer where he or she is, all within the frame of the brand. We need to have a global frame that defines what adidas is, and how we should utilize the brand and have a vision for it. But then how we execute that in the different regions has to be different to be successful. We should still be a sports brand at our core, and we should be utilizing the strength of sports into local culture. And then, of course, there are lifestyle, fashion, and comfort elements to take into account.</t>
+  </si>
+  <si>
+    <t>If we look at the overall product offering last year across global and local, what are the products that you want to call out?</t>
+  </si>
+  <si>
+    <t>With the Samba, the Gazelle, and the Spezial, we really brought the brand back to the young female consumer. This isn’t something that happens quickly, it’s built over time, and it's very, very strong still. Then, I would call out how we extended the popularity of the Three Stripes from footwear to apparel. When you look at the sequence of that, it actually happened exactly that way. Running is another call-out, because it was the most difficult category for us to establish ourselves in at the top. Our teams have done a tremendous job, creating what – in my opinion – are the best running shoes. Once you have credibility at the top, winning marathons and setting records, it's easier to be commercially successful in everyday running and comfort running products. And that is, of course, the plan. I could also call out the Predator in Football, the Adizero Dropset in Training, or so many other examples of great products in our Performance categories. I can't point to one product or one segment. I am extremely proud to see what the teams have done. How creative and innovative we have been across the teams and categories. How the consumers have reacted to it the last three years showcases how good this brand is and the people behind it.</t>
+  </si>
+  <si>
+    <t>I AM VERY HAPPY AND PROUD OF WHAT OUR PEOPLE HAVE ACHIEVED</t>
+  </si>
+  <si>
+    <t>One of the things that you haven’t mentioned is the pet collection that has caught quite some attention globally after being launched in China. Are you trying to expand into new territories here?</t>
+  </si>
+  <si>
+    <t>I had nothing to do with that because that idea, of course, came from our China team. They used the popularity of adidas to extend the range. I would say it's a local marketing tool that has suddenly become a business. Again, it shows the creativity of the team. It shows that our teams on the ground know their consumers and what matters to them most. And it shows the impact of good ideas.</t>
+  </si>
+  <si>
+    <t>You mentioned in the past that it will take time for the improved and expanded product range to become fully visible in the trade. Where are you with that?</t>
+  </si>
+  <si>
+    <t>It’s different from market to market. It's obvious with the success of lifestyle footwear that many retailers wanted it very quickly and adopted it. But there are categories where we still don’t have the space we believe we should. We do think we are competitive, and there are many markets where we should be able to increase our space in the store and on the shelf. But as always, the retailers decide on who they allocate space to. If they do that rationally, they will allocate space to those who give them the highest contribution per square meter, and we think we can do that. We made huge progress in the last three years, but if you look at running for example, there are places around the world where we still have very little distribution, which again shows the huge opportunity we have in our hands.</t>
+  </si>
+  <si>
+    <t>How did listening to the retail partners and working closer with them change the assortment and how the brand shows up in the stores?</t>
+  </si>
+  <si>
+    <t>For me, listening to our retail partners is crucial. If you sit in headquarters and decide what should be in all the stores around the world, it’s simply not going to work. We have an open dialogue with consumers, with athletes, and with our retailers across the different markets. Our market teams have been very active in engaging with our retailers, and we have opened all our creation centers to work with them. We’ve seen improvements in that process, but it can always be better. We are getting very positive feedback from the retailers on the way we work, and how the flexibility and the speed of our creation teams have improved. We are on a very, very good way of giving this fantastic adidas brand the right platform to be market leader in many markets.</t>
+  </si>
+  <si>
+    <t>What has also grown is the roster of partners around the world, from global partners like Liverpool FC to more local ones like Penn State or Gilas Pilipinas, the national basketball team of the Philippines. What role do these partners play for adidas?</t>
+  </si>
+  <si>
+    <t>If you don’t showcase the brand with relevant partners, it will disappear over time. Our philosophy is that adidas should be visible and relevant. There are certain sports and partners that are very global, like football and Liverpool, and there are partners that are very local. Authentic partnerships that give us organic visibility are more important than paid media campaigns. That's why we are investing a lot in partnerships, both globally and locally – not only in sports, but in whatever is culturally relevant for the consumer in the different markets. It can be in fashion, it can be in music, and it can be in other areas that the consumer thinks is relevant.</t>
+  </si>
+  <si>
+    <t>2025 saw the return of adidas into motorsports. How did that go and what's going to happen next?</t>
+  </si>
+  <si>
+    <t>F1 is growing globally when it gets to viewership. And the viewership is getting younger and younger and they’re both female and male. We made the decision to team up with the Mercedes AMG Petronas F1 team very quickly, and our team did an unbelievable job launching it. I think we went from handshake to having products in the markets in under ten months. We now have one year behind us commercially, and it's been more successful than anybody expected. We have also added Audi Revolut and have just launched their first collection, so that means we will have two teams for the upcoming season, and the reaction has been great. With fans buying both merchandise and lifestyle products inspired by F1, there are big opportunities to expand our business in the future.</t>
+  </si>
+  <si>
+    <t>You made some organizational changes in 2025 in order to move closer to markets and consumers. Why were those changes required?</t>
+  </si>
+  <si>
+    <t>Given the uncertainty when it comes to the geopolitical situation and the unstable environment we operate in, getting closer to the consumer and making sure that we work with the markets has become even more important. So, we have strengthened our creative resources in the different regions and given the markets more freedom in developing products, signing partners, and doing activations. I think the biggest success story that we can show here is China. Firstly, our Chinese teams have a lot of creative people. Secondly, they have factories next door, so they can design, develop, and source product on a shorter lead time. Also, given the mono-branded retail environment, where we have around 8,000 adidas branded stores – even if they are operated by wholesale partners – that gives us a different value chain to work with. Empowering our markets to use their local setup to win the local consumer is a key reason for our current success. And our global teams, of course, support it. But this means we also had to change our structures and processes to reflect the reality of how we work, leading to changes and role reductions at our headquarters in Herzogenaurach. It is very important for me to ensure that all changes are carried out with the utmost respect and care for all employees. But there's no choice. In order to be successful long-term, we need to be agile and on our toes to be able to react as quickly as possible to changes. And this means we have to put decision-making as close as we can to where these decisions need to be made.</t>
+  </si>
+  <si>
+    <t>You’ve been in this industry for many years. How has the competitive landscape changed and how attractive is the sporting goods industry today?</t>
+  </si>
+  <si>
+    <t>It depends on what time period you look at. If you go back to the beginning of my time in the industry, European brands were dominating. Then we had the American brands coming up, that was the first big change. Now we are seeing specialist brands coming up, focusing on just one or two categories, and local players trying to go global. So the amount of competitors has increased. But the awareness and the positiveness towards adidas has also increased. We are in a very, very attractive industry, because sports in all its dimensions will continue to grow. I also think on the lifestyle side that casualization will never stop, and I strongly believe that more and more people will be wearing sports shoes across all age groups because they’re the most comfortable choice. All of this is of course very good for us, because we are in many markets, we are in multiple categories, we have 76 years of history we can build on, and we have all the resources to continue our success. So, I see a very positive industry development for us for the future. Moving closer to the consumer locally is key to enabling our ability to successfully compete with all other brands.</t>
+  </si>
+  <si>
+    <t>WHEN PEOPLE COME TOGETHER TO DO SPORTS, THIS IS ALWAYS FANTASTIC</t>
+  </si>
+  <si>
+    <t>adidas’ market share is significantly higher than it was three years ago. How much more potential is there to increase the market share?</t>
+  </si>
+  <si>
+    <t>The potential is different from market to market, depending on what the starting point is. But if you look at our biggest competitor and its size compared to ours, then that should be answer enough. I can’t see any market where we cannot gain substantial share over time. Given our relatively low market share in the US, we have the ambition to double our business there. I just think we need to be more American and that’s what we’re trying to do. The American team needs to invest in what is relevant for America. Outside of the US we have the ambition of being market leader in all markets. That doesn’t mean that we will be it, but we should have the ambition. And we need to understand what we need to do in every market to achieve this ambition.</t>
+  </si>
+  <si>
+    <t>The US is a good segue to the next question. The FIFA World Cup 2026 will be a huge event and a great platform. What are your expectations for the brand and the business?</t>
+  </si>
+  <si>
+    <t>Other than the World Cup, what does success for adidas look like this year? What are your priorities for 2026?</t>
+  </si>
+  <si>
+    <t>The World Cup is always a great event. It is the biggest sports event when it comes to viewership all over the world. Football is the DNA of our brand, and being market leader, it is of huge importance to adidas. And it's a great platform to take football as a sport and highlight the cultural relevance of it. That's why the collection this year is so much wider than it's been before. We clearly see that there is a football interest in fashion and lifestyle that we have never seen before. We will focus on connecting to the US consumer, the Mexican consumer, and the Canadian consumer. So far, the reaction to what we have showcased, and our first product launches has been great. Aside from business, I really believe that the World Cup can be a game changer when it comes to where the world is going, given the positive feelings that these events bring. I strongly believe that sports is one of the few things that brings us all together. Let’s hope that the World Cup will strengthen some of the conversations that are going on to create peace again.</t>
+  </si>
+  <si>
+    <t>2026 is a year where we will continue the momentum that we have. There is no doubt that the potential of this brand in this attractive market is to continue to grow a couple of billions every year. To do that on a consistent basis, we need to keep developing our people and keep working on the way we execute. Not only in front of the consumer, where we are very successful already. But also in the way we work. Just like athletes, we will continue to work hard on us, we will continue to adapt our processes to the changing environment so that we become an even better company and keep building an even stronger platform for the future.</t>
+  </si>
+  <si>
+    <t>Talking about the future, what are your plans and goals for adidas in the coming years?</t>
+  </si>
+  <si>
+    <t>I believe the next couple of years should show that adidas can take market leadership in a lot more markets. I think that we will continue to outgrow the industry and take more market share, utilizing the strength of our brand, our resources, our authenticity, our innovation, and our creativity. And to do that, we need to be dedicated to our consumers and attract, develop, and keep the best people. Because I think in this world where we talk a lot about AI and the tools that can make us better, we are still a people business. We should never forget that the athlete is a person, the consumer is a person, and the employee is a person. adidas is a great company to work with and to work for, and we are obsessed about fulfilling the needs of consumers and athletes.</t>
+  </si>
+  <si>
+    <t>Last question: What are your personal goals for 2026 and beyond?</t>
+  </si>
+  <si>
+    <t>I enjoy what I do, also doing a lot of sports. I have a lot of energy for this great job, a lot of passion for this fantastic brand, and I feel extremely privileged in what I do. So, my goal really is just to continue the great journey we are on, give this brand what it deserves, and get this company to where it belongs.</t>
+  </si>
+  <si>
+    <t>DEU25A01-00</t>
+  </si>
+  <si>
+    <t>DEU25A01-01</t>
+  </si>
+  <si>
+    <t>DEU25A02-00</t>
+  </si>
+  <si>
+    <t>DEU25A02-01</t>
+  </si>
+  <si>
+    <t>DEU25A03-00</t>
+  </si>
+  <si>
+    <t>DEU25A03-01</t>
+  </si>
+  <si>
+    <t>DEU25A04-00</t>
+  </si>
+  <si>
+    <t>DEU25A04-01</t>
+  </si>
+  <si>
+    <t>DEU25A05-00</t>
+  </si>
+  <si>
+    <t>DEU25A05-01</t>
+  </si>
+  <si>
+    <t>DEU25A06-00</t>
+  </si>
+  <si>
+    <t>DEU25A07-00</t>
+  </si>
+  <si>
+    <t>DEU25A07-01</t>
+  </si>
+  <si>
+    <t>DEU25A08-00</t>
+  </si>
+  <si>
+    <t>DEU25A08-01</t>
+  </si>
+  <si>
+    <t>DEU25A09-00</t>
+  </si>
+  <si>
+    <t>DEU25A09-01</t>
+  </si>
+  <si>
+    <t>DEU25A10-00</t>
+  </si>
+  <si>
+    <t>DEU25A10-01</t>
+  </si>
+  <si>
+    <t>DEU25A11-00</t>
+  </si>
+  <si>
+    <t>DEU25A11-01</t>
+  </si>
+  <si>
+    <t>DEU25A12-00</t>
+  </si>
+  <si>
+    <t>DEU25A12-01</t>
+  </si>
+  <si>
+    <t>DEU25A13-00</t>
+  </si>
+  <si>
+    <t>DEU25A13-01</t>
+  </si>
+  <si>
+    <t>DEU25A14-00</t>
+  </si>
+  <si>
+    <t>DEU25A15-00</t>
+  </si>
+  <si>
+    <t>DEU25A15-01</t>
+  </si>
+  <si>
+    <t>DEU25A16-00</t>
+  </si>
+  <si>
+    <t>DEU25A16-01</t>
+  </si>
+  <si>
+    <t>DEU25A17-00</t>
+  </si>
+  <si>
+    <t>DEU25A17-01</t>
+  </si>
+  <si>
+    <t>DEU25A18-00</t>
+  </si>
+  <si>
+    <t>DEU25A18-01</t>
+  </si>
+  <si>
+    <t>DEU25A19-00</t>
+  </si>
+  <si>
+    <t>DEU25A19-01</t>
+  </si>
+  <si>
+    <t>quore</t>
   </si>
 </sst>
 </file>
@@ -1684,7 +1906,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1726,7 +1948,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1751,144 +1973,144 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:L33" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:L33" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
   <autoFilter ref="A1:L33" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L33">
     <sortCondition ref="A1:A33"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="81"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="80"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="79"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="78"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="77"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="76"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="74"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="73"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="72"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="71"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L28" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L28" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="A1:L28" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:L45" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:L45" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A1:L45" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="CEO" dataDxfId="29"/>
-    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="CEO" dataDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:L41" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:L41" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
   <autoFilter ref="A1:L41" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{EBE99108-B696-314E-A6F0-B2F5F90A863B}" name="ID" dataDxfId="81"/>
-    <tableColumn id="2" xr3:uid="{5D56DC3C-B713-2740-963B-AFE8AEFCCDC5}" name="Text" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{9B2B6519-1CB7-7F49-BB9C-204F11C40D79}" name="Text_type" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{5BA923F9-441B-A649-8784-2B77025D0C03}" name="Leadership_context" dataDxfId="78"/>
-    <tableColumn id="5" xr3:uid="{9F6AE6B8-C490-2940-B971-430EDC2EEE65}" name="Information_valence" dataDxfId="77"/>
-    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="76"/>
-    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="74"/>
-    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="73"/>
-    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="72"/>
-    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="CEO" dataDxfId="71"/>
-    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{EBE99108-B696-314E-A6F0-B2F5F90A863B}" name="ID" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{5D56DC3C-B713-2740-963B-AFE8AEFCCDC5}" name="Text" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{9B2B6519-1CB7-7F49-BB9C-204F11C40D79}" name="Text_type" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{5BA923F9-441B-A649-8784-2B77025D0C03}" name="Leadership_context" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{9F6AE6B8-C490-2940-B971-430EDC2EEE65}" name="Information_valence" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="CEO" dataDxfId="29"/>
+    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:L42" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:L42" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:L42" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="CEO" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="CEO" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{98E4B810-202A-7E4C-B2C6-35D4404CA885}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{98E4B810-202A-7E4C-B2C6-35D4404CA885}" name="Tableau134567" displayName="Tableau134567" ref="A1:L38" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L38" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{1EDFD034-5D27-3548-B9B9-99583075B81D}" name="ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{EFC7714F-3B4F-2845-B40A-79112F4B2DEE}" name="Text" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{5D67890B-5706-D740-BEC3-312FE72ADCFA}" name="Text_type" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{E9A847B5-7204-E54B-A14E-1A948434EC56}" name="Leadership_context" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{BD19C5B7-6C1E-9E43-82A8-7B117D5E0919}" name="Information_valence" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{066F6E4C-E842-4E43-A4B5-EF5133865DBD}" name="Communication_type" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{3D9145EE-B2AE-EA43-B6FF-544CF963E633}" name="Company" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{645C94BF-8E35-754B-B12E-328B4734CE50}" name="Country" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{8EF94B9F-4FD1-7A4E-97D7-9DA2D47E3DD5}" name="Year" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{CFE7CD80-3AA1-9041-8B91-270DDA32612B}" name="Covid" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{77CD3889-4929-7348-B4F3-E407474AFD4D}" name="CEO" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{276FB6D5-C797-B046-B256-4A051057EA9E}" name="Comment" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{1EDFD034-5D27-3548-B9B9-99583075B81D}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{EFC7714F-3B4F-2845-B40A-79112F4B2DEE}" name="Text" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{5D67890B-5706-D740-BEC3-312FE72ADCFA}" name="Text_type" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{E9A847B5-7204-E54B-A14E-1A948434EC56}" name="Leadership_context" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{BD19C5B7-6C1E-9E43-82A8-7B117D5E0919}" name="Information_valence" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{066F6E4C-E842-4E43-A4B5-EF5133865DBD}" name="Communication_type" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{3D9145EE-B2AE-EA43-B6FF-544CF963E633}" name="Company" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{645C94BF-8E35-754B-B12E-328B4734CE50}" name="Country" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{8EF94B9F-4FD1-7A4E-97D7-9DA2D47E3DD5}" name="Year" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{CFE7CD80-3AA1-9041-8B91-270DDA32612B}" name="Covid" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{77CD3889-4929-7348-B4F3-E407474AFD4D}" name="CEO" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{276FB6D5-C797-B046-B256-4A051057EA9E}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7005,7 +7227,7 @@
         <v>18</v>
       </c>
       <c r="I3" s="1">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>128</v>
@@ -7034,7 +7256,7 @@
         <v>18</v>
       </c>
       <c r="I4" s="1">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>128</v>
@@ -7063,7 +7285,7 @@
         <v>18</v>
       </c>
       <c r="I5" s="1">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>128</v>
@@ -7092,7 +7314,7 @@
         <v>18</v>
       </c>
       <c r="I6" s="1">
-        <v>2028</v>
+        <v>2024</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>128</v>
@@ -7121,7 +7343,7 @@
         <v>18</v>
       </c>
       <c r="I7" s="1">
-        <v>2029</v>
+        <v>2024</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>128</v>
@@ -7150,7 +7372,7 @@
         <v>18</v>
       </c>
       <c r="I8" s="1">
-        <v>2030</v>
+        <v>2024</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>128</v>
@@ -7179,7 +7401,7 @@
         <v>18</v>
       </c>
       <c r="I9" s="1">
-        <v>2031</v>
+        <v>2024</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>128</v>
@@ -7208,7 +7430,7 @@
         <v>18</v>
       </c>
       <c r="I10" s="1">
-        <v>2032</v>
+        <v>2024</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>128</v>
@@ -7237,7 +7459,7 @@
         <v>18</v>
       </c>
       <c r="I11" s="1">
-        <v>2033</v>
+        <v>2024</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>128</v>
@@ -7266,7 +7488,7 @@
         <v>18</v>
       </c>
       <c r="I12" s="1">
-        <v>2034</v>
+        <v>2024</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>128</v>
@@ -7295,7 +7517,7 @@
         <v>18</v>
       </c>
       <c r="I13" s="1">
-        <v>2035</v>
+        <v>2024</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>128</v>
@@ -7324,7 +7546,7 @@
         <v>18</v>
       </c>
       <c r="I14" s="1">
-        <v>2036</v>
+        <v>2024</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>128</v>
@@ -7353,7 +7575,7 @@
         <v>18</v>
       </c>
       <c r="I15" s="1">
-        <v>2037</v>
+        <v>2024</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>128</v>
@@ -7382,7 +7604,7 @@
         <v>18</v>
       </c>
       <c r="I16" s="1">
-        <v>2038</v>
+        <v>2024</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>128</v>
@@ -7411,7 +7633,7 @@
         <v>18</v>
       </c>
       <c r="I17" s="1">
-        <v>2039</v>
+        <v>2024</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>128</v>
@@ -7440,7 +7662,7 @@
         <v>18</v>
       </c>
       <c r="I18" s="1">
-        <v>2040</v>
+        <v>2024</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>128</v>
@@ -7469,7 +7691,7 @@
         <v>18</v>
       </c>
       <c r="I19" s="1">
-        <v>2041</v>
+        <v>2024</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>128</v>
@@ -7498,7 +7720,7 @@
         <v>18</v>
       </c>
       <c r="I20" s="1">
-        <v>2042</v>
+        <v>2024</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>128</v>
@@ -7527,7 +7749,7 @@
         <v>18</v>
       </c>
       <c r="I21" s="1">
-        <v>2043</v>
+        <v>2024</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>128</v>
@@ -7556,7 +7778,7 @@
         <v>18</v>
       </c>
       <c r="I22" s="1">
-        <v>2044</v>
+        <v>2024</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>128</v>
@@ -7585,7 +7807,7 @@
         <v>18</v>
       </c>
       <c r="I23" s="1">
-        <v>2045</v>
+        <v>2024</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>128</v>
@@ -7614,7 +7836,7 @@
         <v>18</v>
       </c>
       <c r="I24" s="1">
-        <v>2046</v>
+        <v>2024</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>128</v>
@@ -7643,7 +7865,7 @@
         <v>18</v>
       </c>
       <c r="I25" s="1">
-        <v>2047</v>
+        <v>2024</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>128</v>
@@ -7672,7 +7894,7 @@
         <v>18</v>
       </c>
       <c r="I26" s="1">
-        <v>2048</v>
+        <v>2024</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>128</v>
@@ -7701,7 +7923,7 @@
         <v>18</v>
       </c>
       <c r="I27" s="1">
-        <v>2049</v>
+        <v>2024</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>128</v>
@@ -7730,7 +7952,7 @@
         <v>18</v>
       </c>
       <c r="I28" s="1">
-        <v>2050</v>
+        <v>2024</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>128</v>
@@ -7759,7 +7981,7 @@
         <v>18</v>
       </c>
       <c r="I29" s="1">
-        <v>2051</v>
+        <v>2024</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>128</v>
@@ -7788,7 +8010,7 @@
         <v>18</v>
       </c>
       <c r="I30" s="1">
-        <v>2052</v>
+        <v>2024</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>128</v>
@@ -7817,7 +8039,7 @@
         <v>18</v>
       </c>
       <c r="I31" s="1">
-        <v>2053</v>
+        <v>2024</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>128</v>
@@ -7846,7 +8068,7 @@
         <v>18</v>
       </c>
       <c r="I32" s="1">
-        <v>2054</v>
+        <v>2024</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>128</v>
@@ -7875,7 +8097,7 @@
         <v>18</v>
       </c>
       <c r="I33" s="1">
-        <v>2055</v>
+        <v>2024</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>128</v>
@@ -7904,7 +8126,7 @@
         <v>18</v>
       </c>
       <c r="I34" s="1">
-        <v>2056</v>
+        <v>2024</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>128</v>
@@ -7933,7 +8155,7 @@
         <v>18</v>
       </c>
       <c r="I35" s="1">
-        <v>2057</v>
+        <v>2024</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>128</v>
@@ -7962,7 +8184,7 @@
         <v>18</v>
       </c>
       <c r="I36" s="1">
-        <v>2058</v>
+        <v>2024</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>128</v>
@@ -7991,7 +8213,7 @@
         <v>18</v>
       </c>
       <c r="I37" s="1">
-        <v>2059</v>
+        <v>2024</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>128</v>
@@ -8020,7 +8242,7 @@
         <v>18</v>
       </c>
       <c r="I38" s="1">
-        <v>2060</v>
+        <v>2024</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>128</v>
@@ -8049,7 +8271,7 @@
         <v>18</v>
       </c>
       <c r="I39" s="1">
-        <v>2061</v>
+        <v>2024</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>128</v>
@@ -8078,7 +8300,7 @@
         <v>18</v>
       </c>
       <c r="I40" s="1">
-        <v>2062</v>
+        <v>2024</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>128</v>
@@ -8107,7 +8329,7 @@
         <v>18</v>
       </c>
       <c r="I41" s="1">
-        <v>2063</v>
+        <v>2024</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>128</v>
@@ -8136,7 +8358,7 @@
         <v>18</v>
       </c>
       <c r="I42" s="1">
-        <v>2064</v>
+        <v>2024</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>128</v>
@@ -8156,7 +8378,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57D8CED-777E-7D4C-94EE-6BAC68BDA826}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -8208,11 +8430,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>187</v>
       </c>
@@ -8232,7 +8459,1052 @@
         <v>186</v>
       </c>
     </row>
+    <row r="3" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="255" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="255" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="356" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="255" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="238" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/data/input/adidas.xlsx
+++ b/data/input/adidas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2183A7-ADA6-784D-9B2A-A8D49DC0D44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB982AE-1552-9845-8822-89C00875CF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="600" windowWidth="27340" windowHeight="17400" activeTab="4" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="1460" yWindow="600" windowWidth="27340" windowHeight="17400" activeTab="5" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -136,10 +136,6 @@
     <t>Despite all the challenges, we used 2020 to make adidas a better company. Our business recovered quickly after having hit the lowest point in the second quarter and returned to growth in the fourth quarter. We connected with more consumers than ever before and expanded our digital capabilities and reach. We continued to invest in sustainability and our people. Last but not least, we increased our operational and financial flexibility. As a result, we are now well positioned to tackle both short-term uncertainty and long-term growth.</t>
   </si>
   <si>
-    <t>Not surprisingly, our financial results were significantly impacted by the negative effects of the
-coronavirus pandemic. Revenues decreased 14% on a currency-neutral basis due to the widespread store closures and lower traffic once stores reopened. Revenues in Russia/CIS remained flat, while currency neutral sales were down in all other major market segments. We were able to achieve a gross margin level of 49.7%, limiting the decline to 2.3 percentage points through a disciplined sell-in in a very promotional industry environment. As a result of the revenue shortfall, the company’s operating margin decreased 7.5 percentage points to 3.8% and net income from continuing operations decreased 78% to € 429 million.</t>
-  </si>
-  <si>
     <t>Exceptional growth in e-commerce</t>
   </si>
   <si>
@@ -393,14 +389,6 @@
     <t>MY HEARTFELT THANKS GO OUT TO ALL OUR EMPLOYEES AROUND THE WORLD. I AM EXTREMELY PROUD TO BE PART OF THIS WINNING TEAM.</t>
   </si>
   <si>
-    <t>I can confidently say that 2021 was a much better year than 2020. On the back of successful vaccination campaigns around the globe, the worldwide economy started to recover. Sport returned to the global stage, with the UEFA EURO 2020 football tournament and the Tokyo 2020 Olympics finally taking place, creating huge excitement around the world. That said, the covid-19 pandemic continued to impact lives and businesses across the globe. At adidas, we delivered a set of strong results despite heavy disruptions in supply and demand, with currency-neutral sales up 16% to more than € 21 billion and a net income from continuing operations of € 1.492 billion – an improvement of more than € 1 billion compared to the previous year. In addition, welaunched our new 2025 strategy ‘Own the Game’ which will set us up for
-long-term success in this attractive industry.</t>
-  </si>
-  <si>
-    <t>Let me stay on the topic of sport because that’s what adidas is all about. Sport defines our past, present and future. I was so happy to see football returning to the stadiums – albeit with reduced capacities – at the UEFA EURO 2020 last summer. For the first time, the tournament was played across the entire
-continent, showcasing the unifying power of sport. For us, it was a particular pleasure to host the German national football team in the newly built ‘Home Ground’ at our headquarters in Herzogenaurach, Germany. Hosting a world-class team on our premises during such a major tournament was an industry first.</t>
-  </si>
-  <si>
     <t>Our campus also provided the backdrop for yet another world-class sporting event: the ‘adizero: Road to Records,’ a race named after our signature performance running shoe. We invited 90 elite adidas runners to compete in our half-marathon, 10k and 5k races and they didn’t let us down, setting new world records in both the 5k and 10k events. Overall, we had a fantastic year in running with more wins, more world records and more podiums at major road races than all other brands combined. Peres Jepchirchir from Kenya led the charge, becoming the first person to win both the Olympic and the New York City marathon in the same year.</t>
   </si>
   <si>
@@ -430,11 +418,6 @@
   </si>
   <si>
     <t>Based on our strategy, we have set ourselves ambitious targets that will be measured against our 2021 financial year as a baseline. We aim to increase sales by an average of between 8% and 10% per year on a currency-neutral basis over the four-year period between 2021 and 2025. Gross margin is forecast to expand to a level of between 53% and 55%, and the operating margin to a level of between 12% and 14% by 2025. Net income from continuing operations is also projected to increase substantially by an average of between 16% and 18% per year over the four-year period between 2021 and 2025. Driven by the significant top-line growth and strong bottom-line expansion, adidas will generate substantial cumulative free cash flow. The majority of this – between € 8 billion and € 9 billion for the five-year period – will be distributed to you, our shareholders, through regular dividend payouts in a range of between 30% and 50% of net income from continuing operations, complemented with share buybacks.</t>
-  </si>
-  <si>
-    <t>I look into 2022 with optimism. We are well prepared to execute our strategic priorities diligently, our product line-up looks great, and we will impactfully demonstrate our brand attitude of ‘Impossible is Nothing’ throughout the entire year. Consequently, we expect currency-neutral net sales to grow at a rate
-between 12% and 14% and our gross margin is projected to increase to a level of between 51.5% and 52.0%. Driven by the strong sales growth and the gross margin improvement, we expect an operating margin of between 10.5% and 11.0%. We will grow the bottom line significantly faster than the top line. As
-a result, net income from continuing operations is anticipated to increase to a level of between € 1.8 billion and € 1.9 billion, making 2022 another successful year for adidas.</t>
   </si>
   <si>
     <t>2021 threw a variety of challenges at us. I am proud that we mastered these challenges, launched a compelling new strategy, and delivered strong financial results. My heartfelt thanks go out to all our 61,400 employees around the world. They are the ones that serve and delight our consumers every single day by creating, selling, and delivering our products. They are the ones that show incredible commitment, passion, and resilience in times of continued uncertainty. I am extremely proud to be part of this winning team. Together, we are adidas – the best sports brand in the world.
@@ -1222,417 +1205,428 @@
     <t>When you started two years ago, improving the relationship with your retail partners was a key priority. Have you made the progress that you were envisioning back then?</t>
   </si>
   <si>
-    <t>Yes and no. Understandably, it took a while for them to open up to us again. And depending on where in the world you look, that opening up and giving more shelf space to us has happened at different speeds. In our home market in Europe, it was the easiest because we could make our commitment so easily visible. And of course, supplying them with products that they needed to be successful in a difficult marketplace gave them a lot of confidence. It's of course more difficult in the US, given the strong local brands. But also in
-the US, retail partners have started to believe in us and are now giving us more distribution, we just need to have some patience. I think globally, we now have a reputation among retailers that we are there for them. Our people have the service attitude and are starting to get the sales attitude back again. But of
+    <t>You once said that there is literally no retailer around the world where you couldn’t double the business with. How far are you in achieving this?</t>
+  </si>
+  <si>
+    <t>Of course there are retailers today where we have gone from less than 10% share to more than 20%. In that case, doubling again is not realistic. So given what we have achieved over the past two years the statement is probably not true anymore everywhere. But in many, many markets, it's still the same situation. And there is no retailer around the world where we cannot significantly improve our performance, and there are many with which we can still double our share.</t>
+  </si>
+  <si>
+    <t>Halfway into your path towards being a healthy company in 2026 – what has gone better than expected? And has there been anything that has taken longer than initially anticipated?</t>
+  </si>
+  <si>
+    <t>The brand has turned positive in front of the consumer quicker than we could have hoped for. As I said many times, sometimes you need some luck and sometimes timing is everything. And then, of course, the effort and attitude of our people have been key as well. I think we are a little bit further ahead than I would have thought when we started two years ago. On the other hand, the world has become even more complicated. If you look at the conflicts and tensions around the world, these are making the world more difficult. But if we have the right attitude and are agile when there are changes, we may even turn this into a competitive advantage for us.</t>
+  </si>
+  <si>
+    <t>So you are ahead of plan at halftime. What’s your halftime speech to your team going to look like? Do you need to change your gameplan for the second half?</t>
+  </si>
+  <si>
+    <t>The most important thing is not to fall in the trap of being happy with what we have achieved and starting to defend. I think that we need to have that vision to actually be #1 in all markets. We might not achieve it everywhere, but we should have this attitude because there's no rational reason not to. Think of our 75- year history, all the franchises, the pipeline of technologies, the resources and the reach we have as a brand and as a company. We have all the good reasons to be out there in all the markets around the world – maybe with the exception of the US – with the clear ambition of being #1. That will be the halftime speech.</t>
+  </si>
+  <si>
+    <t>Anything that concerns you, from a personal or a business perspective? How do you deal with the elevated uncertainty that affects us all one way or another?</t>
+  </si>
+  <si>
+    <t>The worst thing you can do in an organization is not to talk about the issues that are difficult. I think we have created a culture to talk about all these uncertainties. We can talk about everything, the things that work well and also about things that haven’t worked. In our industry, not everything that you do will be a success. You will make mistakes, but you need to do many things and that's why you shouldn't stop doing things just because something has gone wrong. And we should not be afraid. Our people have strong personalities and the right attitude to take risks. That's why I'm saying that – if we continue to give them the right frame and the right support – then we are going to be a very, very good company.</t>
+  </si>
+  <si>
+    <t>How do you personally deal with such a volatile environment and the pressure that it brings along?</t>
+  </si>
+  <si>
+    <t>I think I have accepted that uncertainty is part of life. When I look at what we have been through just the last five years, there have been things that no one would have imagined to happen. There are always going to be things that are negative or uncertain. But in the bigger scheme of things, I am so lucky working in an industry that has great potential. I am working in a company that has a lot of potential. I've been in rough times, so I don't get worried that easily. I was much more worried when I was 25 than I am now. So it's probably age and experience that make you not feel the pressure that much.</t>
+  </si>
+  <si>
+    <t>What are you looking forward to the most this year</t>
+  </si>
+  <si>
+    <t>There is no such major sports event in 2025 like last year. And still there are so many fun things to lookforward to that I can't mention only one thing. From a business perspective, I look forward to see a continuous improvement in what we do. And I look forward to see our people feeling that they are successful and energized by that. The best thing is to see our people feeling that they're getting things done and seeing them grow because they're successful.</t>
+  </si>
+  <si>
+    <t>DEU24A01-00</t>
+  </si>
+  <si>
+    <t>DEU24A01-01</t>
+  </si>
+  <si>
+    <t>DEU24A02-00</t>
+  </si>
+  <si>
+    <t>DEU24A02-01</t>
+  </si>
+  <si>
+    <t>DEU24A03-00</t>
+  </si>
+  <si>
+    <t>DEU24A03-01</t>
+  </si>
+  <si>
+    <t>DEU24A04-00</t>
+  </si>
+  <si>
+    <t>DEU24A04-01</t>
+  </si>
+  <si>
+    <t>DEU24A05-00</t>
+  </si>
+  <si>
+    <t>DEU24A05-01</t>
+  </si>
+  <si>
+    <t>DEU24A06-00</t>
+  </si>
+  <si>
+    <t>DEU24A06-01</t>
+  </si>
+  <si>
+    <t>DEU24A07-00</t>
+  </si>
+  <si>
+    <t>DEU24A08-00</t>
+  </si>
+  <si>
+    <t>DEU24A08-01</t>
+  </si>
+  <si>
+    <t>DEU24A09-00</t>
+  </si>
+  <si>
+    <t>DEU24A09-01</t>
+  </si>
+  <si>
+    <t>DEU24A10-00</t>
+  </si>
+  <si>
+    <t>DEU24A10-01</t>
+  </si>
+  <si>
+    <t>DEU24A11-00</t>
+  </si>
+  <si>
+    <t>DEU24A11-01</t>
+  </si>
+  <si>
+    <t>DEU24A12-00</t>
+  </si>
+  <si>
+    <t>DEU24A12-01</t>
+  </si>
+  <si>
+    <t>DEU24A13-00</t>
+  </si>
+  <si>
+    <t>DEU24A13-01</t>
+  </si>
+  <si>
+    <t>DEU24A14-00</t>
+  </si>
+  <si>
+    <t>DEU24A15-00</t>
+  </si>
+  <si>
+    <t>DEU24A15-01</t>
+  </si>
+  <si>
+    <t>DEU24A16-00</t>
+  </si>
+  <si>
+    <t>DEU24A16-01</t>
+  </si>
+  <si>
+    <t>DEU24A17-00</t>
+  </si>
+  <si>
+    <t>DEU24A17-01</t>
+  </si>
+  <si>
+    <t>DEU24A18-00</t>
+  </si>
+  <si>
+    <t>DEU24A18-01</t>
+  </si>
+  <si>
+    <t>DEU24A19-00</t>
+  </si>
+  <si>
+    <t>DEU24A19-01</t>
+  </si>
+  <si>
+    <t>DEU24A20-00</t>
+  </si>
+  <si>
+    <t>DEU24A20-01</t>
+  </si>
+  <si>
+    <t>DEU24A21-00</t>
+  </si>
+  <si>
+    <t>DEU24A21-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE GLOBAL POTENTIAL FOR ADIDAS IS ALMOST UNLIMITED </t>
+  </si>
+  <si>
+    <t>Bjørn, 2025 was quite an eventful year, to say the least. Before we move to the business side, what was your most memorable sports moment last year?</t>
+  </si>
+  <si>
+    <t>Given the huge amount of great sports events on small or larger stages throughout the year, it wouldn’t be fair to call out just one. When people come together to do sports, this is always fantastic. I think it's fair to say that, for our brand, there were many events where we showed up both with our athletes and our products that were great. It was definitely a great sports year for our company.</t>
+  </si>
+  <si>
+    <t>Turning to the business, how would you summarize 2025?</t>
+  </si>
+  <si>
+    <t>I am very happy and proud of what our people have achieved. I am very happy when you look at our progress over the last three years, it's gone faster than we expected in many areas. In early 2023, we laid out what we thought we had to do over the next four years. 2025 was the third year, and we already achieved many of the goals we set ourselves. We first had growth in the Lifestyle area, especially driven by footwear, through which we created a lot of brand heat globally. We have gotten credibility in Performance again, also in categories where we thought that the road was longer. The development in Running – especially on the high end – has been great. In Football, we've taken back market leadership, and in Basketball, we have innovation and product that I think people didn't believe we can do that quickly. Our visibility in sports – both in big global sports and smaller local sports – has grown enormously. The fact that we have grown double digits for two consecutive years now and achieved double-digit growth all over the world in 2025 shows you the enormous power of this brand.</t>
+  </si>
+  <si>
+    <t>What’s driving this very broad success in your opinion?</t>
+  </si>
+  <si>
+    <t>First of all, credit to the fantastic brand and company we work for. The global potential for adidas is almost unlimited because we have 76 years of history, and we have so many stories to tell. While the brand has been culturally relevant in all our markets, we are now also back as a sports brand all over the world. The combination of the awareness, the history, the cultural relevance, and the performance credibility is quite unique. And becoming a global brand with a local mindset has been a huge enabler across all of this. The brand is strong, and we have very good and talented people that are utilizing the strength of the brand in the local markets. It’s now up to us how we leverage this in the right way, both in the short term and the long term.</t>
+  </si>
+  <si>
+    <t>Can you help us understand what ‘global brand with a local mindset’ means?</t>
+  </si>
+  <si>
+    <t>In a global world where information flows very quickly, you could believe that the choice of consumers is the same everywhere. But it clearly isn’t. We see that different markets have different developments when it comes to taste. The markets are more conscious of their own culture, meaning that the choice of the product, the usage of the product, the meaning of what sport is, are different. I can't force the consumer in China to buy the same product as in Norway. And we all know the difference between Europe and America when it comes to the sports that are relevant. We need to please the consumer where he or she is, all within the frame of the brand. We need to have a global frame that defines what adidas is, and how we should utilize the brand and have a vision for it. But then how we execute that in the different regions has to be different to be successful. We should still be a sports brand at our core, and we should be utilizing the strength of sports into local culture. And then, of course, there are lifestyle, fashion, and comfort elements to take into account.</t>
+  </si>
+  <si>
+    <t>If we look at the overall product offering last year across global and local, what are the products that you want to call out?</t>
+  </si>
+  <si>
+    <t>With the Samba, the Gazelle, and the Spezial, we really brought the brand back to the young female consumer. This isn’t something that happens quickly, it’s built over time, and it's very, very strong still. Then, I would call out how we extended the popularity of the Three Stripes from footwear to apparel. When you look at the sequence of that, it actually happened exactly that way. Running is another call-out, because it was the most difficult category for us to establish ourselves in at the top. Our teams have done a tremendous job, creating what – in my opinion – are the best running shoes. Once you have credibility at the top, winning marathons and setting records, it's easier to be commercially successful in everyday running and comfort running products. And that is, of course, the plan. I could also call out the Predator in Football, the Adizero Dropset in Training, or so many other examples of great products in our Performance categories. I can't point to one product or one segment. I am extremely proud to see what the teams have done. How creative and innovative we have been across the teams and categories. How the consumers have reacted to it the last three years showcases how good this brand is and the people behind it.</t>
+  </si>
+  <si>
+    <t>I AM VERY HAPPY AND PROUD OF WHAT OUR PEOPLE HAVE ACHIEVED</t>
+  </si>
+  <si>
+    <t>One of the things that you haven’t mentioned is the pet collection that has caught quite some attention globally after being launched in China. Are you trying to expand into new territories here?</t>
+  </si>
+  <si>
+    <t>I had nothing to do with that because that idea, of course, came from our China team. They used the popularity of adidas to extend the range. I would say it's a local marketing tool that has suddenly become a business. Again, it shows the creativity of the team. It shows that our teams on the ground know their consumers and what matters to them most. And it shows the impact of good ideas.</t>
+  </si>
+  <si>
+    <t>You mentioned in the past that it will take time for the improved and expanded product range to become fully visible in the trade. Where are you with that?</t>
+  </si>
+  <si>
+    <t>It’s different from market to market. It's obvious with the success of lifestyle footwear that many retailers wanted it very quickly and adopted it. But there are categories where we still don’t have the space we believe we should. We do think we are competitive, and there are many markets where we should be able to increase our space in the store and on the shelf. But as always, the retailers decide on who they allocate space to. If they do that rationally, they will allocate space to those who give them the highest contribution per square meter, and we think we can do that. We made huge progress in the last three years, but if you look at running for example, there are places around the world where we still have very little distribution, which again shows the huge opportunity we have in our hands.</t>
+  </si>
+  <si>
+    <t>How did listening to the retail partners and working closer with them change the assortment and how the brand shows up in the stores?</t>
+  </si>
+  <si>
+    <t>For me, listening to our retail partners is crucial. If you sit in headquarters and decide what should be in all the stores around the world, it’s simply not going to work. We have an open dialogue with consumers, with athletes, and with our retailers across the different markets. Our market teams have been very active in engaging with our retailers, and we have opened all our creation centers to work with them. We’ve seen improvements in that process, but it can always be better. We are getting very positive feedback from the retailers on the way we work, and how the flexibility and the speed of our creation teams have improved. We are on a very, very good way of giving this fantastic adidas brand the right platform to be market leader in many markets.</t>
+  </si>
+  <si>
+    <t>What has also grown is the roster of partners around the world, from global partners like Liverpool FC to more local ones like Penn State or Gilas Pilipinas, the national basketball team of the Philippines. What role do these partners play for adidas?</t>
+  </si>
+  <si>
+    <t>If you don’t showcase the brand with relevant partners, it will disappear over time. Our philosophy is that adidas should be visible and relevant. There are certain sports and partners that are very global, like football and Liverpool, and there are partners that are very local. Authentic partnerships that give us organic visibility are more important than paid media campaigns. That's why we are investing a lot in partnerships, both globally and locally – not only in sports, but in whatever is culturally relevant for the consumer in the different markets. It can be in fashion, it can be in music, and it can be in other areas that the consumer thinks is relevant.</t>
+  </si>
+  <si>
+    <t>2025 saw the return of adidas into motorsports. How did that go and what's going to happen next?</t>
+  </si>
+  <si>
+    <t>F1 is growing globally when it gets to viewership. And the viewership is getting younger and younger and they’re both female and male. We made the decision to team up with the Mercedes AMG Petronas F1 team very quickly, and our team did an unbelievable job launching it. I think we went from handshake to having products in the markets in under ten months. We now have one year behind us commercially, and it's been more successful than anybody expected. We have also added Audi Revolut and have just launched their first collection, so that means we will have two teams for the upcoming season, and the reaction has been great. With fans buying both merchandise and lifestyle products inspired by F1, there are big opportunities to expand our business in the future.</t>
+  </si>
+  <si>
+    <t>You made some organizational changes in 2025 in order to move closer to markets and consumers. Why were those changes required?</t>
+  </si>
+  <si>
+    <t>Given the uncertainty when it comes to the geopolitical situation and the unstable environment we operate in, getting closer to the consumer and making sure that we work with the markets has become even more important. So, we have strengthened our creative resources in the different regions and given the markets more freedom in developing products, signing partners, and doing activations. I think the biggest success story that we can show here is China. Firstly, our Chinese teams have a lot of creative people. Secondly, they have factories next door, so they can design, develop, and source product on a shorter lead time. Also, given the mono-branded retail environment, where we have around 8,000 adidas branded stores – even if they are operated by wholesale partners – that gives us a different value chain to work with. Empowering our markets to use their local setup to win the local consumer is a key reason for our current success. And our global teams, of course, support it. But this means we also had to change our structures and processes to reflect the reality of how we work, leading to changes and role reductions at our headquarters in Herzogenaurach. It is very important for me to ensure that all changes are carried out with the utmost respect and care for all employees. But there's no choice. In order to be successful long-term, we need to be agile and on our toes to be able to react as quickly as possible to changes. And this means we have to put decision-making as close as we can to where these decisions need to be made.</t>
+  </si>
+  <si>
+    <t>You’ve been in this industry for many years. How has the competitive landscape changed and how attractive is the sporting goods industry today?</t>
+  </si>
+  <si>
+    <t>It depends on what time period you look at. If you go back to the beginning of my time in the industry, European brands were dominating. Then we had the American brands coming up, that was the first big change. Now we are seeing specialist brands coming up, focusing on just one or two categories, and local players trying to go global. So the amount of competitors has increased. But the awareness and the positiveness towards adidas has also increased. We are in a very, very attractive industry, because sports in all its dimensions will continue to grow. I also think on the lifestyle side that casualization will never stop, and I strongly believe that more and more people will be wearing sports shoes across all age groups because they’re the most comfortable choice. All of this is of course very good for us, because we are in many markets, we are in multiple categories, we have 76 years of history we can build on, and we have all the resources to continue our success. So, I see a very positive industry development for us for the future. Moving closer to the consumer locally is key to enabling our ability to successfully compete with all other brands.</t>
+  </si>
+  <si>
+    <t>WHEN PEOPLE COME TOGETHER TO DO SPORTS, THIS IS ALWAYS FANTASTIC</t>
+  </si>
+  <si>
+    <t>adidas’ market share is significantly higher than it was three years ago. How much more potential is there to increase the market share?</t>
+  </si>
+  <si>
+    <t>The potential is different from market to market, depending on what the starting point is. But if you look at our biggest competitor and its size compared to ours, then that should be answer enough. I can’t see any market where we cannot gain substantial share over time. Given our relatively low market share in the US, we have the ambition to double our business there. I just think we need to be more American and that’s what we’re trying to do. The American team needs to invest in what is relevant for America. Outside of the US we have the ambition of being market leader in all markets. That doesn’t mean that we will be it, but we should have the ambition. And we need to understand what we need to do in every market to achieve this ambition.</t>
+  </si>
+  <si>
+    <t>The US is a good segue to the next question. The FIFA World Cup 2026 will be a huge event and a great platform. What are your expectations for the brand and the business?</t>
+  </si>
+  <si>
+    <t>Other than the World Cup, what does success for adidas look like this year? What are your priorities for 2026?</t>
+  </si>
+  <si>
+    <t>The World Cup is always a great event. It is the biggest sports event when it comes to viewership all over the world. Football is the DNA of our brand, and being market leader, it is of huge importance to adidas. And it's a great platform to take football as a sport and highlight the cultural relevance of it. That's why the collection this year is so much wider than it's been before. We clearly see that there is a football interest in fashion and lifestyle that we have never seen before. We will focus on connecting to the US consumer, the Mexican consumer, and the Canadian consumer. So far, the reaction to what we have showcased, and our first product launches has been great. Aside from business, I really believe that the World Cup can be a game changer when it comes to where the world is going, given the positive feelings that these events bring. I strongly believe that sports is one of the few things that brings us all together. Let’s hope that the World Cup will strengthen some of the conversations that are going on to create peace again.</t>
+  </si>
+  <si>
+    <t>2026 is a year where we will continue the momentum that we have. There is no doubt that the potential of this brand in this attractive market is to continue to grow a couple of billions every year. To do that on a consistent basis, we need to keep developing our people and keep working on the way we execute. Not only in front of the consumer, where we are very successful already. But also in the way we work. Just like athletes, we will continue to work hard on us, we will continue to adapt our processes to the changing environment so that we become an even better company and keep building an even stronger platform for the future.</t>
+  </si>
+  <si>
+    <t>Talking about the future, what are your plans and goals for adidas in the coming years?</t>
+  </si>
+  <si>
+    <t>I believe the next couple of years should show that adidas can take market leadership in a lot more markets. I think that we will continue to outgrow the industry and take more market share, utilizing the strength of our brand, our resources, our authenticity, our innovation, and our creativity. And to do that, we need to be dedicated to our consumers and attract, develop, and keep the best people. Because I think in this world where we talk a lot about AI and the tools that can make us better, we are still a people business. We should never forget that the athlete is a person, the consumer is a person, and the employee is a person. adidas is a great company to work with and to work for, and we are obsessed about fulfilling the needs of consumers and athletes.</t>
+  </si>
+  <si>
+    <t>Last question: What are your personal goals for 2026 and beyond?</t>
+  </si>
+  <si>
+    <t>I enjoy what I do, also doing a lot of sports. I have a lot of energy for this great job, a lot of passion for this fantastic brand, and I feel extremely privileged in what I do. So, my goal really is just to continue the great journey we are on, give this brand what it deserves, and get this company to where it belongs.</t>
+  </si>
+  <si>
+    <t>DEU25A01-00</t>
+  </si>
+  <si>
+    <t>DEU25A01-01</t>
+  </si>
+  <si>
+    <t>DEU25A02-00</t>
+  </si>
+  <si>
+    <t>DEU25A02-01</t>
+  </si>
+  <si>
+    <t>DEU25A03-00</t>
+  </si>
+  <si>
+    <t>DEU25A03-01</t>
+  </si>
+  <si>
+    <t>DEU25A04-00</t>
+  </si>
+  <si>
+    <t>DEU25A04-01</t>
+  </si>
+  <si>
+    <t>DEU25A05-00</t>
+  </si>
+  <si>
+    <t>DEU25A05-01</t>
+  </si>
+  <si>
+    <t>DEU25A06-00</t>
+  </si>
+  <si>
+    <t>DEU25A07-00</t>
+  </si>
+  <si>
+    <t>DEU25A07-01</t>
+  </si>
+  <si>
+    <t>DEU25A08-00</t>
+  </si>
+  <si>
+    <t>DEU25A08-01</t>
+  </si>
+  <si>
+    <t>DEU25A09-00</t>
+  </si>
+  <si>
+    <t>DEU25A09-01</t>
+  </si>
+  <si>
+    <t>DEU25A10-00</t>
+  </si>
+  <si>
+    <t>DEU25A10-01</t>
+  </si>
+  <si>
+    <t>DEU25A11-00</t>
+  </si>
+  <si>
+    <t>DEU25A11-01</t>
+  </si>
+  <si>
+    <t>DEU25A12-00</t>
+  </si>
+  <si>
+    <t>DEU25A12-01</t>
+  </si>
+  <si>
+    <t>DEU25A13-00</t>
+  </si>
+  <si>
+    <t>DEU25A13-01</t>
+  </si>
+  <si>
+    <t>DEU25A14-00</t>
+  </si>
+  <si>
+    <t>DEU25A15-00</t>
+  </si>
+  <si>
+    <t>DEU25A15-01</t>
+  </si>
+  <si>
+    <t>DEU25A16-00</t>
+  </si>
+  <si>
+    <t>DEU25A16-01</t>
+  </si>
+  <si>
+    <t>DEU25A17-00</t>
+  </si>
+  <si>
+    <t>DEU25A17-01</t>
+  </si>
+  <si>
+    <t>DEU25A18-00</t>
+  </si>
+  <si>
+    <t>DEU25A18-01</t>
+  </si>
+  <si>
+    <t>DEU25A19-00</t>
+  </si>
+  <si>
+    <t>DEU25A19-01</t>
+  </si>
+  <si>
+    <t>quore</t>
+  </si>
+  <si>
+    <t>Source_type</t>
+  </si>
+  <si>
+    <t>annual_report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Souce_type </t>
+  </si>
+  <si>
+    <t xml:space="preserve">annual_report </t>
+  </si>
+  <si>
+    <t>Communicator_name</t>
+  </si>
+  <si>
+    <t>Communicator_role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ceo </t>
+  </si>
+  <si>
+    <t>ceo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interview </t>
+  </si>
+  <si>
+    <t>interview</t>
+  </si>
+  <si>
+    <t>Yes and no. Understandably, it took a while for them to open up to us again. And depending on where in the world you look, that opening up and giving more shelf space to us has happened at different speeds. In our home market in Europe, it was the easiest because we could make our commitment so easily visible. And of course, supplying them with products that they needed to be successful in a difficult marketplace gave them a lot of confidence. It's of course more difficult in the US, given the strong local brands. But also in the US, retail partners have started to believe in us and are now giving us more distribution, we just need to have some patience. I think globally, we now have a reputation among retailers that we are there for them. Our people have the service attitude and are starting to get the sales attitude back again. But of
 course there are other brands that have more distribution than us, especially in the US. Our goal must be to get more shelf space so we can prove that when we get that, we get better sell through and then build even stronger and bigger partnerships. We definitely aren’t at the end of improving relationships and increasing distribution.</t>
   </si>
   <si>
-    <t>You once said that there is literally no retailer around the world where you couldn’t double the business with. How far are you in achieving this?</t>
-  </si>
-  <si>
-    <t>Of course there are retailers today where we have gone from less than 10% share to more than 20%. In that case, doubling again is not realistic. So given what we have achieved over the past two years the statement is probably not true anymore everywhere. But in many, many markets, it's still the same situation. And there is no retailer around the world where we cannot significantly improve our performance, and there are many with which we can still double our share.</t>
-  </si>
-  <si>
-    <t>Halfway into your path towards being a healthy company in 2026 – what has gone better than expected? And has there been anything that has taken longer than initially anticipated?</t>
-  </si>
-  <si>
-    <t>The brand has turned positive in front of the consumer quicker than we could have hoped for. As I said many times, sometimes you need some luck and sometimes timing is everything. And then, of course, the effort and attitude of our people have been key as well. I think we are a little bit further ahead than I would have thought when we started two years ago. On the other hand, the world has become even more complicated. If you look at the conflicts and tensions around the world, these are making the world more difficult. But if we have the right attitude and are agile when there are changes, we may even turn this into a competitive advantage for us.</t>
-  </si>
-  <si>
-    <t>So you are ahead of plan at halftime. What’s your halftime speech to your team going to look like? Do you need to change your gameplan for the second half?</t>
-  </si>
-  <si>
-    <t>The most important thing is not to fall in the trap of being happy with what we have achieved and starting to defend. I think that we need to have that vision to actually be #1 in all markets. We might not achieve it everywhere, but we should have this attitude because there's no rational reason not to. Think of our 75- year history, all the franchises, the pipeline of technologies, the resources and the reach we have as a brand and as a company. We have all the good reasons to be out there in all the markets around the world – maybe with the exception of the US – with the clear ambition of being #1. That will be the halftime speech.</t>
-  </si>
-  <si>
-    <t>Anything that concerns you, from a personal or a business perspective? How do you deal with the elevated uncertainty that affects us all one way or another?</t>
-  </si>
-  <si>
-    <t>The worst thing you can do in an organization is not to talk about the issues that are difficult. I think we have created a culture to talk about all these uncertainties. We can talk about everything, the things that work well and also about things that haven’t worked. In our industry, not everything that you do will be a success. You will make mistakes, but you need to do many things and that's why you shouldn't stop doing things just because something has gone wrong. And we should not be afraid. Our people have strong personalities and the right attitude to take risks. That's why I'm saying that – if we continue to give them the right frame and the right support – then we are going to be a very, very good company.</t>
-  </si>
-  <si>
-    <t>How do you personally deal with such a volatile environment and the pressure that it brings along?</t>
-  </si>
-  <si>
-    <t>I think I have accepted that uncertainty is part of life. When I look at what we have been through just the last five years, there have been things that no one would have imagined to happen. There are always going to be things that are negative or uncertain. But in the bigger scheme of things, I am so lucky working in an industry that has great potential. I am working in a company that has a lot of potential. I've been in rough times, so I don't get worried that easily. I was much more worried when I was 25 than I am now. So it's probably age and experience that make you not feel the pressure that much.</t>
-  </si>
-  <si>
-    <t>What are you looking forward to the most this year</t>
-  </si>
-  <si>
-    <t>There is no such major sports event in 2025 like last year. And still there are so many fun things to lookforward to that I can't mention only one thing. From a business perspective, I look forward to see a continuous improvement in what we do. And I look forward to see our people feeling that they are successful and energized by that. The best thing is to see our people feeling that they're getting things done and seeing them grow because they're successful.</t>
-  </si>
-  <si>
-    <t>DEU24A01-00</t>
-  </si>
-  <si>
-    <t>DEU24A01-01</t>
-  </si>
-  <si>
-    <t>DEU24A02-00</t>
-  </si>
-  <si>
-    <t>DEU24A02-01</t>
-  </si>
-  <si>
-    <t>DEU24A03-00</t>
-  </si>
-  <si>
-    <t>DEU24A03-01</t>
-  </si>
-  <si>
-    <t>DEU24A04-00</t>
-  </si>
-  <si>
-    <t>DEU24A04-01</t>
-  </si>
-  <si>
-    <t>DEU24A05-00</t>
-  </si>
-  <si>
-    <t>DEU24A05-01</t>
-  </si>
-  <si>
-    <t>DEU24A06-00</t>
-  </si>
-  <si>
-    <t>DEU24A06-01</t>
-  </si>
-  <si>
-    <t>DEU24A07-00</t>
-  </si>
-  <si>
-    <t>DEU24A08-00</t>
-  </si>
-  <si>
-    <t>DEU24A08-01</t>
-  </si>
-  <si>
-    <t>DEU24A09-00</t>
-  </si>
-  <si>
-    <t>DEU24A09-01</t>
-  </si>
-  <si>
-    <t>DEU24A10-00</t>
-  </si>
-  <si>
-    <t>DEU24A10-01</t>
-  </si>
-  <si>
-    <t>DEU24A11-00</t>
-  </si>
-  <si>
-    <t>DEU24A11-01</t>
-  </si>
-  <si>
-    <t>DEU24A12-00</t>
-  </si>
-  <si>
-    <t>DEU24A12-01</t>
-  </si>
-  <si>
-    <t>DEU24A13-00</t>
-  </si>
-  <si>
-    <t>DEU24A13-01</t>
-  </si>
-  <si>
-    <t>DEU24A14-00</t>
-  </si>
-  <si>
-    <t>DEU24A15-00</t>
-  </si>
-  <si>
-    <t>DEU24A15-01</t>
-  </si>
-  <si>
-    <t>DEU24A16-00</t>
-  </si>
-  <si>
-    <t>DEU24A16-01</t>
-  </si>
-  <si>
-    <t>DEU24A17-00</t>
-  </si>
-  <si>
-    <t>DEU24A17-01</t>
-  </si>
-  <si>
-    <t>DEU24A18-00</t>
-  </si>
-  <si>
-    <t>DEU24A18-01</t>
-  </si>
-  <si>
-    <t>DEU24A19-00</t>
-  </si>
-  <si>
-    <t>DEU24A19-01</t>
-  </si>
-  <si>
-    <t>DEU24A20-00</t>
-  </si>
-  <si>
-    <t>DEU24A20-01</t>
-  </si>
-  <si>
-    <t>DEU24A21-00</t>
-  </si>
-  <si>
-    <t>DEU24A21-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE GLOBAL POTENTIAL FOR ADIDAS IS ALMOST UNLIMITED </t>
-  </si>
-  <si>
-    <t>Bjørn, 2025 was quite an eventful year, to say the least. Before we move to the business side, what was your most memorable sports moment last year?</t>
-  </si>
-  <si>
-    <t>Given the huge amount of great sports events on small or larger stages throughout the year, it wouldn’t be fair to call out just one. When people come together to do sports, this is always fantastic. I think it's fair to say that, for our brand, there were many events where we showed up both with our athletes and our products that were great. It was definitely a great sports year for our company.</t>
-  </si>
-  <si>
-    <t>Turning to the business, how would you summarize 2025?</t>
-  </si>
-  <si>
-    <t>I am very happy and proud of what our people have achieved. I am very happy when you look at our progress over the last three years, it's gone faster than we expected in many areas. In early 2023, we laid out what we thought we had to do over the next four years. 2025 was the third year, and we already achieved many of the goals we set ourselves. We first had growth in the Lifestyle area, especially driven by footwear, through which we created a lot of brand heat globally. We have gotten credibility in Performance again, also in categories where we thought that the road was longer. The development in Running – especially on the high end – has been great. In Football, we've taken back market leadership, and in Basketball, we have innovation and product that I think people didn't believe we can do that quickly. Our visibility in sports – both in big global sports and smaller local sports – has grown enormously. The fact that we have grown double digits for two consecutive years now and achieved double-digit growth all over the world in 2025 shows you the enormous power of this brand.</t>
-  </si>
-  <si>
-    <t>What’s driving this very broad success in your opinion?</t>
-  </si>
-  <si>
-    <t>First of all, credit to the fantastic brand and company we work for. The global potential for adidas is almost unlimited because we have 76 years of history, and we have so many stories to tell. While the brand has been culturally relevant in all our markets, we are now also back as a sports brand all over the world. The combination of the awareness, the history, the cultural relevance, and the performance credibility is quite unique. And becoming a global brand with a local mindset has been a huge enabler across all of this. The brand is strong, and we have very good and talented people that are utilizing the strength of the brand in the local markets. It’s now up to us how we leverage this in the right way, both in the short term and the long term.</t>
-  </si>
-  <si>
-    <t>Can you help us understand what ‘global brand with a local mindset’ means?</t>
-  </si>
-  <si>
-    <t>In a global world where information flows very quickly, you could believe that the choice of consumers is the same everywhere. But it clearly isn’t. We see that different markets have different developments when it comes to taste. The markets are more conscious of their own culture, meaning that the choice of the product, the usage of the product, the meaning of what sport is, are different. I can't force the consumer in China to buy the same product as in Norway. And we all know the difference between Europe and America when it comes to the sports that are relevant. We need to please the consumer where he or she is, all within the frame of the brand. We need to have a global frame that defines what adidas is, and how we should utilize the brand and have a vision for it. But then how we execute that in the different regions has to be different to be successful. We should still be a sports brand at our core, and we should be utilizing the strength of sports into local culture. And then, of course, there are lifestyle, fashion, and comfort elements to take into account.</t>
-  </si>
-  <si>
-    <t>If we look at the overall product offering last year across global and local, what are the products that you want to call out?</t>
-  </si>
-  <si>
-    <t>With the Samba, the Gazelle, and the Spezial, we really brought the brand back to the young female consumer. This isn’t something that happens quickly, it’s built over time, and it's very, very strong still. Then, I would call out how we extended the popularity of the Three Stripes from footwear to apparel. When you look at the sequence of that, it actually happened exactly that way. Running is another call-out, because it was the most difficult category for us to establish ourselves in at the top. Our teams have done a tremendous job, creating what – in my opinion – are the best running shoes. Once you have credibility at the top, winning marathons and setting records, it's easier to be commercially successful in everyday running and comfort running products. And that is, of course, the plan. I could also call out the Predator in Football, the Adizero Dropset in Training, or so many other examples of great products in our Performance categories. I can't point to one product or one segment. I am extremely proud to see what the teams have done. How creative and innovative we have been across the teams and categories. How the consumers have reacted to it the last three years showcases how good this brand is and the people behind it.</t>
-  </si>
-  <si>
-    <t>I AM VERY HAPPY AND PROUD OF WHAT OUR PEOPLE HAVE ACHIEVED</t>
-  </si>
-  <si>
-    <t>One of the things that you haven’t mentioned is the pet collection that has caught quite some attention globally after being launched in China. Are you trying to expand into new territories here?</t>
-  </si>
-  <si>
-    <t>I had nothing to do with that because that idea, of course, came from our China team. They used the popularity of adidas to extend the range. I would say it's a local marketing tool that has suddenly become a business. Again, it shows the creativity of the team. It shows that our teams on the ground know their consumers and what matters to them most. And it shows the impact of good ideas.</t>
-  </si>
-  <si>
-    <t>You mentioned in the past that it will take time for the improved and expanded product range to become fully visible in the trade. Where are you with that?</t>
-  </si>
-  <si>
-    <t>It’s different from market to market. It's obvious with the success of lifestyle footwear that many retailers wanted it very quickly and adopted it. But there are categories where we still don’t have the space we believe we should. We do think we are competitive, and there are many markets where we should be able to increase our space in the store and on the shelf. But as always, the retailers decide on who they allocate space to. If they do that rationally, they will allocate space to those who give them the highest contribution per square meter, and we think we can do that. We made huge progress in the last three years, but if you look at running for example, there are places around the world where we still have very little distribution, which again shows the huge opportunity we have in our hands.</t>
-  </si>
-  <si>
-    <t>How did listening to the retail partners and working closer with them change the assortment and how the brand shows up in the stores?</t>
-  </si>
-  <si>
-    <t>For me, listening to our retail partners is crucial. If you sit in headquarters and decide what should be in all the stores around the world, it’s simply not going to work. We have an open dialogue with consumers, with athletes, and with our retailers across the different markets. Our market teams have been very active in engaging with our retailers, and we have opened all our creation centers to work with them. We’ve seen improvements in that process, but it can always be better. We are getting very positive feedback from the retailers on the way we work, and how the flexibility and the speed of our creation teams have improved. We are on a very, very good way of giving this fantastic adidas brand the right platform to be market leader in many markets.</t>
-  </si>
-  <si>
-    <t>What has also grown is the roster of partners around the world, from global partners like Liverpool FC to more local ones like Penn State or Gilas Pilipinas, the national basketball team of the Philippines. What role do these partners play for adidas?</t>
-  </si>
-  <si>
-    <t>If you don’t showcase the brand with relevant partners, it will disappear over time. Our philosophy is that adidas should be visible and relevant. There are certain sports and partners that are very global, like football and Liverpool, and there are partners that are very local. Authentic partnerships that give us organic visibility are more important than paid media campaigns. That's why we are investing a lot in partnerships, both globally and locally – not only in sports, but in whatever is culturally relevant for the consumer in the different markets. It can be in fashion, it can be in music, and it can be in other areas that the consumer thinks is relevant.</t>
-  </si>
-  <si>
-    <t>2025 saw the return of adidas into motorsports. How did that go and what's going to happen next?</t>
-  </si>
-  <si>
-    <t>F1 is growing globally when it gets to viewership. And the viewership is getting younger and younger and they’re both female and male. We made the decision to team up with the Mercedes AMG Petronas F1 team very quickly, and our team did an unbelievable job launching it. I think we went from handshake to having products in the markets in under ten months. We now have one year behind us commercially, and it's been more successful than anybody expected. We have also added Audi Revolut and have just launched their first collection, so that means we will have two teams for the upcoming season, and the reaction has been great. With fans buying both merchandise and lifestyle products inspired by F1, there are big opportunities to expand our business in the future.</t>
-  </si>
-  <si>
-    <t>You made some organizational changes in 2025 in order to move closer to markets and consumers. Why were those changes required?</t>
-  </si>
-  <si>
-    <t>Given the uncertainty when it comes to the geopolitical situation and the unstable environment we operate in, getting closer to the consumer and making sure that we work with the markets has become even more important. So, we have strengthened our creative resources in the different regions and given the markets more freedom in developing products, signing partners, and doing activations. I think the biggest success story that we can show here is China. Firstly, our Chinese teams have a lot of creative people. Secondly, they have factories next door, so they can design, develop, and source product on a shorter lead time. Also, given the mono-branded retail environment, where we have around 8,000 adidas branded stores – even if they are operated by wholesale partners – that gives us a different value chain to work with. Empowering our markets to use their local setup to win the local consumer is a key reason for our current success. And our global teams, of course, support it. But this means we also had to change our structures and processes to reflect the reality of how we work, leading to changes and role reductions at our headquarters in Herzogenaurach. It is very important for me to ensure that all changes are carried out with the utmost respect and care for all employees. But there's no choice. In order to be successful long-term, we need to be agile and on our toes to be able to react as quickly as possible to changes. And this means we have to put decision-making as close as we can to where these decisions need to be made.</t>
-  </si>
-  <si>
-    <t>You’ve been in this industry for many years. How has the competitive landscape changed and how attractive is the sporting goods industry today?</t>
-  </si>
-  <si>
-    <t>It depends on what time period you look at. If you go back to the beginning of my time in the industry, European brands were dominating. Then we had the American brands coming up, that was the first big change. Now we are seeing specialist brands coming up, focusing on just one or two categories, and local players trying to go global. So the amount of competitors has increased. But the awareness and the positiveness towards adidas has also increased. We are in a very, very attractive industry, because sports in all its dimensions will continue to grow. I also think on the lifestyle side that casualization will never stop, and I strongly believe that more and more people will be wearing sports shoes across all age groups because they’re the most comfortable choice. All of this is of course very good for us, because we are in many markets, we are in multiple categories, we have 76 years of history we can build on, and we have all the resources to continue our success. So, I see a very positive industry development for us for the future. Moving closer to the consumer locally is key to enabling our ability to successfully compete with all other brands.</t>
-  </si>
-  <si>
-    <t>WHEN PEOPLE COME TOGETHER TO DO SPORTS, THIS IS ALWAYS FANTASTIC</t>
-  </si>
-  <si>
-    <t>adidas’ market share is significantly higher than it was three years ago. How much more potential is there to increase the market share?</t>
-  </si>
-  <si>
-    <t>The potential is different from market to market, depending on what the starting point is. But if you look at our biggest competitor and its size compared to ours, then that should be answer enough. I can’t see any market where we cannot gain substantial share over time. Given our relatively low market share in the US, we have the ambition to double our business there. I just think we need to be more American and that’s what we’re trying to do. The American team needs to invest in what is relevant for America. Outside of the US we have the ambition of being market leader in all markets. That doesn’t mean that we will be it, but we should have the ambition. And we need to understand what we need to do in every market to achieve this ambition.</t>
-  </si>
-  <si>
-    <t>The US is a good segue to the next question. The FIFA World Cup 2026 will be a huge event and a great platform. What are your expectations for the brand and the business?</t>
-  </si>
-  <si>
-    <t>Other than the World Cup, what does success for adidas look like this year? What are your priorities for 2026?</t>
-  </si>
-  <si>
-    <t>The World Cup is always a great event. It is the biggest sports event when it comes to viewership all over the world. Football is the DNA of our brand, and being market leader, it is of huge importance to adidas. And it's a great platform to take football as a sport and highlight the cultural relevance of it. That's why the collection this year is so much wider than it's been before. We clearly see that there is a football interest in fashion and lifestyle that we have never seen before. We will focus on connecting to the US consumer, the Mexican consumer, and the Canadian consumer. So far, the reaction to what we have showcased, and our first product launches has been great. Aside from business, I really believe that the World Cup can be a game changer when it comes to where the world is going, given the positive feelings that these events bring. I strongly believe that sports is one of the few things that brings us all together. Let’s hope that the World Cup will strengthen some of the conversations that are going on to create peace again.</t>
-  </si>
-  <si>
-    <t>2026 is a year where we will continue the momentum that we have. There is no doubt that the potential of this brand in this attractive market is to continue to grow a couple of billions every year. To do that on a consistent basis, we need to keep developing our people and keep working on the way we execute. Not only in front of the consumer, where we are very successful already. But also in the way we work. Just like athletes, we will continue to work hard on us, we will continue to adapt our processes to the changing environment so that we become an even better company and keep building an even stronger platform for the future.</t>
-  </si>
-  <si>
-    <t>Talking about the future, what are your plans and goals for adidas in the coming years?</t>
-  </si>
-  <si>
-    <t>I believe the next couple of years should show that adidas can take market leadership in a lot more markets. I think that we will continue to outgrow the industry and take more market share, utilizing the strength of our brand, our resources, our authenticity, our innovation, and our creativity. And to do that, we need to be dedicated to our consumers and attract, develop, and keep the best people. Because I think in this world where we talk a lot about AI and the tools that can make us better, we are still a people business. We should never forget that the athlete is a person, the consumer is a person, and the employee is a person. adidas is a great company to work with and to work for, and we are obsessed about fulfilling the needs of consumers and athletes.</t>
-  </si>
-  <si>
-    <t>Last question: What are your personal goals for 2026 and beyond?</t>
-  </si>
-  <si>
-    <t>I enjoy what I do, also doing a lot of sports. I have a lot of energy for this great job, a lot of passion for this fantastic brand, and I feel extremely privileged in what I do. So, my goal really is just to continue the great journey we are on, give this brand what it deserves, and get this company to where it belongs.</t>
-  </si>
-  <si>
-    <t>DEU25A01-00</t>
-  </si>
-  <si>
-    <t>DEU25A01-01</t>
-  </si>
-  <si>
-    <t>DEU25A02-00</t>
-  </si>
-  <si>
-    <t>DEU25A02-01</t>
-  </si>
-  <si>
-    <t>DEU25A03-00</t>
-  </si>
-  <si>
-    <t>DEU25A03-01</t>
-  </si>
-  <si>
-    <t>DEU25A04-00</t>
-  </si>
-  <si>
-    <t>DEU25A04-01</t>
-  </si>
-  <si>
-    <t>DEU25A05-00</t>
-  </si>
-  <si>
-    <t>DEU25A05-01</t>
-  </si>
-  <si>
-    <t>DEU25A06-00</t>
-  </si>
-  <si>
-    <t>DEU25A07-00</t>
-  </si>
-  <si>
-    <t>DEU25A07-01</t>
-  </si>
-  <si>
-    <t>DEU25A08-00</t>
-  </si>
-  <si>
-    <t>DEU25A08-01</t>
-  </si>
-  <si>
-    <t>DEU25A09-00</t>
-  </si>
-  <si>
-    <t>DEU25A09-01</t>
-  </si>
-  <si>
-    <t>DEU25A10-00</t>
-  </si>
-  <si>
-    <t>DEU25A10-01</t>
-  </si>
-  <si>
-    <t>DEU25A11-00</t>
-  </si>
-  <si>
-    <t>DEU25A11-01</t>
-  </si>
-  <si>
-    <t>DEU25A12-00</t>
-  </si>
-  <si>
-    <t>DEU25A12-01</t>
-  </si>
-  <si>
-    <t>DEU25A13-00</t>
-  </si>
-  <si>
-    <t>DEU25A13-01</t>
-  </si>
-  <si>
-    <t>DEU25A14-00</t>
-  </si>
-  <si>
-    <t>DEU25A15-00</t>
-  </si>
-  <si>
-    <t>DEU25A15-01</t>
-  </si>
-  <si>
-    <t>DEU25A16-00</t>
-  </si>
-  <si>
-    <t>DEU25A16-01</t>
-  </si>
-  <si>
-    <t>DEU25A17-00</t>
-  </si>
-  <si>
-    <t>DEU25A17-01</t>
-  </si>
-  <si>
-    <t>DEU25A18-00</t>
-  </si>
-  <si>
-    <t>DEU25A18-01</t>
-  </si>
-  <si>
-    <t>DEU25A19-00</t>
-  </si>
-  <si>
-    <t>DEU25A19-01</t>
-  </si>
-  <si>
-    <t>quore</t>
-  </si>
-  <si>
-    <t>Source_type</t>
-  </si>
-  <si>
-    <t>annual_report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Souce_type </t>
-  </si>
-  <si>
-    <t xml:space="preserve">annual_report </t>
-  </si>
-  <si>
-    <t>Communicator_name</t>
-  </si>
-  <si>
-    <t>Communicator_role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ceo </t>
-  </si>
-  <si>
-    <t>ceo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">interview </t>
-  </si>
-  <si>
-    <t>interview</t>
+    <t>Let me stay on the topic of sport because that’s what adidas is all about. Sport defines our past, present and future. I was so happy to see football returning to the stadiums – albeit with reduced capacities – at the UEFA EURO 2020 last summer. For the first time, the tournament was played across the entire continent, showcasing the unifying power of sport. For us, it was a particular pleasure to host the German national football team in the newly built ‘Home Ground’ at our headquarters in Herzogenaurach, Germany. Hosting a world-class team on our premises during such a major tournament was an industry first.</t>
+  </si>
+  <si>
+    <t>I look into 2022 with optimism. We are well prepared to execute our strategic priorities diligently, our product line-up looks great, and we will impactfully demonstrate our brand attitude of ‘Impossible is Nothing’ throughout the entire year. Consequently, we expect currency-neutral net sales to grow at a rate between 12% and 14% and our gross margin is projected to increase to a level of between 51.5% and 52.0%. Driven by the strong sales growth and the gross margin improvement, we expect an operating margin of between 10.5% and 11.0%. We will grow the bottom line significantly faster than the top line. As a result, net income from continuing operations is anticipated to increase to a level of between € 1.8 billion and € 1.9 billion, making 2022 another successful year for adidas.</t>
+  </si>
+  <si>
+    <t>I can confidently say that 2021 was a much better year than 2020. On the back of successful vaccination campaigns around the globe, the worldwide economy started to recover. Sport returned to the global stage, with the UEFA EURO 2020 football tournament and the Tokyo 2020 Olympics finally taking place, creating huge excitement around the world. That said, the covid-19 pandemic continued to impact lives and businesses across the globe. At adidas, we delivered a set of strong results despite heavy disruptions in supply and demand, with currency-neutral sales up 16% to more than € 21 billion and a net income from continuing operations of € 1.492 billion – an improvement of more than € 1 billion compared to the previous year. In addition, welaunched our new 2025 strategy ‘Own the Game’ which will set us up for long-term success in this attractive industry.</t>
+  </si>
+  <si>
+    <t>Not surprisingly, our financial results were significantly impacted by the negative effects of the coronavirus pandemic. Revenues decreased 14% on a currency-neutral basis due to the widespread store closures and lower traffic once stores reopened. Revenues in Russia/CIS remained flat, while currency neutral sales were down in all other major market segments. We were able to achieve a gross margin level of 49.7%, limiting the decline to 2.3 percentage points through a disciplined sell-in in a very promotional industry environment. As a result of the revenue shortfall, the company’s operating margin decreased 7.5 percentage points to 3.8% and net income from continuing operations decreased 78% to € 429 million.</t>
   </si>
 </sst>
 </file>
@@ -1732,43 +1726,13 @@
   </cellStyles>
   <dxfs count="96">
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1840,6 +1804,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1853,6 +1823,12 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1924,6 +1900,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1937,6 +1919,12 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2008,6 +1996,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2033,156 +2027,156 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N33" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N33" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
   <autoFilter ref="A1:N33" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N33">
     <sortCondition ref="A1:A33"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="77"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="76"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="74"/>
-    <tableColumn id="13" xr3:uid="{C6623026-AD7C-D846-8292-B0329434638D}" name="Source_type" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="73"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="72"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="71"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="70"/>
-    <tableColumn id="14" xr3:uid="{E8AB6ED4-E2FE-6741-AEBB-DDB8B5191E85}" name="Communicator_role" dataDxfId="0"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="69"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="68"/>
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="72"/>
+    <tableColumn id="13" xr3:uid="{C6623026-AD7C-D846-8292-B0329434638D}" name="Source_type" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="69"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="68"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="67"/>
+    <tableColumn id="14" xr3:uid="{E8AB6ED4-E2FE-6741-AEBB-DDB8B5191E85}" name="Communicator_role" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N28" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N28" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:N28" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="63"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="62"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="60"/>
-    <tableColumn id="13" xr3:uid="{E3C8FDE1-7886-EE4B-B0E6-60EB3B43E8FB}" name="Source_type" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="58"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="57"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{907A3C32-C0C2-9146-9644-C2D7BBC7708B}" name="Communicator_role" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="55"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{E3C8FDE1-7886-EE4B-B0E6-60EB3B43E8FB}" name="Source_type" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{907A3C32-C0C2-9146-9644-C2D7BBC7708B}" name="Communicator_role" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:N45" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:N45" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="A1:N45" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="46"/>
-    <tableColumn id="13" xr3:uid="{5DCB13C6-DEDF-3349-960E-1B04CE217447}" name="Source_type" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="42"/>
-    <tableColumn id="14" xr3:uid="{CBF1719A-8645-5E43-AC81-A9877CFB6001}" name="Communicator_role" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="Communicator_name" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{5DCB13C6-DEDF-3349-960E-1B04CE217447}" name="Source_type" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{CBF1719A-8645-5E43-AC81-A9877CFB6001}" name="Communicator_role" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="Communicator_name" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:N41" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:N41" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="A1:N41" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{EBE99108-B696-314E-A6F0-B2F5F90A863B}" name="ID" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{5D56DC3C-B713-2740-963B-AFE8AEFCCDC5}" name="Text" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{9B2B6519-1CB7-7F49-BB9C-204F11C40D79}" name="Text_type" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{5BA923F9-441B-A649-8784-2B77025D0C03}" name="Leadership_context" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{9F6AE6B8-C490-2940-B971-430EDC2EEE65}" name="Information_valence" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{81D2D30E-6E6D-D346-BFF1-6197B3EF3075}" name="Source_type" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="28"/>
-    <tableColumn id="14" xr3:uid="{55CD2F7D-2E4A-504F-B838-5F84F632C612}" name="Communicator_role" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="Communicator_name" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{EBE99108-B696-314E-A6F0-B2F5F90A863B}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{5D56DC3C-B713-2740-963B-AFE8AEFCCDC5}" name="Text" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{9B2B6519-1CB7-7F49-BB9C-204F11C40D79}" name="Text_type" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{5BA923F9-441B-A649-8784-2B77025D0C03}" name="Leadership_context" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{9F6AE6B8-C490-2940-B971-430EDC2EEE65}" name="Information_valence" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{81D2D30E-6E6D-D346-BFF1-6197B3EF3075}" name="Source_type" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{55CD2F7D-2E4A-504F-B838-5F84F632C612}" name="Communicator_role" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="Communicator_name" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:N42" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:N42" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
   <autoFilter ref="A1:N42" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{EA9096A1-A95F-934E-A69D-C3A15CE2958A}" name="Souce_type " dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{713FCDF7-7073-2F46-972B-3A77EC71FC40}" name="Communicator_role" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="Communicator_name" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="88"/>
+    <tableColumn id="13" xr3:uid="{EA9096A1-A95F-934E-A69D-C3A15CE2958A}" name="Souce_type " dataDxfId="87"/>
+    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="85"/>
+    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="84"/>
+    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="83"/>
+    <tableColumn id="14" xr3:uid="{713FCDF7-7073-2F46-972B-3A77EC71FC40}" name="Communicator_role" dataDxfId="82"/>
+    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="Communicator_name" dataDxfId="81"/>
+    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{98E4B810-202A-7E4C-B2C6-35D4404CA885}" name="Tableau134567" displayName="Tableau134567" ref="A1:N38" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{98E4B810-202A-7E4C-B2C6-35D4404CA885}" name="Tableau134567" displayName="Tableau134567" ref="A1:N38" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:N38" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{1EDFD034-5D27-3548-B9B9-99583075B81D}" name="ID" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{EFC7714F-3B4F-2845-B40A-79112F4B2DEE}" name="Text" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{5D67890B-5706-D740-BEC3-312FE72ADCFA}" name="Text_type" dataDxfId="91"/>
-    <tableColumn id="4" xr3:uid="{E9A847B5-7204-E54B-A14E-1A948434EC56}" name="Leadership_context" dataDxfId="90"/>
-    <tableColumn id="5" xr3:uid="{BD19C5B7-6C1E-9E43-82A8-7B117D5E0919}" name="Information_valence" dataDxfId="89"/>
-    <tableColumn id="6" xr3:uid="{066F6E4C-E842-4E43-A4B5-EF5133865DBD}" name="Communication_type" dataDxfId="88"/>
-    <tableColumn id="13" xr3:uid="{E4C657F2-83E9-C44A-9CCD-B156558CD32C}" name="Source_type" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{3D9145EE-B2AE-EA43-B6FF-544CF963E633}" name="Company" dataDxfId="87"/>
-    <tableColumn id="8" xr3:uid="{645C94BF-8E35-754B-B12E-328B4734CE50}" name="Country" dataDxfId="86"/>
-    <tableColumn id="9" xr3:uid="{8EF94B9F-4FD1-7A4E-97D7-9DA2D47E3DD5}" name="Year" dataDxfId="85"/>
-    <tableColumn id="10" xr3:uid="{CFE7CD80-3AA1-9041-8B91-270DDA32612B}" name="Covid" dataDxfId="84"/>
-    <tableColumn id="14" xr3:uid="{8CDA9040-3E39-6C4B-AE88-198675C6F1F4}" name="Communicator_role" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{77CD3889-4929-7348-B4F3-E407474AFD4D}" name="Communicator_name" dataDxfId="83"/>
-    <tableColumn id="12" xr3:uid="{276FB6D5-C797-B046-B256-4A051057EA9E}" name="Comment" dataDxfId="82"/>
+    <tableColumn id="1" xr3:uid="{1EDFD034-5D27-3548-B9B9-99583075B81D}" name="ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{EFC7714F-3B4F-2845-B40A-79112F4B2DEE}" name="Text" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{5D67890B-5706-D740-BEC3-312FE72ADCFA}" name="Text_type" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{E9A847B5-7204-E54B-A14E-1A948434EC56}" name="Leadership_context" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{BD19C5B7-6C1E-9E43-82A8-7B117D5E0919}" name="Information_valence" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{066F6E4C-E842-4E43-A4B5-EF5133865DBD}" name="Communication_type" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{E4C657F2-83E9-C44A-9CCD-B156558CD32C}" name="Source_type" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{3D9145EE-B2AE-EA43-B6FF-544CF963E633}" name="Company" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{645C94BF-8E35-754B-B12E-328B4734CE50}" name="Country" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{8EF94B9F-4FD1-7A4E-97D7-9DA2D47E3DD5}" name="Year" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{CFE7CD80-3AA1-9041-8B91-270DDA32612B}" name="Covid" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{8CDA9040-3E39-6C4B-AE88-198675C6F1F4}" name="Communicator_role" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{77CD3889-4929-7348-B4F3-E407474AFD4D}" name="Communicator_name" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{276FB6D5-C797-B046-B256-4A051057EA9E}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2509,7 +2503,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="90.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
@@ -2539,7 +2533,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -2554,10 +2548,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -2565,7 +2559,7 @@
     </row>
     <row r="2" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>21</v>
@@ -2583,7 +2577,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -2598,27 +2592,27 @@
         <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>23</v>
@@ -2627,7 +2621,7 @@
         <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -2642,27 +2636,27 @@
         <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>23</v>
@@ -2671,7 +2665,7 @@
         <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -2686,36 +2680,36 @@
         <v>16</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -2730,36 +2724,36 @@
         <v>16</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -2774,27 +2768,27 @@
         <v>16</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>23</v>
@@ -2803,7 +2797,7 @@
         <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -2818,27 +2812,27 @@
         <v>16</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>23</v>
@@ -2847,7 +2841,7 @@
         <v>25</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -2862,27 +2856,27 @@
         <v>16</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>23</v>
@@ -2891,7 +2885,7 @@
         <v>25</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -2906,36 +2900,36 @@
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -2950,27 +2944,27 @@
         <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>23</v>
@@ -2979,7 +2973,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -2994,36 +2988,36 @@
         <v>16</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="141" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>520</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -3038,27 +3032,27 @@
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>23</v>
@@ -3067,7 +3061,7 @@
         <v>25</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -3082,24 +3076,24 @@
         <v>16</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>22</v>
@@ -3111,7 +3105,7 @@
         <v>25</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -3126,36 +3120,36 @@
         <v>16</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -3170,27 +3164,27 @@
         <v>16</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="157" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>23</v>
@@ -3199,7 +3193,7 @@
         <v>25</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -3214,36 +3208,36 @@
         <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -3258,36 +3252,36 @@
         <v>16</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -3302,36 +3296,36 @@
         <v>16</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -3346,36 +3340,36 @@
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -3390,27 +3384,27 @@
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>23</v>
@@ -3419,7 +3413,7 @@
         <v>25</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -3434,36 +3428,36 @@
         <v>16</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="309" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -3478,36 +3472,36 @@
         <v>16</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -3522,27 +3516,27 @@
         <v>16</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>23</v>
@@ -3551,7 +3545,7 @@
         <v>25</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -3566,36 +3560,36 @@
         <v>16</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -3610,27 +3604,27 @@
         <v>16</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>23</v>
@@ -3639,7 +3633,7 @@
         <v>25</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -3654,36 +3648,36 @@
         <v>16</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -3698,36 +3692,36 @@
         <v>16</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="323" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -3742,36 +3736,36 @@
         <v>16</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>15</v>
@@ -3786,27 +3780,27 @@
         <v>16</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>23</v>
@@ -3815,7 +3809,7 @@
         <v>25</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>15</v>
@@ -3830,36 +3824,36 @@
         <v>16</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>15</v>
@@ -3874,27 +3868,27 @@
         <v>16</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>23</v>
@@ -3903,7 +3897,7 @@
         <v>25</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>15</v>
@@ -3918,36 +3912,36 @@
         <v>16</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>15</v>
@@ -3962,13 +3956,13 @@
         <v>16</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -3986,7 +3980,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="94.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
@@ -4016,7 +4010,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -4031,10 +4025,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -4042,10 +4036,10 @@
     </row>
     <row r="2" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>26</v>
@@ -4060,7 +4054,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -4075,7 +4069,7 @@
         <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>18</v>
@@ -4083,19 +4077,19 @@
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -4110,27 +4104,27 @@
         <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="221" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>112</v>
+        <v>519</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -4145,7 +4139,7 @@
         <v>16</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>18</v>
@@ -4153,19 +4147,19 @@
     </row>
     <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -4180,27 +4174,27 @@
         <v>16</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>113</v>
+        <v>517</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -4215,7 +4209,7 @@
         <v>16</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>18</v>
@@ -4223,19 +4217,19 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -4250,7 +4244,7 @@
         <v>16</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>18</v>
@@ -4258,19 +4252,19 @@
     </row>
     <row r="8" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -4285,7 +4279,7 @@
         <v>16</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>18</v>
@@ -4293,19 +4287,19 @@
     </row>
     <row r="9" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -4320,7 +4314,7 @@
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>18</v>
@@ -4328,19 +4322,19 @@
     </row>
     <row r="10" spans="1:14" ht="221" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -4355,7 +4349,7 @@
         <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>18</v>
@@ -4363,19 +4357,19 @@
     </row>
     <row r="11" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -4390,7 +4384,7 @@
         <v>16</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>18</v>
@@ -4398,19 +4392,19 @@
     </row>
     <row r="12" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -4425,7 +4419,7 @@
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>18</v>
@@ -4433,19 +4427,19 @@
     </row>
     <row r="13" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -4460,7 +4454,7 @@
         <v>16</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>18</v>
@@ -4468,19 +4462,19 @@
     </row>
     <row r="14" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -4495,7 +4489,7 @@
         <v>16</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>18</v>
@@ -4503,19 +4497,19 @@
     </row>
     <row r="15" spans="1:14" ht="221" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -4530,7 +4524,7 @@
         <v>16</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>18</v>
@@ -4538,19 +4532,19 @@
     </row>
     <row r="16" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -4565,7 +4559,7 @@
         <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>18</v>
@@ -4573,19 +4567,19 @@
     </row>
     <row r="17" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -4600,7 +4594,7 @@
         <v>16</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>18</v>
@@ -4608,19 +4602,19 @@
     </row>
     <row r="18" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -4635,7 +4629,7 @@
         <v>16</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>18</v>
@@ -4643,19 +4637,19 @@
     </row>
     <row r="19" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -4670,7 +4664,7 @@
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>18</v>
@@ -4678,19 +4672,19 @@
     </row>
     <row r="20" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -4705,7 +4699,7 @@
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>18</v>
@@ -4713,19 +4707,19 @@
     </row>
     <row r="21" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -4740,7 +4734,7 @@
         <v>16</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>18</v>
@@ -4748,19 +4742,19 @@
     </row>
     <row r="22" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -4775,7 +4769,7 @@
         <v>16</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>18</v>
@@ -4783,19 +4777,19 @@
     </row>
     <row r="23" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -4810,7 +4804,7 @@
         <v>16</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>18</v>
@@ -4818,19 +4812,19 @@
     </row>
     <row r="24" spans="1:13" ht="238" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -4845,7 +4839,7 @@
         <v>16</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>18</v>
@@ -4853,19 +4847,19 @@
     </row>
     <row r="25" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -4880,27 +4874,27 @@
         <v>16</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="204" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>124</v>
+        <v>518</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -4915,7 +4909,7 @@
         <v>16</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>18</v>
@@ -4923,19 +4917,19 @@
     </row>
     <row r="27" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -4950,7 +4944,7 @@
         <v>16</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>18</v>
@@ -4958,19 +4952,19 @@
     </row>
     <row r="28" spans="1:13" ht="187" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -4985,7 +4979,7 @@
         <v>16</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>18</v>
@@ -5006,7 +5000,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="99" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
@@ -5036,7 +5030,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -5051,10 +5045,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -5062,19 +5056,19 @@
     </row>
     <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -5089,27 +5083,27 @@
         <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -5124,27 +5118,27 @@
         <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -5159,27 +5153,27 @@
         <v>16</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -5194,27 +5188,27 @@
         <v>16</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -5229,27 +5223,27 @@
         <v>16</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -5264,27 +5258,27 @@
         <v>16</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -5299,27 +5293,27 @@
         <v>16</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -5334,27 +5328,27 @@
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -5369,27 +5363,27 @@
         <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -5404,27 +5398,27 @@
         <v>16</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -5439,27 +5433,27 @@
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -5474,27 +5468,27 @@
         <v>16</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -5509,27 +5503,27 @@
         <v>16</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -5544,27 +5538,27 @@
         <v>16</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -5579,27 +5573,27 @@
         <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -5614,27 +5608,27 @@
         <v>16</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -5649,27 +5643,27 @@
         <v>16</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -5684,27 +5678,27 @@
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -5719,27 +5713,27 @@
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -5754,27 +5748,27 @@
         <v>16</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -5789,27 +5783,27 @@
         <v>16</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -5824,27 +5818,27 @@
         <v>16</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -5859,27 +5853,27 @@
         <v>16</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -5894,27 +5888,27 @@
         <v>16</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -5929,27 +5923,27 @@
         <v>16</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -5964,27 +5958,27 @@
         <v>16</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -5999,27 +5993,27 @@
         <v>16</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>15</v>
@@ -6034,27 +6028,27 @@
         <v>16</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>15</v>
@@ -6069,27 +6063,27 @@
         <v>16</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>15</v>
@@ -6104,27 +6098,27 @@
         <v>16</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>15</v>
@@ -6139,27 +6133,27 @@
         <v>16</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>15</v>
@@ -6174,27 +6168,27 @@
         <v>16</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>15</v>
@@ -6209,27 +6203,27 @@
         <v>16</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>15</v>
@@ -6244,27 +6238,27 @@
         <v>16</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>15</v>
@@ -6279,27 +6273,27 @@
         <v>16</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>15</v>
@@ -6314,27 +6308,27 @@
         <v>16</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>15</v>
@@ -6349,27 +6343,27 @@
         <v>16</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>15</v>
@@ -6384,27 +6378,27 @@
         <v>16</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>15</v>
@@ -6419,27 +6413,27 @@
         <v>16</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="F41" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>15</v>
@@ -6454,27 +6448,27 @@
         <v>16</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>15</v>
@@ -6489,27 +6483,27 @@
         <v>16</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>15</v>
@@ -6524,27 +6518,27 @@
         <v>16</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>15</v>
@@ -6559,27 +6553,27 @@
         <v>16</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>15</v>
@@ -6594,10 +6588,10 @@
         <v>16</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -6615,7 +6609,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="89.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
@@ -6646,7 +6640,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -6661,10 +6655,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -6672,19 +6666,19 @@
     </row>
     <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -6699,27 +6693,27 @@
         <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -6734,27 +6728,27 @@
         <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -6769,27 +6763,27 @@
         <v>16</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -6804,27 +6798,27 @@
         <v>16</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -6839,27 +6833,27 @@
         <v>16</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="204" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -6874,27 +6868,27 @@
         <v>16</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -6909,27 +6903,27 @@
         <v>16</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -6944,27 +6938,27 @@
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="289" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -6979,27 +6973,27 @@
         <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -7014,27 +7008,27 @@
         <v>16</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -7049,27 +7043,27 @@
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -7084,27 +7078,27 @@
         <v>16</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -7119,27 +7113,27 @@
         <v>16</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -7154,27 +7148,27 @@
         <v>16</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -7189,27 +7183,27 @@
         <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -7224,27 +7218,27 @@
         <v>16</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="187" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -7259,27 +7253,27 @@
         <v>16</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -7294,27 +7288,27 @@
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -7329,27 +7323,27 @@
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -7364,27 +7358,27 @@
         <v>16</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="221" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -7399,27 +7393,27 @@
         <v>16</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -7434,27 +7428,27 @@
         <v>16</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -7469,27 +7463,27 @@
         <v>16</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -7504,27 +7498,27 @@
         <v>16</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -7539,27 +7533,27 @@
         <v>16</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -7574,27 +7568,27 @@
         <v>16</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -7609,27 +7603,27 @@
         <v>16</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>15</v>
@@ -7644,27 +7638,27 @@
         <v>16</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>15</v>
@@ -7679,27 +7673,27 @@
         <v>16</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>15</v>
@@ -7714,27 +7708,27 @@
         <v>16</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>15</v>
@@ -7749,27 +7743,27 @@
         <v>16</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>15</v>
@@ -7784,27 +7778,27 @@
         <v>16</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="204" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>15</v>
@@ -7819,27 +7813,27 @@
         <v>16</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>15</v>
@@ -7854,27 +7848,27 @@
         <v>16</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="255" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>15</v>
@@ -7889,27 +7883,27 @@
         <v>16</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>15</v>
@@ -7924,27 +7918,27 @@
         <v>16</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>15</v>
@@ -7959,27 +7953,27 @@
         <v>16</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>15</v>
@@ -7994,27 +7988,27 @@
         <v>16</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>15</v>
@@ -8029,27 +8023,27 @@
         <v>16</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>15</v>
@@ -8064,10 +8058,10 @@
         <v>16</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -8085,7 +8079,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="66.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
@@ -8116,7 +8110,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -8131,10 +8125,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -8142,19 +8136,19 @@
     </row>
     <row r="2" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -8166,30 +8160,30 @@
         <v>2024</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -8201,30 +8195,30 @@
         <v>2024</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -8236,30 +8230,30 @@
         <v>2024</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -8271,30 +8265,30 @@
         <v>2024</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="221" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -8306,30 +8300,30 @@
         <v>2024</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -8341,30 +8335,30 @@
         <v>2024</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="255" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -8376,30 +8370,30 @@
         <v>2024</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -8411,30 +8405,30 @@
         <v>2024</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="289" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -8446,30 +8440,30 @@
         <v>2024</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -8481,30 +8475,30 @@
         <v>2024</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="204" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -8516,30 +8510,30 @@
         <v>2024</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -8551,30 +8545,30 @@
         <v>2024</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="221" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -8586,30 +8580,30 @@
         <v>2024</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -8621,30 +8615,30 @@
         <v>2024</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -8656,30 +8650,30 @@
         <v>2024</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -8691,30 +8685,30 @@
         <v>2024</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -8726,30 +8720,30 @@
         <v>2024</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -8761,30 +8755,30 @@
         <v>2024</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -8796,30 +8790,30 @@
         <v>2024</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="221" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -8831,30 +8825,30 @@
         <v>2024</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -8866,30 +8860,30 @@
         <v>2024</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -8901,30 +8895,30 @@
         <v>2024</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -8936,30 +8930,30 @@
         <v>2024</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -8971,30 +8965,30 @@
         <v>2024</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -9006,30 +9000,30 @@
         <v>2024</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="289" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -9041,30 +9035,30 @@
         <v>2024</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -9076,30 +9070,30 @@
         <v>2024</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>15</v>
@@ -9111,30 +9105,30 @@
         <v>2024</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="289" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>384</v>
+        <v>516</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>15</v>
@@ -9146,30 +9140,30 @@
         <v>2024</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>15</v>
@@ -9181,30 +9175,30 @@
         <v>2024</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>15</v>
@@ -9216,30 +9210,30 @@
         <v>2024</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>15</v>
@@ -9251,30 +9245,30 @@
         <v>2024</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>15</v>
@@ -9286,30 +9280,30 @@
         <v>2024</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>15</v>
@@ -9321,30 +9315,30 @@
         <v>2024</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>15</v>
@@ -9356,30 +9350,30 @@
         <v>2024</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>15</v>
@@ -9391,30 +9385,30 @@
         <v>2024</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>15</v>
@@ -9426,30 +9420,30 @@
         <v>2024</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>15</v>
@@ -9461,30 +9455,30 @@
         <v>2024</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>15</v>
@@ -9496,30 +9490,30 @@
         <v>2024</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>15</v>
@@ -9531,30 +9525,30 @@
         <v>2024</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>15</v>
@@ -9566,13 +9560,13 @@
         <v>2024</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -9590,7 +9584,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="102.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
@@ -9620,7 +9614,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -9635,10 +9629,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -9646,19 +9640,19 @@
     </row>
     <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -9670,30 +9664,30 @@
         <v>2025</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -9705,30 +9699,30 @@
         <v>2025</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -9740,30 +9734,30 @@
         <v>2025</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -9775,30 +9769,30 @@
         <v>2025</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="255" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -9810,30 +9804,30 @@
         <v>2025</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -9845,30 +9839,30 @@
         <v>2025</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -9880,30 +9874,30 @@
         <v>2025</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -9915,30 +9909,30 @@
         <v>2025</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="255" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -9950,30 +9944,30 @@
         <v>2025</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -9985,30 +9979,30 @@
         <v>2025</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="289" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -10020,30 +10014,30 @@
         <v>2025</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -10055,30 +10049,30 @@
         <v>2025</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -10090,30 +10084,30 @@
         <v>2025</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -10125,30 +10119,30 @@
         <v>2025</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -10160,30 +10154,30 @@
         <v>2025</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="187" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -10195,30 +10189,30 @@
         <v>2025</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -10230,30 +10224,30 @@
         <v>2025</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -10265,30 +10259,30 @@
         <v>2025</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -10300,30 +10294,30 @@
         <v>2025</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -10335,30 +10329,30 @@
         <v>2025</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -10370,30 +10364,30 @@
         <v>2025</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="187" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -10405,30 +10399,30 @@
         <v>2025</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -10440,30 +10434,30 @@
         <v>2025</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="356" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -10475,30 +10469,30 @@
         <v>2025</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -10510,30 +10504,30 @@
         <v>2025</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="255" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -10545,30 +10539,30 @@
         <v>2025</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -10580,30 +10574,30 @@
         <v>2025</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>15</v>
@@ -10615,30 +10609,30 @@
         <v>2025</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="187" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>15</v>
@@ -10650,30 +10644,30 @@
         <v>2025</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>15</v>
@@ -10685,30 +10679,30 @@
         <v>2025</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="238" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>15</v>
@@ -10720,30 +10714,30 @@
         <v>2025</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>15</v>
@@ -10755,30 +10749,30 @@
         <v>2025</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>15</v>
@@ -10790,30 +10784,30 @@
         <v>2025</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>15</v>
@@ -10825,30 +10819,30 @@
         <v>2025</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>15</v>
@@ -10860,30 +10854,30 @@
         <v>2025</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>15</v>
@@ -10895,30 +10889,30 @@
         <v>2025</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>15</v>
@@ -10930,13 +10924,13 @@
         <v>2025</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/adidas.xlsx
+++ b/data/input/adidas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB982AE-1552-9845-8822-89C00875CF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946E532A-0FFC-FF42-AF1C-D39F4EACC6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="600" windowWidth="27340" windowHeight="17400" activeTab="5" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="8100" yWindow="600" windowWidth="20700" windowHeight="17400" activeTab="1" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="515">
   <si>
     <t>ID</t>
   </si>
@@ -332,22 +332,7 @@
     <t>Expresses care and well wishes toward the recipients at the close of the communication.</t>
   </si>
   <si>
-    <t xml:space="preserve">2020 was anything but easy. The only way to get through such a year is by working together as a team. Therefore, I would like to extend my heartfelt thanks to our 62,000 adidas employees. They have demonstrated resilience and shown great commitment in these unprecedented times. </t>
-  </si>
-  <si>
     <t>Expresses appreciation for employees and recognizes their resilience and commitment during a challenging year.</t>
-  </si>
-  <si>
-    <t>And I would also like to say thank you to you, our shareholders, for the trust you have placed in us. We will continue to do everything we can to remain worthy of this trust.</t>
-  </si>
-  <si>
-    <t>I am confident of the attractive prospects the sporting goods industry will continue to present for adidas, especially given that many people have developed an increased appreciation of well-being. They want to stay fit and healthy through sports. At the same time, wearing sportswear is becoming more and more popular, in particular for people working from home. adidas will continue to benefit from these trends. As a global leader in our industry with a strong strategy in place, we are very well positioned for the years ahead.</t>
-  </si>
-  <si>
-    <t>Discusses favorable sporting-goods market trends and adidas’ expected positioning to benefit from changing consumer preferences.</t>
-  </si>
-  <si>
-    <t>Expresses appreciation to shareholders for their trust and commitment to maintaining it.</t>
   </si>
   <si>
     <t>DEU21A00-00</t>
@@ -516,12 +501,6 @@
     <t>DEU20A01-28</t>
   </si>
   <si>
-    <t>DEU20A01-29</t>
-  </si>
-  <si>
-    <t>DEU20A01-30</t>
-  </si>
-  <si>
     <t>DEU21A01-00</t>
   </si>
   <si>
@@ -1627,6 +1606,9 @@
   </si>
   <si>
     <t>Not surprisingly, our financial results were significantly impacted by the negative effects of the coronavirus pandemic. Revenues decreased 14% on a currency-neutral basis due to the widespread store closures and lower traffic once stores reopened. Revenues in Russia/CIS remained flat, while currency neutral sales were down in all other major market segments. We were able to achieve a gross margin level of 49.7%, limiting the decline to 2.3 percentage points through a disciplined sell-in in a very promotional industry environment. As a result of the revenue shortfall, the company’s operating margin decreased 7.5 percentage points to 3.8% and net income from continuing operations decreased 78% to € 429 million.</t>
+  </si>
+  <si>
+    <t>2020 was anything but easy. The only way to get through such a year is by working together as a team. Therefore, I would like to extend my heartfelt thanks to our 62,000 adidas employees. They have demonstrated resilience and shown great commitment in these unprecedented times. And I would also like to say thank you to you, our shareholders, for the trust you have placed in us. We will continue to do everything we can to remain worthy of this trust. I am confident of the attractive prospects the sporting goods industry will continue to present for adidas, especially given that many people have developed an increased appreciation of well-being. They want to stay fit and healthy through sports. At the same time, wearing sportswear is becoming more and more popular, in particular for people working from home. adidas will continue to benefit from these trends. As a global leader in our industry with a strong strategy in place, we are very well positioned for the years ahead.</t>
   </si>
 </sst>
 </file>
@@ -2027,10 +2009,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N33" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
-  <autoFilter ref="A1:N33" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N33">
-    <sortCondition ref="A1:A33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N31" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
+  <autoFilter ref="A1:N31" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N31">
+    <sortCondition ref="A1:A31"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="77"/>
@@ -2053,104 +2035,104 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N28" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N28" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
   <autoFilter ref="A1:N28" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="56"/>
-    <tableColumn id="13" xr3:uid="{E3C8FDE1-7886-EE4B-B0E6-60EB3B43E8FB}" name="Source_type" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="51"/>
-    <tableColumn id="14" xr3:uid="{907A3C32-C0C2-9146-9644-C2D7BBC7708B}" name="Communicator_role" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="88"/>
+    <tableColumn id="13" xr3:uid="{E3C8FDE1-7886-EE4B-B0E6-60EB3B43E8FB}" name="Source_type" dataDxfId="87"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="85"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="84"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="83"/>
+    <tableColumn id="14" xr3:uid="{907A3C32-C0C2-9146-9644-C2D7BBC7708B}" name="Communicator_role" dataDxfId="82"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="81"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:N45" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{26588558-D0CF-4F48-8207-1E2A5392AF8E}" name="Tableau134" displayName="Tableau134" ref="A1:N45" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:N45" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{5DCB13C6-DEDF-3349-960E-1B04CE217447}" name="Source_type" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="35"/>
-    <tableColumn id="14" xr3:uid="{CBF1719A-8645-5E43-AC81-A9877CFB6001}" name="Communicator_role" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="Communicator_name" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{04D3B6A3-AEC3-AE42-B147-A6ABBB5B6354}" name="ID" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{A08ABCF2-CA8B-A044-921C-1984A277415E}" name="Text" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{7601C852-E34B-BC47-BAF2-A92FE54D60CA}" name="Text_type" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{98541F64-80E1-3A48-9298-300E3F65D4B0}" name="Leadership_context" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{C7FB9E71-FFDF-C945-957D-B1FE0C569631}" name="Information_valence" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{CD0856A2-B204-324A-A2AB-D66D6063D1D8}" name="Communication_type" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{5DCB13C6-DEDF-3349-960E-1B04CE217447}" name="Source_type" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{FC6997A1-4BD5-8C46-81D4-7420C657AE65}" name="Company" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{08DAFEA7-C601-AB45-990E-646BA3CCE41C}" name="Country" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{5101C202-E584-F944-91E7-59E2256B8F43}" name="Year" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{C6DDA0CF-2324-4C49-9633-672B400C8CB9}" name="Covid" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{CBF1719A-8645-5E43-AC81-A9877CFB6001}" name="Communicator_role" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{57DA2786-5BB0-664B-91AF-88552FC594AF}" name="Communicator_name" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{E0B94C81-6FCD-464E-93CB-03CDB472FBC7}" name="Comment" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:N41" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7BE17E5B-825A-C640-9BF8-E0C1F2950D5A}" name="Tableau1345" displayName="Tableau1345" ref="A1:N41" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="A1:N41" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{EBE99108-B696-314E-A6F0-B2F5F90A863B}" name="ID" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{5D56DC3C-B713-2740-963B-AFE8AEFCCDC5}" name="Text" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{9B2B6519-1CB7-7F49-BB9C-204F11C40D79}" name="Text_type" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{5BA923F9-441B-A649-8784-2B77025D0C03}" name="Leadership_context" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{9F6AE6B8-C490-2940-B971-430EDC2EEE65}" name="Information_valence" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{81D2D30E-6E6D-D346-BFF1-6197B3EF3075}" name="Source_type" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{55CD2F7D-2E4A-504F-B838-5F84F632C612}" name="Communicator_role" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="Communicator_name" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{EBE99108-B696-314E-A6F0-B2F5F90A863B}" name="ID" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{5D56DC3C-B713-2740-963B-AFE8AEFCCDC5}" name="Text" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{9B2B6519-1CB7-7F49-BB9C-204F11C40D79}" name="Text_type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{5BA923F9-441B-A649-8784-2B77025D0C03}" name="Leadership_context" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{9F6AE6B8-C490-2940-B971-430EDC2EEE65}" name="Information_valence" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{183164AD-1F95-FA4F-BE6C-4D08FD20BBC2}" name="Communication_type" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{81D2D30E-6E6D-D346-BFF1-6197B3EF3075}" name="Source_type" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{B8136F0C-4262-C84A-B0AA-03BCE28F0ABF}" name="Company" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{122F01E4-2BB4-2A41-9D94-69C88758D82F}" name="Country" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{5DA32F4C-36CE-BC4B-8A74-E9D70EB409E6}" name="Year" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{7A5C3DD7-5BD3-304F-8FEC-936857C8FA9C}" name="Covid" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{55CD2F7D-2E4A-504F-B838-5F84F632C612}" name="Communicator_role" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{73D5EBD3-3B08-BE4E-A07E-3D71F957756A}" name="Communicator_name" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{20350EE8-7408-9945-ACD7-64833CAC8B87}" name="Comment" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:N42" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A52DC8ED-8AC4-F540-9CAD-282910FB623B}" name="Tableau13456" displayName="Tableau13456" ref="A1:N42" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="A1:N42" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="91"/>
-    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="90"/>
-    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="89"/>
-    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="88"/>
-    <tableColumn id="13" xr3:uid="{EA9096A1-A95F-934E-A69D-C3A15CE2958A}" name="Souce_type " dataDxfId="87"/>
-    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="86"/>
-    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="85"/>
-    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="84"/>
-    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="83"/>
-    <tableColumn id="14" xr3:uid="{713FCDF7-7073-2F46-972B-3A77EC71FC40}" name="Communicator_role" dataDxfId="82"/>
-    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="Communicator_name" dataDxfId="81"/>
-    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{D1670C9C-3BF8-E64C-8FDC-0556DDD12E29}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{47AEB82A-7FC0-8B41-BCCE-0A2CFB840D38}" name="Text" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{FFBCA903-1B47-D946-AA9F-EA7F17406713}" name="Text_type" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{FD845195-6741-C242-B8DA-A0FECBDA8F9B}" name="Leadership_context" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{91979307-6943-9C48-B440-30B70C2122E4}" name="Information_valence" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{B668CFB6-6C60-6B48-999F-393A0D1A5DC9}" name="Communication_type" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{EA9096A1-A95F-934E-A69D-C3A15CE2958A}" name="Souce_type " dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{C94DA90F-F077-9241-B9ED-4E8747E45894}" name="Company" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{14E8A229-F0FD-6848-8E85-BF0FBBC27017}" name="Country" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{20F9C2AC-A634-6F48-85CB-130605A883F0}" name="Year" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{F7C043D1-4814-2A41-B1A7-FBB5645E1179}" name="Covid" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{713FCDF7-7073-2F46-972B-3A77EC71FC40}" name="Communicator_role" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{C806B569-1E1C-4E4D-98B6-1EE4B2752BE2}" name="Communicator_name" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{FFE0B8B3-56E5-6E47-A6D4-B3AA651933DD}" name="Comment" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2499,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3826A9C-6C80-494E-9252-B920A5705A8F}">
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -2533,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -2548,10 +2530,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -2568,7 +2550,7 @@
         <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
@@ -2577,7 +2559,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -2592,7 +2574,7 @@
         <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>18</v>
@@ -2621,7 +2603,7 @@
         <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -2636,7 +2618,7 @@
         <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>18</v>
@@ -2645,7 +2627,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
@@ -2665,7 +2647,7 @@
         <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -2680,7 +2662,7 @@
         <v>16</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>18</v>
@@ -2709,7 +2691,7 @@
         <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -2724,7 +2706,7 @@
         <v>16</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>18</v>
@@ -2733,7 +2715,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>41</v>
       </c>
@@ -2753,7 +2735,7 @@
         <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -2768,7 +2750,7 @@
         <v>16</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>18</v>
@@ -2779,7 +2761,7 @@
     </row>
     <row r="7" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>20</v>
@@ -2797,7 +2779,7 @@
         <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -2812,7 +2794,7 @@
         <v>16</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>18</v>
@@ -2821,9 +2803,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>19</v>
@@ -2841,7 +2823,7 @@
         <v>25</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -2856,7 +2838,7 @@
         <v>16</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>18</v>
@@ -2865,9 +2847,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -2885,7 +2867,7 @@
         <v>25</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -2900,7 +2882,7 @@
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>18</v>
@@ -2911,7 +2893,7 @@
     </row>
     <row r="10" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>27</v>
@@ -2929,7 +2911,7 @@
         <v>25</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -2944,7 +2926,7 @@
         <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>18</v>
@@ -2953,9 +2935,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
@@ -2973,7 +2955,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -2988,7 +2970,7 @@
         <v>16</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>18</v>
@@ -2999,10 +2981,10 @@
     </row>
     <row r="12" spans="1:14" ht="141" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>53</v>
@@ -3017,7 +2999,7 @@
         <v>25</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -3032,7 +3014,7 @@
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>18</v>
@@ -3043,7 +3025,7 @@
     </row>
     <row r="13" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
@@ -3061,7 +3043,7 @@
         <v>25</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -3076,7 +3058,7 @@
         <v>16</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>18</v>
@@ -3085,9 +3067,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>42</v>
@@ -3105,7 +3087,7 @@
         <v>25</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -3120,7 +3102,7 @@
         <v>16</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>18</v>
@@ -3131,7 +3113,7 @@
     </row>
     <row r="15" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>30</v>
@@ -3149,7 +3131,7 @@
         <v>25</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -3164,7 +3146,7 @@
         <v>16</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>18</v>
@@ -3173,9 +3155,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="157" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
@@ -3193,7 +3175,7 @@
         <v>25</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -3208,7 +3190,7 @@
         <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>18</v>
@@ -3219,7 +3201,7 @@
     </row>
     <row r="17" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>31</v>
@@ -3237,7 +3219,7 @@
         <v>25</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -3252,7 +3234,7 @@
         <v>16</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>18</v>
@@ -3261,9 +3243,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>44</v>
@@ -3281,7 +3263,7 @@
         <v>25</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -3296,7 +3278,7 @@
         <v>16</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>18</v>
@@ -3305,9 +3287,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>45</v>
@@ -3325,7 +3307,7 @@
         <v>25</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -3340,7 +3322,7 @@
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>18</v>
@@ -3351,7 +3333,7 @@
     </row>
     <row r="20" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>32</v>
@@ -3369,7 +3351,7 @@
         <v>25</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -3384,7 +3366,7 @@
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>18</v>
@@ -3393,9 +3375,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>46</v>
@@ -3413,7 +3395,7 @@
         <v>25</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -3428,7 +3410,7 @@
         <v>16</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>18</v>
@@ -3437,9 +3419,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="309" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="221" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>50</v>
@@ -3457,7 +3439,7 @@
         <v>25</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -3472,7 +3454,7 @@
         <v>16</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>18</v>
@@ -3483,7 +3465,7 @@
     </row>
     <row r="23" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>55</v>
@@ -3501,7 +3483,7 @@
         <v>25</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -3516,7 +3498,7 @@
         <v>16</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>18</v>
@@ -3527,7 +3509,7 @@
     </row>
     <row r="24" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>33</v>
@@ -3545,7 +3527,7 @@
         <v>25</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -3560,7 +3542,7 @@
         <v>16</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>18</v>
@@ -3569,9 +3551,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="187" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>47</v>
@@ -3589,7 +3571,7 @@
         <v>25</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -3604,7 +3586,7 @@
         <v>16</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>18</v>
@@ -3613,9 +3595,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>48</v>
@@ -3633,7 +3615,7 @@
         <v>25</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -3648,7 +3630,7 @@
         <v>16</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>18</v>
@@ -3659,7 +3641,7 @@
     </row>
     <row r="27" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>34</v>
@@ -3677,7 +3659,7 @@
         <v>25</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -3692,7 +3674,7 @@
         <v>16</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>18</v>
@@ -3701,9 +3683,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="323" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="221" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>88</v>
@@ -3721,7 +3703,7 @@
         <v>25</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -3736,7 +3718,7 @@
         <v>16</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>18</v>
@@ -3747,7 +3729,7 @@
     </row>
     <row r="29" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>35</v>
@@ -3765,7 +3747,7 @@
         <v>25</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>15</v>
@@ -3780,7 +3762,7 @@
         <v>16</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>18</v>
@@ -3789,18 +3771,18 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>92</v>
+        <v>514</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>23</v>
@@ -3809,7 +3791,7 @@
         <v>25</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>15</v>
@@ -3824,27 +3806,27 @@
         <v>16</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>60</v>
@@ -3853,7 +3835,7 @@
         <v>25</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>15</v>
@@ -3868,100 +3850,12 @@
         <v>16</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="1">
-        <v>2021</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="1">
-        <v>2020</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N33" s="2" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4010,7 +3904,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -4025,10 +3919,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -4036,10 +3930,10 @@
     </row>
     <row r="2" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>26</v>
@@ -4054,7 +3948,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -4069,7 +3963,7 @@
         <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>18</v>
@@ -4077,19 +3971,19 @@
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -4104,7 +3998,7 @@
         <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>18</v>
@@ -4112,10 +4006,10 @@
     </row>
     <row r="4" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>53</v>
@@ -4124,7 +4018,7 @@
         <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -4139,7 +4033,7 @@
         <v>16</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>18</v>
@@ -4147,19 +4041,19 @@
     </row>
     <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -4174,7 +4068,7 @@
         <v>16</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>18</v>
@@ -4182,10 +4076,10 @@
     </row>
     <row r="6" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>53</v>
@@ -4194,7 +4088,7 @@
         <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -4209,7 +4103,7 @@
         <v>16</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>18</v>
@@ -4217,19 +4111,19 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -4244,18 +4138,18 @@
         <v>16</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>53</v>
@@ -4264,7 +4158,7 @@
         <v>25</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -4279,7 +4173,7 @@
         <v>16</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>18</v>
@@ -4287,19 +4181,19 @@
     </row>
     <row r="9" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -4314,18 +4208,18 @@
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="221" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>53</v>
@@ -4334,7 +4228,7 @@
         <v>25</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -4349,18 +4243,18 @@
         <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>53</v>
@@ -4369,7 +4263,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -4384,7 +4278,7 @@
         <v>16</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>18</v>
@@ -4392,19 +4286,19 @@
     </row>
     <row r="12" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -4419,18 +4313,18 @@
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>53</v>
@@ -4439,7 +4333,7 @@
         <v>25</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -4454,7 +4348,7 @@
         <v>16</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>18</v>
@@ -4462,19 +4356,19 @@
     </row>
     <row r="14" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -4489,18 +4383,18 @@
         <v>16</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="221" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>53</v>
@@ -4509,7 +4403,7 @@
         <v>25</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -4524,7 +4418,7 @@
         <v>16</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>18</v>
@@ -4532,19 +4426,19 @@
     </row>
     <row r="16" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -4559,18 +4453,18 @@
         <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>53</v>
@@ -4579,7 +4473,7 @@
         <v>25</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -4594,7 +4488,7 @@
         <v>16</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>18</v>
@@ -4602,19 +4496,19 @@
     </row>
     <row r="18" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -4629,18 +4523,18 @@
         <v>16</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>53</v>
@@ -4649,7 +4543,7 @@
         <v>25</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -4664,7 +4558,7 @@
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>18</v>
@@ -4672,10 +4566,10 @@
     </row>
     <row r="20" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>53</v>
@@ -4684,7 +4578,7 @@
         <v>25</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -4699,7 +4593,7 @@
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>18</v>
@@ -4707,19 +4601,19 @@
     </row>
     <row r="21" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -4734,18 +4628,18 @@
         <v>16</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>53</v>
@@ -4754,7 +4648,7 @@
         <v>25</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -4769,7 +4663,7 @@
         <v>16</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>18</v>
@@ -4777,19 +4671,19 @@
     </row>
     <row r="23" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -4804,18 +4698,18 @@
         <v>16</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="238" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>53</v>
@@ -4824,7 +4718,7 @@
         <v>25</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -4839,7 +4733,7 @@
         <v>16</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>18</v>
@@ -4847,19 +4741,19 @@
     </row>
     <row r="25" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -4874,7 +4768,7 @@
         <v>16</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>18</v>
@@ -4882,10 +4776,10 @@
     </row>
     <row r="26" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>53</v>
@@ -4894,7 +4788,7 @@
         <v>25</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -4909,7 +4803,7 @@
         <v>16</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>18</v>
@@ -4917,19 +4811,19 @@
     </row>
     <row r="27" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -4944,18 +4838,18 @@
         <v>16</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="187" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>53</v>
@@ -4964,7 +4858,7 @@
         <v>25</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -4979,7 +4873,7 @@
         <v>16</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>18</v>
@@ -5030,7 +4924,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -5045,10 +4939,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -5056,19 +4950,19 @@
     </row>
     <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -5083,27 +4977,27 @@
         <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -5118,27 +5012,27 @@
         <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -5153,27 +5047,27 @@
         <v>16</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -5188,27 +5082,27 @@
         <v>16</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -5223,27 +5117,27 @@
         <v>16</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M6" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>188</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -5258,27 +5152,27 @@
         <v>16</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -5293,27 +5187,27 @@
         <v>16</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -5328,27 +5222,27 @@
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -5363,27 +5257,27 @@
         <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -5398,27 +5292,27 @@
         <v>16</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -5433,27 +5327,27 @@
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -5468,27 +5362,27 @@
         <v>16</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -5503,27 +5397,27 @@
         <v>16</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -5538,27 +5432,27 @@
         <v>16</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -5573,27 +5467,27 @@
         <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -5608,27 +5502,27 @@
         <v>16</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -5643,27 +5537,27 @@
         <v>16</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -5678,27 +5572,27 @@
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -5713,27 +5607,27 @@
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -5748,27 +5642,27 @@
         <v>16</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -5783,27 +5677,27 @@
         <v>16</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -5818,27 +5712,27 @@
         <v>16</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -5853,27 +5747,27 @@
         <v>16</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -5888,27 +5782,27 @@
         <v>16</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -5923,27 +5817,27 @@
         <v>16</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -5958,27 +5852,27 @@
         <v>16</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -5993,27 +5887,27 @@
         <v>16</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>15</v>
@@ -6028,27 +5922,27 @@
         <v>16</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>15</v>
@@ -6063,27 +5957,27 @@
         <v>16</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>15</v>
@@ -6098,27 +5992,27 @@
         <v>16</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>15</v>
@@ -6133,27 +6027,27 @@
         <v>16</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>15</v>
@@ -6168,27 +6062,27 @@
         <v>16</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>15</v>
@@ -6203,27 +6097,27 @@
         <v>16</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>15</v>
@@ -6238,27 +6132,27 @@
         <v>16</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>15</v>
@@ -6273,27 +6167,27 @@
         <v>16</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="F37" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>15</v>
@@ -6308,27 +6202,27 @@
         <v>16</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>15</v>
@@ -6343,27 +6237,27 @@
         <v>16</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>15</v>
@@ -6378,27 +6272,27 @@
         <v>16</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>15</v>
@@ -6413,27 +6307,27 @@
         <v>16</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>15</v>
@@ -6448,27 +6342,27 @@
         <v>16</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>15</v>
@@ -6483,27 +6377,27 @@
         <v>16</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>15</v>
@@ -6518,27 +6412,27 @@
         <v>16</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>15</v>
@@ -6553,27 +6447,27 @@
         <v>16</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>15</v>
@@ -6588,10 +6482,10 @@
         <v>16</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -6640,7 +6534,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -6655,10 +6549,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -6666,19 +6560,19 @@
     </row>
     <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -6693,27 +6587,27 @@
         <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -6728,27 +6622,27 @@
         <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -6763,27 +6657,27 @@
         <v>16</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -6798,27 +6692,27 @@
         <v>16</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -6833,27 +6727,27 @@
         <v>16</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="204" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -6868,27 +6762,27 @@
         <v>16</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -6903,27 +6797,27 @@
         <v>16</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -6938,27 +6832,27 @@
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="289" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="204" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -6973,27 +6867,27 @@
         <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -7008,27 +6902,27 @@
         <v>16</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="187" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -7043,27 +6937,27 @@
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -7078,27 +6972,27 @@
         <v>16</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -7113,27 +7007,27 @@
         <v>16</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -7148,27 +7042,27 @@
         <v>16</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -7183,27 +7077,27 @@
         <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -7218,27 +7112,27 @@
         <v>16</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="187" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -7253,27 +7147,27 @@
         <v>16</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -7288,27 +7182,27 @@
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -7323,27 +7217,27 @@
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -7358,27 +7252,27 @@
         <v>16</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="221" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -7393,27 +7287,27 @@
         <v>16</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -7428,27 +7322,27 @@
         <v>16</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -7463,27 +7357,27 @@
         <v>16</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -7498,27 +7392,27 @@
         <v>16</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -7533,27 +7427,27 @@
         <v>16</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -7568,27 +7462,27 @@
         <v>16</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -7603,27 +7497,27 @@
         <v>16</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>15</v>
@@ -7638,27 +7532,27 @@
         <v>16</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>15</v>
@@ -7673,27 +7567,27 @@
         <v>16</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>15</v>
@@ -7708,27 +7602,27 @@
         <v>16</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>15</v>
@@ -7743,27 +7637,27 @@
         <v>16</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>15</v>
@@ -7778,27 +7672,27 @@
         <v>16</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="204" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>15</v>
@@ -7813,27 +7707,27 @@
         <v>16</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>15</v>
@@ -7848,27 +7742,27 @@
         <v>16</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="255" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>15</v>
@@ -7883,27 +7777,27 @@
         <v>16</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>15</v>
@@ -7918,27 +7812,27 @@
         <v>16</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>15</v>
@@ -7953,27 +7847,27 @@
         <v>16</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>15</v>
@@ -7988,27 +7882,27 @@
         <v>16</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>15</v>
@@ -8023,27 +7917,27 @@
         <v>16</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>15</v>
@@ -8058,10 +7952,10 @@
         <v>16</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -8110,7 +8004,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -8125,10 +8019,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -8136,19 +8030,19 @@
     </row>
     <row r="2" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -8160,30 +8054,30 @@
         <v>2024</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -8195,30 +8089,30 @@
         <v>2024</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -8230,30 +8124,30 @@
         <v>2024</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -8265,30 +8159,30 @@
         <v>2024</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="221" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="204" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -8300,30 +8194,30 @@
         <v>2024</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -8335,30 +8229,30 @@
         <v>2024</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="255" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -8370,30 +8264,30 @@
         <v>2024</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -8405,30 +8299,30 @@
         <v>2024</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="289" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -8440,30 +8334,30 @@
         <v>2024</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -8475,30 +8369,30 @@
         <v>2024</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="204" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -8510,30 +8404,30 @@
         <v>2024</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -8545,30 +8439,30 @@
         <v>2024</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="221" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -8580,30 +8474,30 @@
         <v>2024</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -8615,30 +8509,30 @@
         <v>2024</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -8650,30 +8544,30 @@
         <v>2024</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -8685,30 +8579,30 @@
         <v>2024</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -8720,30 +8614,30 @@
         <v>2024</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -8755,30 +8649,30 @@
         <v>2024</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -8790,30 +8684,30 @@
         <v>2024</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="221" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="204" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -8825,30 +8719,30 @@
         <v>2024</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -8860,30 +8754,30 @@
         <v>2024</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -8895,30 +8789,30 @@
         <v>2024</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -8930,30 +8824,30 @@
         <v>2024</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -8965,30 +8859,30 @@
         <v>2024</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -9000,30 +8894,30 @@
         <v>2024</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="289" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="272" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -9035,30 +8929,30 @@
         <v>2024</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -9070,30 +8964,30 @@
         <v>2024</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>15</v>
@@ -9105,30 +8999,30 @@
         <v>2024</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="272" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>15</v>
@@ -9140,30 +9034,30 @@
         <v>2024</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>15</v>
@@ -9175,30 +9069,30 @@
         <v>2024</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>15</v>
@@ -9210,30 +9104,30 @@
         <v>2024</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>15</v>
@@ -9245,30 +9139,30 @@
         <v>2024</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>15</v>
@@ -9280,30 +9174,30 @@
         <v>2024</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>15</v>
@@ -9315,30 +9209,30 @@
         <v>2024</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>15</v>
@@ -9350,30 +9244,30 @@
         <v>2024</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>15</v>
@@ -9385,30 +9279,30 @@
         <v>2024</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>15</v>
@@ -9420,30 +9314,30 @@
         <v>2024</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>15</v>
@@ -9455,30 +9349,30 @@
         <v>2024</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>15</v>
@@ -9490,30 +9384,30 @@
         <v>2024</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>15</v>
@@ -9525,30 +9419,30 @@
         <v>2024</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>15</v>
@@ -9560,13 +9454,13 @@
         <v>2024</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -9614,7 +9508,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -9629,10 +9523,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -9640,19 +9534,19 @@
     </row>
     <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -9664,30 +9558,30 @@
         <v>2025</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -9699,30 +9593,30 @@
         <v>2025</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
@@ -9734,30 +9628,30 @@
         <v>2025</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
@@ -9769,30 +9663,30 @@
         <v>2025</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="255" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
@@ -9804,30 +9698,30 @@
         <v>2025</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>15</v>
@@ -9839,30 +9733,30 @@
         <v>2025</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>15</v>
@@ -9874,30 +9768,30 @@
         <v>2025</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -9909,30 +9803,30 @@
         <v>2025</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="255" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -9944,30 +9838,30 @@
         <v>2025</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>15</v>
@@ -9979,30 +9873,30 @@
         <v>2025</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="289" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>15</v>
@@ -10014,30 +9908,30 @@
         <v>2025</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>15</v>
@@ -10049,30 +9943,30 @@
         <v>2025</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>15</v>
@@ -10084,30 +9978,30 @@
         <v>2025</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>15</v>
@@ -10119,30 +10013,30 @@
         <v>2025</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>15</v>
@@ -10154,30 +10048,30 @@
         <v>2025</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="187" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>15</v>
@@ -10189,30 +10083,30 @@
         <v>2025</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>15</v>
@@ -10224,30 +10118,30 @@
         <v>2025</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>15</v>
@@ -10259,30 +10153,30 @@
         <v>2025</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>15</v>
@@ -10294,30 +10188,30 @@
         <v>2025</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>15</v>
@@ -10329,30 +10223,30 @@
         <v>2025</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>15</v>
@@ -10364,30 +10258,30 @@
         <v>2025</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="187" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>15</v>
@@ -10399,30 +10293,30 @@
         <v>2025</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>15</v>
@@ -10434,30 +10328,30 @@
         <v>2025</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="356" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="221" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>15</v>
@@ -10469,30 +10363,30 @@
         <v>2025</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>15</v>
@@ -10504,30 +10398,30 @@
         <v>2025</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="255" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>15</v>
@@ -10539,30 +10433,30 @@
         <v>2025</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>15</v>
@@ -10574,30 +10468,30 @@
         <v>2025</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>15</v>
@@ -10609,30 +10503,30 @@
         <v>2025</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="187" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>15</v>
@@ -10644,30 +10538,30 @@
         <v>2025</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>15</v>
@@ -10679,30 +10573,30 @@
         <v>2025</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="238" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>15</v>
@@ -10714,30 +10608,30 @@
         <v>2025</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>15</v>
@@ -10749,30 +10643,30 @@
         <v>2025</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>15</v>
@@ -10784,30 +10678,30 @@
         <v>2025</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>15</v>
@@ -10819,30 +10713,30 @@
         <v>2025</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>15</v>
@@ -10854,30 +10748,30 @@
         <v>2025</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>15</v>
@@ -10889,30 +10783,30 @@
         <v>2025</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>15</v>
@@ -10924,13 +10818,13 @@
         <v>2025</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/adidas.xlsx
+++ b/data/input/adidas.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11011"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF8CA64-0AE9-1A4A-A12B-F97934A5E196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415B7695-3A9E-D14E-9040-DBC5E01A0701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2643" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="481">
   <si>
     <t>ID</t>
   </si>
@@ -104,9 +104,6 @@
     <t>DEAR SHAREHOLDERS,</t>
   </si>
   <si>
-    <t xml:space="preserve">title </t>
-  </si>
-  <si>
     <t>STAKE</t>
   </si>
   <si>
@@ -119,9 +116,6 @@
     <t>body_text</t>
   </si>
   <si>
-    <t xml:space="preserve">PERF </t>
-  </si>
-  <si>
     <t>DEU20A01-02</t>
   </si>
   <si>
@@ -144,9 +138,6 @@
   </si>
   <si>
     <t>The health and safety of our employees is our top priority</t>
-  </si>
-  <si>
-    <t>heading</t>
   </si>
   <si>
     <t>PEOPLE</t>
@@ -159,9 +150,6 @@
 ─ Securing the well-being, health and safety of our own employees, and of our suppliers.
 ─ Steering the company successfully through this unprecedented crisis.
 I am proud to report that we achieved both.</t>
-  </si>
-  <si>
-    <t>body_text_list</t>
   </si>
   <si>
     <t>DEU20A01-06</t>
@@ -772,9 +760,6 @@
     <t>THE TRUST IN ADIDAS HAS STARTED TO COME BACK.</t>
   </si>
   <si>
-    <t xml:space="preserve">quote </t>
-  </si>
-  <si>
     <t xml:space="preserve">annual_report </t>
   </si>
   <si>
@@ -1340,9 +1325,6 @@
   </si>
   <si>
     <t>I AM VERY HAPPY AND PROUD OF WHAT OUR PEOPLE HAVE ACHIEVED</t>
-  </si>
-  <si>
-    <t>quore</t>
   </si>
   <si>
     <t>DEU25A07-00</t>
@@ -1548,6 +1530,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C017026D-7A16-AC4F-A79A-0D9ABE99C12C}" name="Tableau1" displayName="Tableau1" ref="A1:P220" totalsRowShown="0">
+  <autoFilter ref="A1:P220" xr:uid="{C017026D-7A16-AC4F-A79A-0D9ABE99C12C}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{B62BEF1E-3EE6-8F45-A71A-6C6AFDBC6AF6}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{8D627663-2AB4-374C-98B0-916E40C71952}" name="Text"/>
+    <tableColumn id="3" xr3:uid="{08093461-CC15-5540-A316-A950751D7C4C}" name="Text_type"/>
+    <tableColumn id="4" xr3:uid="{79F51273-F44D-D044-ABA5-2A4839E97735}" name="Leadership_context_human"/>
+    <tableColumn id="5" xr3:uid="{E155B594-A0C2-E246-B855-F9763CC1926C}" name="Information_valence_human"/>
+    <tableColumn id="6" xr3:uid="{678812AB-DE6E-5F42-85BA-78BCAC9960DC}" name="Communication_type"/>
+    <tableColumn id="7" xr3:uid="{F053472D-1726-2E45-B76E-E66634D51D47}" name="Source_type"/>
+    <tableColumn id="8" xr3:uid="{FE2C2D19-D642-4F45-A0E1-BBB54801999C}" name="Company"/>
+    <tableColumn id="9" xr3:uid="{3A4FBE10-CA9D-D34B-A897-3D33E7895D1C}" name="Country"/>
+    <tableColumn id="10" xr3:uid="{283793F1-42D0-214E-B5F0-986455D189A8}" name="Year"/>
+    <tableColumn id="11" xr3:uid="{6363D855-F1C2-A544-A5EC-B920EA27DBFD}" name="Covid"/>
+    <tableColumn id="12" xr3:uid="{7981647B-7905-4F4A-A51B-ABAA21DA75BC}" name="Communicator_role"/>
+    <tableColumn id="13" xr3:uid="{31F99462-892B-F44C-ACC2-09EC82E83E66}" name="Communicator_name"/>
+    <tableColumn id="14" xr3:uid="{EF1F23CA-82FA-2D42-B2C0-2DA864CCA522}" name="Comment"/>
+    <tableColumn id="15" xr3:uid="{04E9089C-179E-DD45-A73C-080C9840540A}" name="Coding_ambiguity"/>
+    <tableColumn id="16" xr3:uid="{6BBA7DF2-CC29-A246-9206-DD179356B60E}" name="Alternative_context"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1875,10 +1882,17 @@
   <dimension ref="A1:P220"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" customWidth="1"/>
-    <col min="15" max="24" width="13.5" customWidth="1"/>
+    <col min="1" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="24.5" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="17.33203125" customWidth="1"/>
+    <col min="16" max="16" width="18.5" customWidth="1"/>
+    <col min="17" max="24" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -1892,7 +1906,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1980,10 +1994,10 @@
         <v>28</v>
       </c>
       <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" t="s">
         <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -2015,16 +2029,16 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -2056,19 +2070,19 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
@@ -2097,19 +2111,19 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
         <v>20</v>
@@ -2138,16 +2152,16 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
         <v>41</v>
-      </c>
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
@@ -2179,16 +2193,16 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -2220,16 +2234,16 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
@@ -2261,19 +2275,19 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
@@ -2302,16 +2316,16 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
@@ -2343,19 +2357,19 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
         <v>20</v>
@@ -2384,16 +2398,16 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -2425,16 +2439,16 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -2466,19 +2480,19 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
@@ -2507,16 +2521,16 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
@@ -2548,19 +2562,19 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
@@ -2589,19 +2603,19 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
@@ -2630,19 +2644,19 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
@@ -2671,19 +2685,19 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
         <v>20</v>
@@ -2712,16 +2726,16 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -2753,19 +2767,19 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s">
         <v>20</v>
@@ -2794,19 +2808,19 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
         <v>20</v>
@@ -2835,16 +2849,16 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -2876,19 +2890,19 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
         <v>20</v>
@@ -2917,16 +2931,16 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
@@ -2958,19 +2972,19 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
         <v>20</v>
@@ -2999,19 +3013,19 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -3040,19 +3054,19 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
         <v>20</v>
@@ -3081,13 +3095,13 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -3122,19 +3136,19 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
         <v>20</v>
@@ -3163,16 +3177,16 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
@@ -3196,7 +3210,7 @@
         <v>24</v>
       </c>
       <c r="L32" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M32" t="s">
         <v>26</v>
@@ -3204,16 +3218,16 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
         <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -3237,7 +3251,7 @@
         <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M33" t="s">
         <v>26</v>
@@ -3245,16 +3259,16 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -3278,7 +3292,7 @@
         <v>24</v>
       </c>
       <c r="L34" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M34" t="s">
         <v>26</v>
@@ -3286,16 +3300,16 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
@@ -3319,7 +3333,7 @@
         <v>24</v>
       </c>
       <c r="L35" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M35" t="s">
         <v>26</v>
@@ -3327,16 +3341,16 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -3360,7 +3374,7 @@
         <v>24</v>
       </c>
       <c r="L36" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M36" t="s">
         <v>26</v>
@@ -3368,16 +3382,16 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -3401,7 +3415,7 @@
         <v>24</v>
       </c>
       <c r="L37" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M37" t="s">
         <v>26</v>
@@ -3409,16 +3423,16 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -3442,7 +3456,7 @@
         <v>24</v>
       </c>
       <c r="L38" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M38" t="s">
         <v>26</v>
@@ -3450,19 +3464,19 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
         <v>20</v>
@@ -3483,7 +3497,7 @@
         <v>24</v>
       </c>
       <c r="L39" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M39" t="s">
         <v>26</v>
@@ -3491,19 +3505,19 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F40" t="s">
         <v>20</v>
@@ -3524,7 +3538,7 @@
         <v>24</v>
       </c>
       <c r="L40" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M40" t="s">
         <v>26</v>
@@ -3532,16 +3546,16 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
@@ -3565,7 +3579,7 @@
         <v>24</v>
       </c>
       <c r="L41" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M41" t="s">
         <v>26</v>
@@ -3573,19 +3587,19 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F42" t="s">
         <v>20</v>
@@ -3606,7 +3620,7 @@
         <v>24</v>
       </c>
       <c r="L42" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M42" t="s">
         <v>26</v>
@@ -3614,16 +3628,16 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D43" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -3647,7 +3661,7 @@
         <v>24</v>
       </c>
       <c r="L43" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M43" t="s">
         <v>26</v>
@@ -3655,16 +3669,16 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
@@ -3688,7 +3702,7 @@
         <v>24</v>
       </c>
       <c r="L44" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M44" t="s">
         <v>26</v>
@@ -3696,16 +3710,16 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B45" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
@@ -3729,7 +3743,7 @@
         <v>24</v>
       </c>
       <c r="L45" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M45" t="s">
         <v>26</v>
@@ -3737,16 +3751,16 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B46" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D46" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
@@ -3770,7 +3784,7 @@
         <v>24</v>
       </c>
       <c r="L46" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M46" t="s">
         <v>26</v>
@@ -3778,16 +3792,16 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
@@ -3811,7 +3825,7 @@
         <v>24</v>
       </c>
       <c r="L47" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M47" t="s">
         <v>26</v>
@@ -3819,16 +3833,16 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B48" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D48" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E48" t="s">
         <v>19</v>
@@ -3852,7 +3866,7 @@
         <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M48" t="s">
         <v>26</v>
@@ -3860,16 +3874,16 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B49" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
@@ -3893,7 +3907,7 @@
         <v>24</v>
       </c>
       <c r="L49" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M49" t="s">
         <v>26</v>
@@ -3901,16 +3915,16 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
@@ -3934,7 +3948,7 @@
         <v>24</v>
       </c>
       <c r="L50" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M50" t="s">
         <v>26</v>
@@ -3942,19 +3956,19 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B51" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F51" t="s">
         <v>20</v>
@@ -3975,7 +3989,7 @@
         <v>24</v>
       </c>
       <c r="L51" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M51" t="s">
         <v>26</v>
@@ -3983,16 +3997,16 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
@@ -4016,7 +4030,7 @@
         <v>24</v>
       </c>
       <c r="L52" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M52" t="s">
         <v>26</v>
@@ -4024,16 +4038,16 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D53" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E53" t="s">
         <v>19</v>
@@ -4057,7 +4071,7 @@
         <v>24</v>
       </c>
       <c r="L53" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M53" t="s">
         <v>26</v>
@@ -4065,16 +4079,16 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E54" t="s">
         <v>19</v>
@@ -4098,7 +4112,7 @@
         <v>24</v>
       </c>
       <c r="L54" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M54" t="s">
         <v>26</v>
@@ -4106,16 +4120,16 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D55" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E55" t="s">
         <v>19</v>
@@ -4139,7 +4153,7 @@
         <v>24</v>
       </c>
       <c r="L55" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M55" t="s">
         <v>26</v>
@@ -4147,16 +4161,16 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
@@ -4180,7 +4194,7 @@
         <v>24</v>
       </c>
       <c r="L56" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M56" t="s">
         <v>26</v>
@@ -4188,19 +4202,19 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C57" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D57" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E57" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F57" t="s">
         <v>20</v>
@@ -4221,7 +4235,7 @@
         <v>24</v>
       </c>
       <c r="L57" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M57" t="s">
         <v>26</v>
@@ -4229,16 +4243,16 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
@@ -4262,7 +4276,7 @@
         <v>24</v>
       </c>
       <c r="L58" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M58" t="s">
         <v>26</v>
@@ -4270,22 +4284,22 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G59" t="s">
         <v>21</v>
@@ -4306,27 +4320,27 @@
         <v>25</v>
       </c>
       <c r="M59" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G60" t="s">
         <v>21</v>
@@ -4347,27 +4361,27 @@
         <v>25</v>
       </c>
       <c r="M60" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D61" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G61" t="s">
         <v>21</v>
@@ -4388,27 +4402,27 @@
         <v>25</v>
       </c>
       <c r="M61" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B62" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C62" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D62" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E62" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F62" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G62" t="s">
         <v>21</v>
@@ -4429,27 +4443,27 @@
         <v>25</v>
       </c>
       <c r="M62" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C63" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D63" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G63" t="s">
         <v>21</v>
@@ -4470,27 +4484,27 @@
         <v>25</v>
       </c>
       <c r="M63" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B64" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C64" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D64" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F64" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G64" t="s">
         <v>21</v>
@@ -4511,27 +4525,27 @@
         <v>25</v>
       </c>
       <c r="M64" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B65" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C65" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D65" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G65" t="s">
         <v>21</v>
@@ -4552,27 +4566,27 @@
         <v>25</v>
       </c>
       <c r="M65" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B66" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C66" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D66" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E66" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F66" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G66" t="s">
         <v>21</v>
@@ -4593,27 +4607,27 @@
         <v>25</v>
       </c>
       <c r="M66" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B67" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C67" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D67" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E67" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F67" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G67" t="s">
         <v>21</v>
@@ -4634,27 +4648,27 @@
         <v>25</v>
       </c>
       <c r="M67" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B68" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C68" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D68" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G68" t="s">
         <v>21</v>
@@ -4675,27 +4689,27 @@
         <v>25</v>
       </c>
       <c r="M68" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B69" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C69" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E69" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F69" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G69" t="s">
         <v>21</v>
@@ -4716,27 +4730,27 @@
         <v>25</v>
       </c>
       <c r="M69" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B70" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C70" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D70" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F70" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G70" t="s">
         <v>21</v>
@@ -4757,27 +4771,27 @@
         <v>25</v>
       </c>
       <c r="M70" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B71" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C71" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E71" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F71" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G71" t="s">
         <v>21</v>
@@ -4798,27 +4812,27 @@
         <v>25</v>
       </c>
       <c r="M71" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B72" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C72" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D72" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E72" t="s">
         <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G72" t="s">
         <v>21</v>
@@ -4839,27 +4853,27 @@
         <v>25</v>
       </c>
       <c r="M72" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B73" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C73" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D73" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E73" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F73" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G73" t="s">
         <v>21</v>
@@ -4880,18 +4894,18 @@
         <v>25</v>
       </c>
       <c r="M73" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B74" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C74" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -4900,7 +4914,7 @@
         <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G74" t="s">
         <v>21</v>
@@ -4921,27 +4935,27 @@
         <v>25</v>
       </c>
       <c r="M74" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B75" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C75" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F75" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G75" t="s">
         <v>21</v>
@@ -4962,27 +4976,27 @@
         <v>25</v>
       </c>
       <c r="M75" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B76" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C76" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D76" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E76" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F76" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G76" t="s">
         <v>21</v>
@@ -5003,27 +5017,27 @@
         <v>25</v>
       </c>
       <c r="M76" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B77" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C77" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
       </c>
       <c r="E77" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F77" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G77" t="s">
         <v>21</v>
@@ -5044,27 +5058,27 @@
         <v>25</v>
       </c>
       <c r="M77" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B78" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C78" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D78" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G78" t="s">
         <v>21</v>
@@ -5085,27 +5099,27 @@
         <v>25</v>
       </c>
       <c r="M78" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B79" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C79" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D79" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G79" t="s">
         <v>21</v>
@@ -5126,27 +5140,27 @@
         <v>25</v>
       </c>
       <c r="M79" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B80" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C80" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D80" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E80" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F80" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G80" t="s">
         <v>21</v>
@@ -5167,27 +5181,27 @@
         <v>25</v>
       </c>
       <c r="M80" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B81" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C81" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D81" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G81" t="s">
         <v>21</v>
@@ -5208,27 +5222,27 @@
         <v>25</v>
       </c>
       <c r="M81" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B82" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C82" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D82" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E82" t="s">
         <v>19</v>
       </c>
       <c r="F82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G82" t="s">
         <v>21</v>
@@ -5249,27 +5263,27 @@
         <v>25</v>
       </c>
       <c r="M82" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B83" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C83" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D83" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E83" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F83" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G83" t="s">
         <v>21</v>
@@ -5290,27 +5304,27 @@
         <v>25</v>
       </c>
       <c r="M83" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B84" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C84" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F84" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G84" t="s">
         <v>21</v>
@@ -5331,27 +5345,27 @@
         <v>25</v>
       </c>
       <c r="M84" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B85" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C85" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D85" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E85" t="s">
         <v>19</v>
       </c>
       <c r="F85" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G85" t="s">
         <v>21</v>
@@ -5372,27 +5386,27 @@
         <v>25</v>
       </c>
       <c r="M85" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B86" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C86" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D86" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G86" t="s">
         <v>21</v>
@@ -5413,27 +5427,27 @@
         <v>25</v>
       </c>
       <c r="M86" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B87" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C87" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D87" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E87" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F87" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G87" t="s">
         <v>21</v>
@@ -5454,27 +5468,27 @@
         <v>25</v>
       </c>
       <c r="M87" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B88" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C88" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D88" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E88" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F88" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G88" t="s">
         <v>21</v>
@@ -5495,18 +5509,18 @@
         <v>25</v>
       </c>
       <c r="M88" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B89" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C89" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -5515,7 +5529,7 @@
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G89" t="s">
         <v>21</v>
@@ -5536,27 +5550,27 @@
         <v>25</v>
       </c>
       <c r="M89" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B90" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C90" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D90" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G90" t="s">
         <v>21</v>
@@ -5577,27 +5591,27 @@
         <v>25</v>
       </c>
       <c r="M90" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B91" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C91" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D91" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E91" t="s">
         <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G91" t="s">
         <v>21</v>
@@ -5618,27 +5632,27 @@
         <v>25</v>
       </c>
       <c r="M91" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B92" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C92" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D92" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E92" t="s">
         <v>19</v>
       </c>
       <c r="F92" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G92" t="s">
         <v>21</v>
@@ -5659,27 +5673,27 @@
         <v>25</v>
       </c>
       <c r="M92" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B93" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C93" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D93" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E93" t="s">
         <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G93" t="s">
         <v>21</v>
@@ -5700,27 +5714,27 @@
         <v>25</v>
       </c>
       <c r="M93" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B94" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C94" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D94" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E94" t="s">
         <v>19</v>
       </c>
       <c r="F94" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G94" t="s">
         <v>21</v>
@@ -5741,27 +5755,27 @@
         <v>25</v>
       </c>
       <c r="M94" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B95" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C95" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D95" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E95" t="s">
         <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G95" t="s">
         <v>21</v>
@@ -5782,27 +5796,27 @@
         <v>25</v>
       </c>
       <c r="M95" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B96" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C96" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D96" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E96" t="s">
         <v>19</v>
       </c>
       <c r="F96" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G96" t="s">
         <v>21</v>
@@ -5823,27 +5837,27 @@
         <v>25</v>
       </c>
       <c r="M96" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B97" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C97" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D97" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E97" t="s">
         <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G97" t="s">
         <v>21</v>
@@ -5864,27 +5878,27 @@
         <v>25</v>
       </c>
       <c r="M97" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B98" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C98" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D98" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E98" t="s">
         <v>19</v>
       </c>
       <c r="F98" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G98" t="s">
         <v>21</v>
@@ -5905,27 +5919,27 @@
         <v>25</v>
       </c>
       <c r="M98" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B99" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C99" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D99" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E99" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F99" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G99" t="s">
         <v>21</v>
@@ -5946,27 +5960,27 @@
         <v>25</v>
       </c>
       <c r="M99" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B100" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C100" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D100" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E100" t="s">
         <v>19</v>
       </c>
       <c r="F100" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G100" t="s">
         <v>21</v>
@@ -5987,27 +6001,27 @@
         <v>25</v>
       </c>
       <c r="M100" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B101" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C101" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D101" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E101" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F101" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G101" t="s">
         <v>21</v>
@@ -6028,27 +6042,27 @@
         <v>25</v>
       </c>
       <c r="M101" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B102" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C102" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D102" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E102" t="s">
         <v>19</v>
       </c>
       <c r="F102" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G102" t="s">
         <v>21</v>
@@ -6069,30 +6083,30 @@
         <v>25</v>
       </c>
       <c r="M102" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B103" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C103" t="s">
-        <v>247</v>
+        <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E103" t="s">
         <v>19</v>
       </c>
       <c r="F103" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G103" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H103" t="s">
         <v>22</v>
@@ -6110,30 +6124,30 @@
         <v>25</v>
       </c>
       <c r="M103" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B104" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C104" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D104" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E104" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F104" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G104" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H104" t="s">
         <v>22</v>
@@ -6151,30 +6165,30 @@
         <v>25</v>
       </c>
       <c r="M104" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B105" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C105" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D105" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E105" t="s">
         <v>19</v>
       </c>
       <c r="F105" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G105" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H105" t="s">
         <v>22</v>
@@ -6192,30 +6206,30 @@
         <v>25</v>
       </c>
       <c r="M105" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B106" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C106" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D106" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E106" t="s">
         <v>19</v>
       </c>
       <c r="F106" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G106" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H106" t="s">
         <v>22</v>
@@ -6233,30 +6247,30 @@
         <v>25</v>
       </c>
       <c r="M106" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B107" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C107" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D107" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E107" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F107" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G107" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H107" t="s">
         <v>22</v>
@@ -6274,30 +6288,30 @@
         <v>25</v>
       </c>
       <c r="M107" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B108" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C108" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D108" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E108" t="s">
         <v>19</v>
       </c>
       <c r="F108" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G108" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H108" t="s">
         <v>22</v>
@@ -6315,30 +6329,30 @@
         <v>25</v>
       </c>
       <c r="M108" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B109" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C109" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D109" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E109" t="s">
         <v>19</v>
       </c>
       <c r="F109" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G109" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H109" t="s">
         <v>22</v>
@@ -6356,30 +6370,30 @@
         <v>25</v>
       </c>
       <c r="M109" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B110" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C110" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D110" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E110" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F110" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G110" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H110" t="s">
         <v>22</v>
@@ -6397,30 +6411,30 @@
         <v>25</v>
       </c>
       <c r="M110" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B111" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C111" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D111" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
       </c>
       <c r="F111" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G111" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H111" t="s">
         <v>22</v>
@@ -6438,30 +6452,30 @@
         <v>25</v>
       </c>
       <c r="M111" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B112" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C112" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D112" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E112" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F112" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G112" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H112" t="s">
         <v>22</v>
@@ -6479,30 +6493,30 @@
         <v>25</v>
       </c>
       <c r="M112" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B113" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C113" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D113" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E113" t="s">
         <v>19</v>
       </c>
       <c r="F113" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G113" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H113" t="s">
         <v>22</v>
@@ -6520,30 +6534,30 @@
         <v>25</v>
       </c>
       <c r="M113" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B114" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C114" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D114" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E114" t="s">
         <v>19</v>
       </c>
       <c r="F114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G114" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H114" t="s">
         <v>22</v>
@@ -6561,30 +6575,30 @@
         <v>25</v>
       </c>
       <c r="M114" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B115" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C115" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D115" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E115" t="s">
         <v>19</v>
       </c>
       <c r="F115" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G115" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H115" t="s">
         <v>22</v>
@@ -6602,30 +6616,30 @@
         <v>25</v>
       </c>
       <c r="M115" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B116" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C116" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D116" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E116" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F116" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G116" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H116" t="s">
         <v>22</v>
@@ -6643,30 +6657,30 @@
         <v>25</v>
       </c>
       <c r="M116" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B117" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C117" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D117" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E117" t="s">
         <v>19</v>
       </c>
       <c r="F117" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G117" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H117" t="s">
         <v>22</v>
@@ -6684,30 +6698,30 @@
         <v>25</v>
       </c>
       <c r="M117" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B118" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C118" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D118" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E118" t="s">
         <v>19</v>
       </c>
       <c r="F118" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G118" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H118" t="s">
         <v>22</v>
@@ -6725,30 +6739,30 @@
         <v>25</v>
       </c>
       <c r="M118" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B119" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C119" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D119" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E119" t="s">
         <v>19</v>
       </c>
       <c r="F119" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G119" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H119" t="s">
         <v>22</v>
@@ -6766,30 +6780,30 @@
         <v>25</v>
       </c>
       <c r="M119" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B120" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C120" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D120" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E120" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F120" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G120" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H120" t="s">
         <v>22</v>
@@ -6807,30 +6821,30 @@
         <v>25</v>
       </c>
       <c r="M120" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B121" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C121" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D121" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
       </c>
       <c r="F121" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G121" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H121" t="s">
         <v>22</v>
@@ -6848,30 +6862,30 @@
         <v>25</v>
       </c>
       <c r="M121" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B122" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C122" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D122" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E122" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F122" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G122" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H122" t="s">
         <v>22</v>
@@ -6889,30 +6903,30 @@
         <v>25</v>
       </c>
       <c r="M122" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B123" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C123" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D123" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E123" t="s">
         <v>19</v>
       </c>
       <c r="F123" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G123" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H123" t="s">
         <v>22</v>
@@ -6930,30 +6944,30 @@
         <v>25</v>
       </c>
       <c r="M123" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B124" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C124" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D124" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E124" t="s">
         <v>19</v>
       </c>
       <c r="F124" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G124" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H124" t="s">
         <v>22</v>
@@ -6971,30 +6985,30 @@
         <v>25</v>
       </c>
       <c r="M124" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B125" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C125" t="s">
-        <v>247</v>
+        <v>17</v>
       </c>
       <c r="D125" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E125" t="s">
         <v>19</v>
       </c>
       <c r="F125" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G125" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H125" t="s">
         <v>22</v>
@@ -7012,30 +7026,30 @@
         <v>25</v>
       </c>
       <c r="M125" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B126" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C126" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D126" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E126" t="s">
         <v>19</v>
       </c>
       <c r="F126" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G126" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H126" t="s">
         <v>22</v>
@@ -7053,30 +7067,30 @@
         <v>25</v>
       </c>
       <c r="M126" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B127" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C127" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D127" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E127" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F127" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G127" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H127" t="s">
         <v>22</v>
@@ -7094,30 +7108,30 @@
         <v>25</v>
       </c>
       <c r="M127" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B128" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C128" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D128" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E128" t="s">
         <v>19</v>
       </c>
       <c r="F128" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G128" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H128" t="s">
         <v>22</v>
@@ -7135,30 +7149,30 @@
         <v>25</v>
       </c>
       <c r="M128" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B129" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C129" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D129" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E129" t="s">
         <v>19</v>
       </c>
       <c r="F129" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G129" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H129" t="s">
         <v>22</v>
@@ -7176,30 +7190,30 @@
         <v>25</v>
       </c>
       <c r="M129" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B130" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C130" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D130" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E130" t="s">
         <v>19</v>
       </c>
       <c r="F130" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G130" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H130" t="s">
         <v>22</v>
@@ -7217,30 +7231,30 @@
         <v>25</v>
       </c>
       <c r="M130" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B131" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C131" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D131" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E131" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F131" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G131" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H131" t="s">
         <v>22</v>
@@ -7258,18 +7272,18 @@
         <v>25</v>
       </c>
       <c r="M131" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B132" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C132" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D132" t="s">
         <v>18</v>
@@ -7278,10 +7292,10 @@
         <v>19</v>
       </c>
       <c r="F132" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G132" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H132" t="s">
         <v>22</v>
@@ -7299,30 +7313,30 @@
         <v>25</v>
       </c>
       <c r="M132" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B133" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C133" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D133" t="s">
         <v>18</v>
       </c>
       <c r="E133" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F133" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G133" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H133" t="s">
         <v>22</v>
@@ -7340,30 +7354,30 @@
         <v>25</v>
       </c>
       <c r="M133" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B134" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C134" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D134" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E134" t="s">
         <v>19</v>
       </c>
       <c r="F134" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G134" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H134" t="s">
         <v>22</v>
@@ -7381,30 +7395,30 @@
         <v>25</v>
       </c>
       <c r="M134" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B135" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C135" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D135" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E135" t="s">
         <v>19</v>
       </c>
       <c r="F135" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G135" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H135" t="s">
         <v>22</v>
@@ -7422,30 +7436,30 @@
         <v>25</v>
       </c>
       <c r="M135" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B136" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C136" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D136" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E136" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F136" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G136" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H136" t="s">
         <v>22</v>
@@ -7463,30 +7477,30 @@
         <v>25</v>
       </c>
       <c r="M136" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B137" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C137" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D137" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E137" t="s">
         <v>19</v>
       </c>
       <c r="F137" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G137" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H137" t="s">
         <v>22</v>
@@ -7504,30 +7518,30 @@
         <v>25</v>
       </c>
       <c r="M137" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B138" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C138" t="s">
-        <v>247</v>
+        <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E138" t="s">
         <v>19</v>
       </c>
       <c r="F138" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G138" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H138" t="s">
         <v>22</v>
@@ -7545,30 +7559,30 @@
         <v>25</v>
       </c>
       <c r="M138" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B139" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C139" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D139" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E139" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F139" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G139" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H139" t="s">
         <v>22</v>
@@ -7586,30 +7600,30 @@
         <v>25</v>
       </c>
       <c r="M139" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B140" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C140" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D140" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E140" t="s">
         <v>19</v>
       </c>
       <c r="F140" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G140" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H140" t="s">
         <v>22</v>
@@ -7627,30 +7641,30 @@
         <v>25</v>
       </c>
       <c r="M140" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B141" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C141" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D141" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E141" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F141" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G141" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H141" t="s">
         <v>22</v>
@@ -7668,30 +7682,30 @@
         <v>25</v>
       </c>
       <c r="M141" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B142" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C142" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D142" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E142" t="s">
         <v>19</v>
       </c>
       <c r="F142" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G142" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H142" t="s">
         <v>22</v>
@@ -7709,30 +7723,30 @@
         <v>25</v>
       </c>
       <c r="M142" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B143" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E143" t="s">
         <v>19</v>
       </c>
       <c r="F143" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G143" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H143" t="s">
         <v>22</v>
@@ -7744,36 +7758,36 @@
         <v>2024</v>
       </c>
       <c r="K143" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L143" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M143" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B144" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C144" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D144" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E144" t="s">
         <v>19</v>
       </c>
       <c r="F144" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G144" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H144" t="s">
         <v>22</v>
@@ -7785,36 +7799,36 @@
         <v>2024</v>
       </c>
       <c r="K144" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L144" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M144" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B145" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C145" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D145" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E145" t="s">
         <v>19</v>
       </c>
       <c r="F145" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G145" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H145" t="s">
         <v>22</v>
@@ -7826,36 +7840,36 @@
         <v>2024</v>
       </c>
       <c r="K145" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L145" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M145" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B146" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C146" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D146" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E146" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F146" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G146" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H146" t="s">
         <v>22</v>
@@ -7867,36 +7881,36 @@
         <v>2024</v>
       </c>
       <c r="K146" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L146" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M146" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B147" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C147" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D147" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E147" t="s">
         <v>19</v>
       </c>
       <c r="F147" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G147" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H147" t="s">
         <v>22</v>
@@ -7908,36 +7922,36 @@
         <v>2024</v>
       </c>
       <c r="K147" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L147" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M147" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B148" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C148" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D148" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E148" t="s">
         <v>19</v>
       </c>
       <c r="F148" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G148" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H148" t="s">
         <v>22</v>
@@ -7949,36 +7963,36 @@
         <v>2024</v>
       </c>
       <c r="K148" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L148" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M148" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B149" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C149" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D149" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E149" t="s">
         <v>19</v>
       </c>
       <c r="F149" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G149" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H149" t="s">
         <v>22</v>
@@ -7990,36 +8004,36 @@
         <v>2024</v>
       </c>
       <c r="K149" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L149" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M149" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B150" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C150" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D150" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E150" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F150" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G150" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H150" t="s">
         <v>22</v>
@@ -8031,36 +8045,36 @@
         <v>2024</v>
       </c>
       <c r="K150" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L150" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M150" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B151" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C151" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D151" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E151" t="s">
         <v>19</v>
       </c>
       <c r="F151" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G151" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H151" t="s">
         <v>22</v>
@@ -8072,36 +8086,36 @@
         <v>2024</v>
       </c>
       <c r="K151" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L151" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M151" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B152" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C152" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D152" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E152" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F152" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G152" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H152" t="s">
         <v>22</v>
@@ -8113,36 +8127,36 @@
         <v>2024</v>
       </c>
       <c r="K152" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L152" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M152" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B153" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C153" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D153" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E153" t="s">
         <v>19</v>
       </c>
       <c r="F153" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G153" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H153" t="s">
         <v>22</v>
@@ -8154,36 +8168,36 @@
         <v>2024</v>
       </c>
       <c r="K153" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L153" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M153" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B154" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C154" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D154" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E154" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F154" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G154" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H154" t="s">
         <v>22</v>
@@ -8195,36 +8209,36 @@
         <v>2024</v>
       </c>
       <c r="K154" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L154" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M154" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B155" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C155" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D155" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E155" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F155" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G155" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H155" t="s">
         <v>22</v>
@@ -8236,36 +8250,36 @@
         <v>2024</v>
       </c>
       <c r="K155" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L155" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M155" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B156" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
       </c>
       <c r="D156" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E156" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F156" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G156" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H156" t="s">
         <v>22</v>
@@ -8277,36 +8291,36 @@
         <v>2024</v>
       </c>
       <c r="K156" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L156" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M156" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B157" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C157" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D157" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E157" t="s">
         <v>19</v>
       </c>
       <c r="F157" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G157" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H157" t="s">
         <v>22</v>
@@ -8318,36 +8332,36 @@
         <v>2024</v>
       </c>
       <c r="K157" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L157" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M157" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B158" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C158" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D158" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E158" t="s">
         <v>19</v>
       </c>
       <c r="F158" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G158" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H158" t="s">
         <v>22</v>
@@ -8359,36 +8373,36 @@
         <v>2024</v>
       </c>
       <c r="K158" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L158" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M158" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B159" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C159" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D159" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E159" t="s">
         <v>19</v>
       </c>
       <c r="F159" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G159" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H159" t="s">
         <v>22</v>
@@ -8400,36 +8414,36 @@
         <v>2024</v>
       </c>
       <c r="K159" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L159" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M159" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B160" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C160" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D160" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E160" t="s">
         <v>19</v>
       </c>
       <c r="F160" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G160" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H160" t="s">
         <v>22</v>
@@ -8441,36 +8455,36 @@
         <v>2024</v>
       </c>
       <c r="K160" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L160" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M160" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B161" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C161" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D161" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E161" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F161" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G161" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H161" t="s">
         <v>22</v>
@@ -8482,36 +8496,36 @@
         <v>2024</v>
       </c>
       <c r="K161" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L161" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M161" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B162" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C162" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D162" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E162" t="s">
         <v>19</v>
       </c>
       <c r="F162" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G162" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H162" t="s">
         <v>22</v>
@@ -8523,36 +8537,36 @@
         <v>2024</v>
       </c>
       <c r="K162" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L162" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M162" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B163" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C163" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D163" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E163" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F163" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G163" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H163" t="s">
         <v>22</v>
@@ -8564,36 +8578,36 @@
         <v>2024</v>
       </c>
       <c r="K163" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L163" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M163" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B164" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C164" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D164" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E164" t="s">
         <v>19</v>
       </c>
       <c r="F164" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G164" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H164" t="s">
         <v>22</v>
@@ -8605,36 +8619,36 @@
         <v>2024</v>
       </c>
       <c r="K164" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L164" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M164" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B165" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C165" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D165" t="s">
         <v>18</v>
       </c>
       <c r="E165" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F165" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G165" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H165" t="s">
         <v>22</v>
@@ -8646,24 +8660,24 @@
         <v>2024</v>
       </c>
       <c r="K165" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L165" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M165" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B166" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C166" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D166" t="s">
         <v>18</v>
@@ -8672,10 +8686,10 @@
         <v>19</v>
       </c>
       <c r="F166" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G166" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H166" t="s">
         <v>22</v>
@@ -8687,36 +8701,36 @@
         <v>2024</v>
       </c>
       <c r="K166" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L166" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M166" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B167" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C167" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D167" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E167" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F167" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G167" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H167" t="s">
         <v>22</v>
@@ -8728,36 +8742,36 @@
         <v>2024</v>
       </c>
       <c r="K167" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L167" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M167" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B168" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C168" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D168" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E168" t="s">
         <v>19</v>
       </c>
       <c r="F168" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G168" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H168" t="s">
         <v>22</v>
@@ -8769,36 +8783,36 @@
         <v>2024</v>
       </c>
       <c r="K168" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L168" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M168" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B169" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C169" t="s">
         <v>17</v>
       </c>
       <c r="D169" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E169" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F169" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G169" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H169" t="s">
         <v>22</v>
@@ -8810,36 +8824,36 @@
         <v>2024</v>
       </c>
       <c r="K169" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L169" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M169" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B170" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C170" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D170" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E170" t="s">
         <v>19</v>
       </c>
       <c r="F170" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G170" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H170" t="s">
         <v>22</v>
@@ -8851,36 +8865,36 @@
         <v>2024</v>
       </c>
       <c r="K170" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L170" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M170" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B171" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C171" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D171" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E171" t="s">
         <v>19</v>
       </c>
       <c r="F171" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G171" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H171" t="s">
         <v>22</v>
@@ -8892,36 +8906,36 @@
         <v>2024</v>
       </c>
       <c r="K171" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L171" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M171" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B172" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C172" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D172" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E172" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F172" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G172" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H172" t="s">
         <v>22</v>
@@ -8933,36 +8947,36 @@
         <v>2024</v>
       </c>
       <c r="K172" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L172" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M172" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B173" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C173" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D173" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E173" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F173" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G173" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H173" t="s">
         <v>22</v>
@@ -8974,36 +8988,36 @@
         <v>2024</v>
       </c>
       <c r="K173" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L173" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M173" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B174" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C174" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D174" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E174" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F174" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G174" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H174" t="s">
         <v>22</v>
@@ -9015,36 +9029,36 @@
         <v>2024</v>
       </c>
       <c r="K174" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L174" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M174" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B175" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C175" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D175" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E175" t="s">
         <v>19</v>
       </c>
       <c r="F175" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G175" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H175" t="s">
         <v>22</v>
@@ -9056,36 +9070,36 @@
         <v>2024</v>
       </c>
       <c r="K175" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L175" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M175" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B176" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C176" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D176" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E176" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F176" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G176" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H176" t="s">
         <v>22</v>
@@ -9097,36 +9111,36 @@
         <v>2024</v>
       </c>
       <c r="K176" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L176" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M176" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B177" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C177" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D177" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E177" t="s">
         <v>19</v>
       </c>
       <c r="F177" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G177" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H177" t="s">
         <v>22</v>
@@ -9138,36 +9152,36 @@
         <v>2024</v>
       </c>
       <c r="K177" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L177" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M177" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B178" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C178" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D178" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E178" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F178" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G178" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H178" t="s">
         <v>22</v>
@@ -9179,24 +9193,24 @@
         <v>2024</v>
       </c>
       <c r="K178" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L178" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M178" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B179" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C179" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D179" t="s">
         <v>18</v>
@@ -9205,10 +9219,10 @@
         <v>19</v>
       </c>
       <c r="F179" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G179" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H179" t="s">
         <v>22</v>
@@ -9220,36 +9234,36 @@
         <v>2024</v>
       </c>
       <c r="K179" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L179" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M179" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B180" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C180" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D180" t="s">
         <v>18</v>
       </c>
       <c r="E180" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F180" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G180" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H180" t="s">
         <v>22</v>
@@ -9261,24 +9275,24 @@
         <v>2024</v>
       </c>
       <c r="K180" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L180" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M180" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B181" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C181" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D181" t="s">
         <v>18</v>
@@ -9287,10 +9301,10 @@
         <v>19</v>
       </c>
       <c r="F181" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G181" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H181" t="s">
         <v>22</v>
@@ -9302,36 +9316,36 @@
         <v>2024</v>
       </c>
       <c r="K181" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L181" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M181" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B182" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C182" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D182" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E182" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F182" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G182" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H182" t="s">
         <v>22</v>
@@ -9343,36 +9357,36 @@
         <v>2024</v>
       </c>
       <c r="K182" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L182" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M182" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B183" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C183" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D183" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E183" t="s">
         <v>19</v>
       </c>
       <c r="F183" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G183" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H183" t="s">
         <v>22</v>
@@ -9384,33 +9398,33 @@
         <v>2024</v>
       </c>
       <c r="K183" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L183" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M183" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B184" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C184" t="s">
         <v>17</v>
       </c>
       <c r="D184" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E184" t="s">
         <v>19</v>
       </c>
       <c r="F184" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G184" t="s">
         <v>21</v>
@@ -9425,33 +9439,33 @@
         <v>2025</v>
       </c>
       <c r="K184" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L184" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M184" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B185" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C185" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D185" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E185" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F185" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G185" t="s">
         <v>21</v>
@@ -9466,33 +9480,33 @@
         <v>2025</v>
       </c>
       <c r="K185" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L185" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M185" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B186" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C186" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D186" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E186" t="s">
         <v>19</v>
       </c>
       <c r="F186" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G186" t="s">
         <v>21</v>
@@ -9507,33 +9521,33 @@
         <v>2025</v>
       </c>
       <c r="K186" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L186" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M186" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B187" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C187" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D187" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E187" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F187" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G187" t="s">
         <v>21</v>
@@ -9548,33 +9562,33 @@
         <v>2025</v>
       </c>
       <c r="K187" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L187" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M187" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B188" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C188" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D188" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E188" t="s">
         <v>19</v>
       </c>
       <c r="F188" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G188" t="s">
         <v>21</v>
@@ -9589,33 +9603,33 @@
         <v>2025</v>
       </c>
       <c r="K188" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L188" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M188" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B189" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C189" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D189" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E189" t="s">
         <v>19</v>
       </c>
       <c r="F189" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G189" t="s">
         <v>21</v>
@@ -9630,33 +9644,33 @@
         <v>2025</v>
       </c>
       <c r="K189" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L189" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M189" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B190" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C190" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D190" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E190" t="s">
         <v>19</v>
       </c>
       <c r="F190" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G190" t="s">
         <v>21</v>
@@ -9671,33 +9685,33 @@
         <v>2025</v>
       </c>
       <c r="K190" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L190" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M190" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B191" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C191" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D191" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E191" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F191" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G191" t="s">
         <v>21</v>
@@ -9712,33 +9726,33 @@
         <v>2025</v>
       </c>
       <c r="K191" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L191" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M191" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B192" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C192" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D192" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E192" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F192" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G192" t="s">
         <v>21</v>
@@ -9753,33 +9767,33 @@
         <v>2025</v>
       </c>
       <c r="K192" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L192" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M192" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B193" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C193" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D193" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E193" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F193" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G193" t="s">
         <v>21</v>
@@ -9794,33 +9808,33 @@
         <v>2025</v>
       </c>
       <c r="K193" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L193" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M193" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B194" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C194" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D194" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E194" t="s">
         <v>19</v>
       </c>
       <c r="F194" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G194" t="s">
         <v>21</v>
@@ -9835,33 +9849,33 @@
         <v>2025</v>
       </c>
       <c r="K194" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L194" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M194" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B195" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C195" t="s">
-        <v>435</v>
+        <v>17</v>
       </c>
       <c r="D195" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E195" t="s">
         <v>19</v>
       </c>
       <c r="F195" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G195" t="s">
         <v>21</v>
@@ -9876,30 +9890,33 @@
         <v>2025</v>
       </c>
       <c r="K195" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L195" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M195" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B196" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C196" t="s">
-        <v>159</v>
+        <v>155</v>
+      </c>
+      <c r="D196" t="s">
+        <v>56</v>
       </c>
       <c r="E196" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F196" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G196" t="s">
         <v>21</v>
@@ -9914,33 +9931,33 @@
         <v>2025</v>
       </c>
       <c r="K196" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L196" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M196" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B197" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C197" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D197" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E197" t="s">
         <v>19</v>
       </c>
       <c r="F197" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G197" t="s">
         <v>21</v>
@@ -9955,33 +9972,33 @@
         <v>2025</v>
       </c>
       <c r="K197" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L197" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M197" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B198" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C198" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D198" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E198" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F198" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G198" t="s">
         <v>21</v>
@@ -9996,33 +10013,33 @@
         <v>2025</v>
       </c>
       <c r="K198" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L198" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M198" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B199" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C199" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D199" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E199" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F199" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G199" t="s">
         <v>21</v>
@@ -10037,33 +10054,33 @@
         <v>2025</v>
       </c>
       <c r="K199" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L199" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M199" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B200" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C200" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D200" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E200" t="s">
         <v>19</v>
       </c>
       <c r="F200" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G200" t="s">
         <v>21</v>
@@ -10078,33 +10095,33 @@
         <v>2025</v>
       </c>
       <c r="K200" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L200" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M200" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B201" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C201" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D201" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E201" t="s">
         <v>19</v>
       </c>
       <c r="F201" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G201" t="s">
         <v>21</v>
@@ -10119,33 +10136,33 @@
         <v>2025</v>
       </c>
       <c r="K201" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L201" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M201" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B202" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C202" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D202" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E202" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F202" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G202" t="s">
         <v>21</v>
@@ -10160,33 +10177,33 @@
         <v>2025</v>
       </c>
       <c r="K202" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L202" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M202" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B203" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C203" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D203" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E203" t="s">
         <v>19</v>
       </c>
       <c r="F203" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G203" t="s">
         <v>21</v>
@@ -10201,33 +10218,33 @@
         <v>2025</v>
       </c>
       <c r="K203" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L203" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M203" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B204" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C204" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D204" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E204" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F204" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G204" t="s">
         <v>21</v>
@@ -10242,33 +10259,33 @@
         <v>2025</v>
       </c>
       <c r="K204" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L204" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M204" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B205" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C205" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D205" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E205" t="s">
         <v>19</v>
       </c>
       <c r="F205" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G205" t="s">
         <v>21</v>
@@ -10283,33 +10300,33 @@
         <v>2025</v>
       </c>
       <c r="K205" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L205" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M205" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B206" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C206" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D206" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E206" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F206" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G206" t="s">
         <v>21</v>
@@ -10324,33 +10341,33 @@
         <v>2025</v>
       </c>
       <c r="K206" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L206" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M206" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B207" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C207" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D207" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E207" t="s">
         <v>19</v>
       </c>
       <c r="F207" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G207" t="s">
         <v>21</v>
@@ -10365,33 +10382,33 @@
         <v>2025</v>
       </c>
       <c r="K207" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L207" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M207" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B208" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C208" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D208" t="s">
         <v>18</v>
       </c>
       <c r="E208" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F208" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G208" t="s">
         <v>21</v>
@@ -10406,33 +10423,33 @@
         <v>2025</v>
       </c>
       <c r="K208" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L208" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M208" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B209" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C209" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D209" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E209" t="s">
         <v>19</v>
       </c>
       <c r="F209" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G209" t="s">
         <v>21</v>
@@ -10447,33 +10464,33 @@
         <v>2025</v>
       </c>
       <c r="K209" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L209" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M209" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B210" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C210" t="s">
         <v>17</v>
       </c>
       <c r="D210" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E210" t="s">
         <v>19</v>
       </c>
       <c r="F210" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G210" t="s">
         <v>21</v>
@@ -10488,33 +10505,33 @@
         <v>2025</v>
       </c>
       <c r="K210" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L210" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M210" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B211" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C211" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D211" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E211" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F211" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G211" t="s">
         <v>21</v>
@@ -10529,33 +10546,33 @@
         <v>2025</v>
       </c>
       <c r="K211" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L211" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M211" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B212" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C212" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D212" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E212" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F212" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G212" t="s">
         <v>21</v>
@@ -10570,33 +10587,33 @@
         <v>2025</v>
       </c>
       <c r="K212" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L212" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M212" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B213" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C213" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D213" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E213" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F213" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G213" t="s">
         <v>21</v>
@@ -10611,33 +10628,33 @@
         <v>2025</v>
       </c>
       <c r="K213" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L213" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M213" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B214" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C214" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D214" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E214" t="s">
         <v>19</v>
       </c>
       <c r="F214" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G214" t="s">
         <v>21</v>
@@ -10652,33 +10669,33 @@
         <v>2025</v>
       </c>
       <c r="K214" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L214" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M214" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B215" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C215" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D215" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E215" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F215" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G215" t="s">
         <v>21</v>
@@ -10693,33 +10710,33 @@
         <v>2025</v>
       </c>
       <c r="K215" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L215" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M215" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B216" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C216" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D216" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E216" t="s">
         <v>19</v>
       </c>
       <c r="F216" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G216" t="s">
         <v>21</v>
@@ -10734,33 +10751,33 @@
         <v>2025</v>
       </c>
       <c r="K216" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L216" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M216" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B217" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C217" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D217" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E217" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F217" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G217" t="s">
         <v>21</v>
@@ -10775,33 +10792,33 @@
         <v>2025</v>
       </c>
       <c r="K217" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L217" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M217" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B218" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C218" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D218" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E218" t="s">
         <v>19</v>
       </c>
       <c r="F218" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G218" t="s">
         <v>21</v>
@@ -10816,33 +10833,33 @@
         <v>2025</v>
       </c>
       <c r="K218" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L218" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M218" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B219" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C219" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D219" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E219" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F219" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G219" t="s">
         <v>21</v>
@@ -10857,33 +10874,33 @@
         <v>2025</v>
       </c>
       <c r="K219" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L219" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M219" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B220" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C220" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D220" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E220" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F220" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G220" t="s">
         <v>21</v>
@@ -10898,17 +10915,20 @@
         <v>2025</v>
       </c>
       <c r="K220" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L220" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M220" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/input/adidas.xlsx
+++ b/data/input/adidas.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11020"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415B7695-3A9E-D14E-9040-DBC5E01A0701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A76815A-9715-FA44-932A-EDC94B77D7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="21400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13240" yWindow="1880" windowWidth="24980" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="490">
   <si>
     <t>ID</t>
   </si>
@@ -1258,9 +1258,6 @@
     <t>DEU25A00-00</t>
   </si>
   <si>
-    <t xml:space="preserve">THE GLOBAL POTENTIAL FOR ADIDAS IS ALMOST UNLIMITED </t>
-  </si>
-  <si>
     <t>DEU25A01-00</t>
   </si>
   <si>
@@ -1478,6 +1475,36 @@
   </si>
   <si>
     <t>Leadership_context_human</t>
+  </si>
+  <si>
+    <t>Reports realized brand and product success. Although the subject is product-market activity, the primary proposition is the achieved popularity of the Samba and Gazelle, therefore coded PERF</t>
+  </si>
+  <si>
+    <t>Product-focused question; “better future” is background purpose, not the primary communicative object</t>
+  </si>
+  <si>
+    <t>Reports realized product and sports achievements more than their produtcts</t>
+  </si>
+  <si>
+    <t>Coded MARKET because brand and consumer-market activity are the primary object, while improved performance is the reported outcome.</t>
+  </si>
+  <si>
+    <t>Interview question about the commercial and brand importance of major sports events for adidas. The substantive focus is market and business impact, so MARKET is preferred over STRAT.</t>
+  </si>
+  <si>
+    <t>The primary purpose is to explain the positive business and brand-market impact of the Olympic and Paralympic Games for adidas.</t>
+  </si>
+  <si>
+    <t>The question contains positive evaluative information about product popularity and Lifestyle development.</t>
+  </si>
+  <si>
+    <t>Expresses a favorable societal and community effect of sport bringing people together.</t>
+  </si>
+  <si>
+    <t>THE GLOBAL POTENTIAL FOR ADIDAS IS ALMOST UNLIMITED</t>
+  </si>
+  <si>
+    <t>The strategic direction is positive, but “potential” is not a realized achievement, so valence is neutral  rather than positive.</t>
   </si>
 </sst>
 </file>
@@ -1882,7 +1909,9 @@
   <dimension ref="A1:P220"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
     <col min="4" max="4" width="24.5" customWidth="1"/>
     <col min="5" max="5" width="25.33203125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
@@ -1906,7 +1935,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1985,6 +2014,9 @@
       <c r="M2" t="s">
         <v>26</v>
       </c>
+      <c r="O2" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -2026,6 +2058,9 @@
       <c r="M3" t="s">
         <v>26</v>
       </c>
+      <c r="O3" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -2067,6 +2102,9 @@
       <c r="M4" t="s">
         <v>26</v>
       </c>
+      <c r="O4" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -2108,6 +2146,9 @@
       <c r="M5" t="s">
         <v>26</v>
       </c>
+      <c r="O5" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -2149,6 +2190,9 @@
       <c r="M6" t="s">
         <v>26</v>
       </c>
+      <c r="O6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -2190,6 +2234,9 @@
       <c r="M7" t="s">
         <v>26</v>
       </c>
+      <c r="O7" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -2231,6 +2278,9 @@
       <c r="M8" t="s">
         <v>26</v>
       </c>
+      <c r="O8" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -2272,6 +2322,9 @@
       <c r="M9" t="s">
         <v>26</v>
       </c>
+      <c r="O9" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -2313,6 +2366,9 @@
       <c r="M10" t="s">
         <v>26</v>
       </c>
+      <c r="O10" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -2354,6 +2410,9 @@
       <c r="M11" t="s">
         <v>26</v>
       </c>
+      <c r="O11" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -2395,6 +2454,9 @@
       <c r="M12" t="s">
         <v>26</v>
       </c>
+      <c r="O12" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -2436,6 +2498,9 @@
       <c r="M13" t="s">
         <v>26</v>
       </c>
+      <c r="O13" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -2477,6 +2542,9 @@
       <c r="M14" t="s">
         <v>26</v>
       </c>
+      <c r="O14" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -2518,6 +2586,9 @@
       <c r="M15" t="s">
         <v>26</v>
       </c>
+      <c r="O15" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -2559,8 +2630,11 @@
       <c r="M16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O16" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -2571,7 +2645,7 @@
         <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
         <v>38</v>
@@ -2600,8 +2674,11 @@
       <c r="M17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O17" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -2615,7 +2692,7 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
@@ -2641,8 +2718,11 @@
       <c r="M18" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O18" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -2682,8 +2762,11 @@
       <c r="M19" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O19" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -2723,8 +2806,11 @@
       <c r="M20" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O20" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -2764,8 +2850,11 @@
       <c r="M21" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O21" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -2805,8 +2894,11 @@
       <c r="M22" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O22" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -2846,8 +2938,11 @@
       <c r="M23" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O23" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -2887,8 +2982,11 @@
       <c r="M24" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O24" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>78</v>
       </c>
@@ -2928,8 +3026,11 @@
       <c r="M25" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O25" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -2969,8 +3070,11 @@
       <c r="M26" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O26" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>82</v>
       </c>
@@ -3010,8 +3114,11 @@
       <c r="M27" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O27" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -3051,8 +3158,11 @@
       <c r="M28" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O28" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>86</v>
       </c>
@@ -3092,8 +3202,11 @@
       <c r="M29" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O29" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>88</v>
       </c>
@@ -3133,8 +3246,11 @@
       <c r="M30" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O30" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -3174,8 +3290,11 @@
       <c r="M31" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O31" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>92</v>
       </c>
@@ -3186,7 +3305,7 @@
         <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
@@ -3215,8 +3334,11 @@
       <c r="M32" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O32" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>95</v>
       </c>
@@ -3227,7 +3349,7 @@
         <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -3256,8 +3378,11 @@
       <c r="M33" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O33" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>97</v>
       </c>
@@ -3297,8 +3422,11 @@
       <c r="M34" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O34" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>100</v>
       </c>
@@ -3338,8 +3466,11 @@
       <c r="M35" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O35" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>103</v>
       </c>
@@ -3379,8 +3510,11 @@
       <c r="M36" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O36" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>105</v>
       </c>
@@ -3420,8 +3554,11 @@
       <c r="M37" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O37" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>107</v>
       </c>
@@ -3461,8 +3598,11 @@
       <c r="M38" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O38" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>109</v>
       </c>
@@ -3502,8 +3642,11 @@
       <c r="M39" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O39" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>111</v>
       </c>
@@ -3543,8 +3686,11 @@
       <c r="M40" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O40" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>113</v>
       </c>
@@ -3584,8 +3730,11 @@
       <c r="M41" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O41" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>115</v>
       </c>
@@ -3625,8 +3774,11 @@
       <c r="M42" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O42" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -3666,8 +3818,11 @@
       <c r="M43" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O43" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>119</v>
       </c>
@@ -3707,8 +3862,11 @@
       <c r="M44" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O44" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>121</v>
       </c>
@@ -3748,8 +3906,11 @@
       <c r="M45" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O45" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>123</v>
       </c>
@@ -3789,8 +3950,11 @@
       <c r="M46" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O46" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>125</v>
       </c>
@@ -3804,7 +3968,7 @@
         <v>56</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F47" t="s">
         <v>20</v>
@@ -3830,8 +3994,11 @@
       <c r="M47" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O47" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>127</v>
       </c>
@@ -3871,8 +4038,11 @@
       <c r="M48" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O48" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>129</v>
       </c>
@@ -3912,8 +4082,11 @@
       <c r="M49" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O49" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>131</v>
       </c>
@@ -3953,8 +4126,11 @@
       <c r="M50" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O50" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>133</v>
       </c>
@@ -3994,8 +4170,11 @@
       <c r="M51" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O51" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>135</v>
       </c>
@@ -4035,8 +4214,11 @@
       <c r="M52" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O52" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>137</v>
       </c>
@@ -4076,8 +4258,11 @@
       <c r="M53" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O53" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>139</v>
       </c>
@@ -4117,8 +4302,11 @@
       <c r="M54" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O54" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>141</v>
       </c>
@@ -4158,8 +4346,11 @@
       <c r="M55" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O55" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>143</v>
       </c>
@@ -4199,8 +4390,11 @@
       <c r="M56" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O56" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>145</v>
       </c>
@@ -4240,8 +4434,11 @@
       <c r="M57" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O57" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>147</v>
       </c>
@@ -4281,8 +4478,11 @@
       <c r="M58" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O58" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>149</v>
       </c>
@@ -4322,8 +4522,11 @@
       <c r="M59" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O59" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>153</v>
       </c>
@@ -4363,8 +4566,11 @@
       <c r="M60" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O60" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>156</v>
       </c>
@@ -4404,8 +4610,11 @@
       <c r="M61" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O61" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>159</v>
       </c>
@@ -4445,8 +4654,11 @@
       <c r="M62" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O62" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>161</v>
       </c>
@@ -4486,8 +4698,11 @@
       <c r="M63" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O63" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>163</v>
       </c>
@@ -4527,8 +4742,11 @@
       <c r="M64" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O64" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>165</v>
       </c>
@@ -4568,8 +4786,11 @@
       <c r="M65" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O65" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>167</v>
       </c>
@@ -4609,8 +4830,11 @@
       <c r="M66" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O66" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>169</v>
       </c>
@@ -4650,8 +4874,11 @@
       <c r="M67" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O67" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>171</v>
       </c>
@@ -4691,8 +4918,11 @@
       <c r="M68" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O68" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>173</v>
       </c>
@@ -4732,8 +4962,11 @@
       <c r="M69" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O69" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>175</v>
       </c>
@@ -4773,8 +5006,11 @@
       <c r="M70" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O70" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>177</v>
       </c>
@@ -4814,8 +5050,11 @@
       <c r="M71" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O71" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>179</v>
       </c>
@@ -4855,8 +5094,11 @@
       <c r="M72" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O72" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>181</v>
       </c>
@@ -4896,8 +5138,11 @@
       <c r="M73" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O73" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>183</v>
       </c>
@@ -4937,8 +5182,11 @@
       <c r="M74" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O74" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>185</v>
       </c>
@@ -4978,8 +5226,11 @@
       <c r="M75" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O75" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>187</v>
       </c>
@@ -5019,8 +5270,11 @@
       <c r="M76" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O76" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>189</v>
       </c>
@@ -5060,8 +5314,11 @@
       <c r="M77" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O77" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>191</v>
       </c>
@@ -5101,8 +5358,11 @@
       <c r="M78" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O78" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>193</v>
       </c>
@@ -5142,8 +5402,11 @@
       <c r="M79" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O79" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>195</v>
       </c>
@@ -5183,8 +5446,11 @@
       <c r="M80" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O80" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>197</v>
       </c>
@@ -5224,8 +5490,11 @@
       <c r="M81" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O81" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>199</v>
       </c>
@@ -5265,8 +5534,11 @@
       <c r="M82" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O82" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>201</v>
       </c>
@@ -5306,8 +5578,11 @@
       <c r="M83" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O83" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>203</v>
       </c>
@@ -5321,7 +5596,7 @@
         <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F84" t="s">
         <v>151</v>
@@ -5347,8 +5622,11 @@
       <c r="M84" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O84" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>205</v>
       </c>
@@ -5388,8 +5666,11 @@
       <c r="M85" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O85" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>207</v>
       </c>
@@ -5429,8 +5710,11 @@
       <c r="M86" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O86" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>209</v>
       </c>
@@ -5470,8 +5754,11 @@
       <c r="M87" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O87" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>211</v>
       </c>
@@ -5511,8 +5798,11 @@
       <c r="M88" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O88" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>213</v>
       </c>
@@ -5552,8 +5842,11 @@
       <c r="M89" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O89" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>215</v>
       </c>
@@ -5593,8 +5886,11 @@
       <c r="M90" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O90" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>217</v>
       </c>
@@ -5634,8 +5930,11 @@
       <c r="M91" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O91" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>219</v>
       </c>
@@ -5675,8 +5974,11 @@
       <c r="M92" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O92" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>221</v>
       </c>
@@ -5716,8 +6018,11 @@
       <c r="M93" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O93" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>223</v>
       </c>
@@ -5757,8 +6062,11 @@
       <c r="M94" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O94" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>225</v>
       </c>
@@ -5798,8 +6106,17 @@
       <c r="M95" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N95" t="s">
+        <v>480</v>
+      </c>
+      <c r="O95" t="s">
+        <v>24</v>
+      </c>
+      <c r="P95" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>227</v>
       </c>
@@ -5839,8 +6156,11 @@
       <c r="M96" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O96" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>229</v>
       </c>
@@ -5880,8 +6200,11 @@
       <c r="M97" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O97" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>231</v>
       </c>
@@ -5921,8 +6244,11 @@
       <c r="M98" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O98" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>233</v>
       </c>
@@ -5962,8 +6288,14 @@
       <c r="M99" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O99" t="s">
+        <v>325</v>
+      </c>
+      <c r="P99" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>235</v>
       </c>
@@ -6003,8 +6335,11 @@
       <c r="M100" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O100" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>237</v>
       </c>
@@ -6044,8 +6379,11 @@
       <c r="M101" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O101" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>239</v>
       </c>
@@ -6056,10 +6394,10 @@
         <v>158</v>
       </c>
       <c r="D102" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E102" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F102" t="s">
         <v>151</v>
@@ -6085,8 +6423,11 @@
       <c r="M102" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O102" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>241</v>
       </c>
@@ -6126,8 +6467,11 @@
       <c r="M103" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O103" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>244</v>
       </c>
@@ -6167,8 +6511,11 @@
       <c r="M104" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O104" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>246</v>
       </c>
@@ -6208,8 +6555,11 @@
       <c r="M105" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O105" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>248</v>
       </c>
@@ -6249,8 +6599,17 @@
       <c r="M106" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N106" t="s">
+        <v>482</v>
+      </c>
+      <c r="O106" t="s">
+        <v>24</v>
+      </c>
+      <c r="P106" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>250</v>
       </c>
@@ -6290,8 +6649,11 @@
       <c r="M107" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O107" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>252</v>
       </c>
@@ -6331,8 +6693,11 @@
       <c r="M108" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O108" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>254</v>
       </c>
@@ -6372,8 +6737,11 @@
       <c r="M109" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O109" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>256</v>
       </c>
@@ -6413,8 +6781,17 @@
       <c r="M110" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N110" t="s">
+        <v>481</v>
+      </c>
+      <c r="O110" t="s">
+        <v>24</v>
+      </c>
+      <c r="P110" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>258</v>
       </c>
@@ -6454,8 +6831,11 @@
       <c r="M111" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O111" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>260</v>
       </c>
@@ -6495,8 +6875,11 @@
       <c r="M112" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O112" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>262</v>
       </c>
@@ -6536,8 +6919,11 @@
       <c r="M113" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O113" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>264</v>
       </c>
@@ -6577,8 +6963,11 @@
       <c r="M114" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O114" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>266</v>
       </c>
@@ -6618,8 +7007,11 @@
       <c r="M115" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O115" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>268</v>
       </c>
@@ -6659,8 +7051,11 @@
       <c r="M116" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O116" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>270</v>
       </c>
@@ -6700,8 +7095,11 @@
       <c r="M117" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O117" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>272</v>
       </c>
@@ -6741,8 +7139,11 @@
       <c r="M118" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O118" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>274</v>
       </c>
@@ -6782,8 +7183,11 @@
       <c r="M119" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O119" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>276</v>
       </c>
@@ -6823,8 +7227,11 @@
       <c r="M120" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O120" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>278</v>
       </c>
@@ -6835,7 +7242,7 @@
         <v>158</v>
       </c>
       <c r="D121" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
@@ -6864,8 +7271,17 @@
       <c r="M121" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N121" t="s">
+        <v>483</v>
+      </c>
+      <c r="O121" t="s">
+        <v>24</v>
+      </c>
+      <c r="P121" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>280</v>
       </c>
@@ -6876,7 +7292,7 @@
         <v>155</v>
       </c>
       <c r="D122" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E122" t="s">
         <v>38</v>
@@ -6905,8 +7321,17 @@
       <c r="M122" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N122" t="s">
+        <v>484</v>
+      </c>
+      <c r="O122" t="s">
+        <v>24</v>
+      </c>
+      <c r="P122" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>282</v>
       </c>
@@ -6946,8 +7371,11 @@
       <c r="M123" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O123" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>284</v>
       </c>
@@ -6958,7 +7386,7 @@
         <v>158</v>
       </c>
       <c r="D124" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E124" t="s">
         <v>19</v>
@@ -6987,8 +7415,14 @@
       <c r="M124" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N124" t="s">
+        <v>485</v>
+      </c>
+      <c r="O124" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>286</v>
       </c>
@@ -7028,8 +7462,11 @@
       <c r="M125" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O125" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>288</v>
       </c>
@@ -7069,8 +7506,11 @@
       <c r="M126" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O126" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>290</v>
       </c>
@@ -7110,8 +7550,11 @@
       <c r="M127" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O127" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>292</v>
       </c>
@@ -7122,10 +7565,10 @@
         <v>155</v>
       </c>
       <c r="D128" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="E128" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F128" t="s">
         <v>151</v>
@@ -7151,8 +7594,11 @@
       <c r="M128" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O128" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>294</v>
       </c>
@@ -7192,8 +7638,11 @@
       <c r="M129" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O129" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>296</v>
       </c>
@@ -7233,8 +7682,11 @@
       <c r="M130" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O130" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>298</v>
       </c>
@@ -7274,8 +7726,11 @@
       <c r="M131" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O131" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>300</v>
       </c>
@@ -7315,8 +7770,11 @@
       <c r="M132" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O132" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>302</v>
       </c>
@@ -7356,8 +7814,11 @@
       <c r="M133" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O133" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>304</v>
       </c>
@@ -7397,8 +7858,11 @@
       <c r="M134" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O134" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>306</v>
       </c>
@@ -7438,8 +7902,11 @@
       <c r="M135" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O135" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>308</v>
       </c>
@@ -7479,8 +7946,11 @@
       <c r="M136" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O136" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>310</v>
       </c>
@@ -7520,8 +7990,11 @@
       <c r="M137" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O137" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>312</v>
       </c>
@@ -7561,8 +8034,11 @@
       <c r="M138" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O138" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>314</v>
       </c>
@@ -7602,8 +8078,11 @@
       <c r="M139" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O139" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>316</v>
       </c>
@@ -7643,8 +8122,11 @@
       <c r="M140" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O140" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>318</v>
       </c>
@@ -7684,8 +8166,11 @@
       <c r="M141" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O141" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>320</v>
       </c>
@@ -7699,7 +8184,7 @@
         <v>102</v>
       </c>
       <c r="E142" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F142" t="s">
         <v>151</v>
@@ -7725,8 +8210,11 @@
       <c r="M142" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O142" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>322</v>
       </c>
@@ -7766,8 +8254,11 @@
       <c r="M143" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O143" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>326</v>
       </c>
@@ -7807,8 +8298,11 @@
       <c r="M144" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O144" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>328</v>
       </c>
@@ -7848,8 +8342,11 @@
       <c r="M145" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O145" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>330</v>
       </c>
@@ -7889,8 +8386,11 @@
       <c r="M146" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O146" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>332</v>
       </c>
@@ -7930,8 +8430,11 @@
       <c r="M147" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O147" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>334</v>
       </c>
@@ -7971,8 +8474,11 @@
       <c r="M148" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O148" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>336</v>
       </c>
@@ -8012,8 +8518,11 @@
       <c r="M149" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O149" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>338</v>
       </c>
@@ -8024,10 +8533,10 @@
         <v>155</v>
       </c>
       <c r="D150" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E150" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F150" t="s">
         <v>324</v>
@@ -8053,8 +8562,14 @@
       <c r="M150" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N150" t="s">
+        <v>486</v>
+      </c>
+      <c r="O150" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>340</v>
       </c>
@@ -8094,8 +8609,11 @@
       <c r="M151" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O151" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>342</v>
       </c>
@@ -8135,8 +8653,11 @@
       <c r="M152" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O152" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>344</v>
       </c>
@@ -8176,8 +8697,11 @@
       <c r="M153" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O153" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>346</v>
       </c>
@@ -8188,7 +8712,7 @@
         <v>155</v>
       </c>
       <c r="D154" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="E154" t="s">
         <v>38</v>
@@ -8217,8 +8741,11 @@
       <c r="M154" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O154" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>348</v>
       </c>
@@ -8258,8 +8785,11 @@
       <c r="M155" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O155" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>350</v>
       </c>
@@ -8270,7 +8800,7 @@
         <v>17</v>
       </c>
       <c r="D156" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E156" t="s">
         <v>38</v>
@@ -8299,8 +8829,11 @@
       <c r="M156" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O156" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>352</v>
       </c>
@@ -8340,8 +8873,11 @@
       <c r="M157" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O157" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>354</v>
       </c>
@@ -8355,7 +8891,7 @@
         <v>59</v>
       </c>
       <c r="E158" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F158" t="s">
         <v>324</v>
@@ -8381,8 +8917,11 @@
       <c r="M158" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O158" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>356</v>
       </c>
@@ -8422,8 +8961,11 @@
       <c r="M159" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O159" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>358</v>
       </c>
@@ -8463,8 +9005,11 @@
       <c r="M160" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O160" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>360</v>
       </c>
@@ -8504,8 +9049,11 @@
       <c r="M161" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O161" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>362</v>
       </c>
@@ -8545,8 +9093,11 @@
       <c r="M162" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O162" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>364</v>
       </c>
@@ -8586,8 +9137,11 @@
       <c r="M163" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O163" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>366</v>
       </c>
@@ -8627,8 +9181,11 @@
       <c r="M164" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O164" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>368</v>
       </c>
@@ -8668,8 +9225,11 @@
       <c r="M165" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O165" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>370</v>
       </c>
@@ -8709,8 +9269,11 @@
       <c r="M166" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O166" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>372</v>
       </c>
@@ -8750,8 +9313,11 @@
       <c r="M167" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O167" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>374</v>
       </c>
@@ -8791,8 +9357,11 @@
       <c r="M168" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O168" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>376</v>
       </c>
@@ -8832,8 +9401,11 @@
       <c r="M169" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O169" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>378</v>
       </c>
@@ -8873,8 +9445,11 @@
       <c r="M170" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O170" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>380</v>
       </c>
@@ -8914,8 +9489,11 @@
       <c r="M171" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O171" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>382</v>
       </c>
@@ -8955,8 +9533,11 @@
       <c r="M172" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O172" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>384</v>
       </c>
@@ -8996,8 +9577,11 @@
       <c r="M173" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O173" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>386</v>
       </c>
@@ -9037,8 +9621,11 @@
       <c r="M174" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O174" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>388</v>
       </c>
@@ -9078,8 +9665,11 @@
       <c r="M175" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O175" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>390</v>
       </c>
@@ -9119,8 +9709,11 @@
       <c r="M176" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O176" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>392</v>
       </c>
@@ -9160,8 +9753,11 @@
       <c r="M177" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O177" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>394</v>
       </c>
@@ -9201,8 +9797,11 @@
       <c r="M178" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O178" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>396</v>
       </c>
@@ -9242,8 +9841,11 @@
       <c r="M179" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O179" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>398</v>
       </c>
@@ -9283,8 +9885,11 @@
       <c r="M180" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O180" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>400</v>
       </c>
@@ -9324,8 +9929,11 @@
       <c r="M181" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O181" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>402</v>
       </c>
@@ -9365,8 +9973,11 @@
       <c r="M182" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O182" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>404</v>
       </c>
@@ -9406,22 +10017,25 @@
       <c r="M183" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O183" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>406</v>
       </c>
       <c r="B184" t="s">
-        <v>407</v>
+        <v>488</v>
       </c>
       <c r="C184" t="s">
         <v>17</v>
       </c>
       <c r="D184" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="E184" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F184" t="s">
         <v>324</v>
@@ -9447,13 +10061,19 @@
       <c r="M184" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N184" t="s">
+        <v>489</v>
+      </c>
+      <c r="O184" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
+        <v>407</v>
+      </c>
+      <c r="B185" t="s">
         <v>408</v>
-      </c>
-      <c r="B185" t="s">
-        <v>409</v>
       </c>
       <c r="C185" t="s">
         <v>155</v>
@@ -9488,13 +10108,16 @@
       <c r="M185" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O185" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
+        <v>409</v>
+      </c>
+      <c r="B186" t="s">
         <v>410</v>
-      </c>
-      <c r="B186" t="s">
-        <v>411</v>
       </c>
       <c r="C186" t="s">
         <v>158</v>
@@ -9529,13 +10152,16 @@
       <c r="M186" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O186" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
+        <v>411</v>
+      </c>
+      <c r="B187" t="s">
         <v>412</v>
-      </c>
-      <c r="B187" t="s">
-        <v>413</v>
       </c>
       <c r="C187" t="s">
         <v>155</v>
@@ -9570,13 +10196,16 @@
       <c r="M187" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O187" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
+        <v>413</v>
+      </c>
+      <c r="B188" t="s">
         <v>414</v>
-      </c>
-      <c r="B188" t="s">
-        <v>415</v>
       </c>
       <c r="C188" t="s">
         <v>158</v>
@@ -9611,13 +10240,16 @@
       <c r="M188" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O188" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
+        <v>415</v>
+      </c>
+      <c r="B189" t="s">
         <v>416</v>
-      </c>
-      <c r="B189" t="s">
-        <v>417</v>
       </c>
       <c r="C189" t="s">
         <v>155</v>
@@ -9652,13 +10284,16 @@
       <c r="M189" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O189" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
+        <v>417</v>
+      </c>
+      <c r="B190" t="s">
         <v>418</v>
-      </c>
-      <c r="B190" t="s">
-        <v>419</v>
       </c>
       <c r="C190" t="s">
         <v>158</v>
@@ -9693,19 +10328,22 @@
       <c r="M190" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O190" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
+        <v>419</v>
+      </c>
+      <c r="B191" t="s">
         <v>420</v>
-      </c>
-      <c r="B191" t="s">
-        <v>421</v>
       </c>
       <c r="C191" t="s">
         <v>155</v>
       </c>
       <c r="D191" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="E191" t="s">
         <v>38</v>
@@ -9734,13 +10372,16 @@
       <c r="M191" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O191" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
+        <v>421</v>
+      </c>
+      <c r="B192" t="s">
         <v>422</v>
-      </c>
-      <c r="B192" t="s">
-        <v>423</v>
       </c>
       <c r="C192" t="s">
         <v>158</v>
@@ -9775,13 +10416,16 @@
       <c r="M192" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O192" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
+        <v>423</v>
+      </c>
+      <c r="B193" t="s">
         <v>424</v>
-      </c>
-      <c r="B193" t="s">
-        <v>425</v>
       </c>
       <c r="C193" t="s">
         <v>155</v>
@@ -9816,13 +10460,16 @@
       <c r="M193" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O193" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
+        <v>425</v>
+      </c>
+      <c r="B194" t="s">
         <v>426</v>
-      </c>
-      <c r="B194" t="s">
-        <v>427</v>
       </c>
       <c r="C194" t="s">
         <v>158</v>
@@ -9857,13 +10504,16 @@
       <c r="M194" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O194" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
+        <v>427</v>
+      </c>
+      <c r="B195" t="s">
         <v>428</v>
-      </c>
-      <c r="B195" t="s">
-        <v>429</v>
       </c>
       <c r="C195" t="s">
         <v>17</v>
@@ -9898,13 +10548,16 @@
       <c r="M195" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O195" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
+        <v>429</v>
+      </c>
+      <c r="B196" t="s">
         <v>430</v>
-      </c>
-      <c r="B196" t="s">
-        <v>431</v>
       </c>
       <c r="C196" t="s">
         <v>155</v>
@@ -9939,13 +10592,16 @@
       <c r="M196" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O196" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
+        <v>431</v>
+      </c>
+      <c r="B197" t="s">
         <v>432</v>
-      </c>
-      <c r="B197" t="s">
-        <v>433</v>
       </c>
       <c r="C197" t="s">
         <v>158</v>
@@ -9980,13 +10636,16 @@
       <c r="M197" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O197" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
+        <v>433</v>
+      </c>
+      <c r="B198" t="s">
         <v>434</v>
-      </c>
-      <c r="B198" t="s">
-        <v>435</v>
       </c>
       <c r="C198" t="s">
         <v>155</v>
@@ -10021,13 +10680,16 @@
       <c r="M198" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O198" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
+        <v>435</v>
+      </c>
+      <c r="B199" t="s">
         <v>436</v>
-      </c>
-      <c r="B199" t="s">
-        <v>437</v>
       </c>
       <c r="C199" t="s">
         <v>158</v>
@@ -10062,13 +10724,16 @@
       <c r="M199" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O199" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
+        <v>437</v>
+      </c>
+      <c r="B200" t="s">
         <v>438</v>
-      </c>
-      <c r="B200" t="s">
-        <v>439</v>
       </c>
       <c r="C200" t="s">
         <v>155</v>
@@ -10103,13 +10768,16 @@
       <c r="M200" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O200" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
+        <v>439</v>
+      </c>
+      <c r="B201" t="s">
         <v>440</v>
-      </c>
-      <c r="B201" t="s">
-        <v>441</v>
       </c>
       <c r="C201" t="s">
         <v>158</v>
@@ -10144,13 +10812,16 @@
       <c r="M201" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O201" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
+        <v>441</v>
+      </c>
+      <c r="B202" t="s">
         <v>442</v>
-      </c>
-      <c r="B202" t="s">
-        <v>443</v>
       </c>
       <c r="C202" t="s">
         <v>155</v>
@@ -10185,13 +10856,16 @@
       <c r="M202" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O202" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
+        <v>443</v>
+      </c>
+      <c r="B203" t="s">
         <v>444</v>
-      </c>
-      <c r="B203" t="s">
-        <v>445</v>
       </c>
       <c r="C203" t="s">
         <v>158</v>
@@ -10226,13 +10900,16 @@
       <c r="M203" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O203" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
+        <v>445</v>
+      </c>
+      <c r="B204" t="s">
         <v>446</v>
-      </c>
-      <c r="B204" t="s">
-        <v>447</v>
       </c>
       <c r="C204" t="s">
         <v>155</v>
@@ -10267,13 +10944,16 @@
       <c r="M204" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O204" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
+        <v>447</v>
+      </c>
+      <c r="B205" t="s">
         <v>448</v>
-      </c>
-      <c r="B205" t="s">
-        <v>449</v>
       </c>
       <c r="C205" t="s">
         <v>158</v>
@@ -10308,13 +10988,16 @@
       <c r="M205" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O205" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
+        <v>449</v>
+      </c>
+      <c r="B206" t="s">
         <v>450</v>
-      </c>
-      <c r="B206" t="s">
-        <v>451</v>
       </c>
       <c r="C206" t="s">
         <v>155</v>
@@ -10349,13 +11032,16 @@
       <c r="M206" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O206" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
+        <v>451</v>
+      </c>
+      <c r="B207" t="s">
         <v>452</v>
-      </c>
-      <c r="B207" t="s">
-        <v>453</v>
       </c>
       <c r="C207" t="s">
         <v>158</v>
@@ -10390,13 +11076,16 @@
       <c r="M207" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O207" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
+        <v>453</v>
+      </c>
+      <c r="B208" t="s">
         <v>454</v>
-      </c>
-      <c r="B208" t="s">
-        <v>455</v>
       </c>
       <c r="C208" t="s">
         <v>155</v>
@@ -10431,13 +11120,16 @@
       <c r="M208" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O208" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
+        <v>455</v>
+      </c>
+      <c r="B209" t="s">
         <v>456</v>
-      </c>
-      <c r="B209" t="s">
-        <v>457</v>
       </c>
       <c r="C209" t="s">
         <v>158</v>
@@ -10472,19 +11164,22 @@
       <c r="M209" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O209" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
+        <v>457</v>
+      </c>
+      <c r="B210" t="s">
         <v>458</v>
-      </c>
-      <c r="B210" t="s">
-        <v>459</v>
       </c>
       <c r="C210" t="s">
         <v>17</v>
       </c>
       <c r="D210" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="E210" t="s">
         <v>19</v>
@@ -10513,13 +11208,19 @@
       <c r="M210" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N210" t="s">
+        <v>487</v>
+      </c>
+      <c r="O210" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
+        <v>459</v>
+      </c>
+      <c r="B211" t="s">
         <v>460</v>
-      </c>
-      <c r="B211" t="s">
-        <v>461</v>
       </c>
       <c r="C211" t="s">
         <v>155</v>
@@ -10554,13 +11255,16 @@
       <c r="M211" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O211" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
+        <v>461</v>
+      </c>
+      <c r="B212" t="s">
         <v>462</v>
-      </c>
-      <c r="B212" t="s">
-        <v>463</v>
       </c>
       <c r="C212" t="s">
         <v>158</v>
@@ -10595,13 +11299,16 @@
       <c r="M212" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O212" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
+        <v>463</v>
+      </c>
+      <c r="B213" t="s">
         <v>464</v>
-      </c>
-      <c r="B213" t="s">
-        <v>465</v>
       </c>
       <c r="C213" t="s">
         <v>155</v>
@@ -10636,13 +11343,16 @@
       <c r="M213" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O213" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
+        <v>465</v>
+      </c>
+      <c r="B214" t="s">
         <v>466</v>
-      </c>
-      <c r="B214" t="s">
-        <v>467</v>
       </c>
       <c r="C214" t="s">
         <v>158</v>
@@ -10677,13 +11387,16 @@
       <c r="M214" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O214" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
+        <v>467</v>
+      </c>
+      <c r="B215" t="s">
         <v>468</v>
-      </c>
-      <c r="B215" t="s">
-        <v>469</v>
       </c>
       <c r="C215" t="s">
         <v>155</v>
@@ -10718,22 +11431,25 @@
       <c r="M215" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O215" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
+        <v>469</v>
+      </c>
+      <c r="B216" t="s">
         <v>470</v>
-      </c>
-      <c r="B216" t="s">
-        <v>471</v>
       </c>
       <c r="C216" t="s">
         <v>158</v>
       </c>
       <c r="D216" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="E216" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F216" t="s">
         <v>324</v>
@@ -10759,13 +11475,16 @@
       <c r="M216" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O216" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
+        <v>471</v>
+      </c>
+      <c r="B217" t="s">
         <v>472</v>
-      </c>
-      <c r="B217" t="s">
-        <v>473</v>
       </c>
       <c r="C217" t="s">
         <v>155</v>
@@ -10800,13 +11519,16 @@
       <c r="M217" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O217" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
+        <v>473</v>
+      </c>
+      <c r="B218" t="s">
         <v>474</v>
-      </c>
-      <c r="B218" t="s">
-        <v>475</v>
       </c>
       <c r="C218" t="s">
         <v>158</v>
@@ -10815,7 +11537,7 @@
         <v>56</v>
       </c>
       <c r="E218" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F218" t="s">
         <v>324</v>
@@ -10841,13 +11563,16 @@
       <c r="M218" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O218" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
+        <v>475</v>
+      </c>
+      <c r="B219" t="s">
         <v>476</v>
-      </c>
-      <c r="B219" t="s">
-        <v>477</v>
       </c>
       <c r="C219" t="s">
         <v>155</v>
@@ -10882,13 +11607,16 @@
       <c r="M219" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O219" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
+        <v>477</v>
+      </c>
+      <c r="B220" t="s">
         <v>478</v>
-      </c>
-      <c r="B220" t="s">
-        <v>479</v>
       </c>
       <c r="C220" t="s">
         <v>158</v>
@@ -10922,6 +11650,9 @@
       </c>
       <c r="M220" t="s">
         <v>152</v>
+      </c>
+      <c r="O220" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
